--- a/Versão5/EST/Ontologia_Geotecnica.xlsx
+++ b/Versão5/EST/Ontologia_Geotecnica.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GEOT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0757131-A58B-4E8F-8273-043F5D98D849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EFB9F4C-215F-4B7B-8426-2F5366EC6103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -2113,6 +2113,14 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2120,14 +2128,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2308,6 +2308,14 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2315,14 +2323,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2773,15 +2773,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="23" customWidth="1"/>
-    <col min="2" max="2" width="39.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="38" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="23"/>
+    <col min="1" max="1" width="9.3046875" style="23" customWidth="1"/>
+    <col min="2" max="2" width="39.15234375" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="38" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="10" t="s">
         <v>43</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="11" t="s">
         <v>45</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="11" t="s">
         <v>47</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="12" t="s">
         <v>48</v>
       </c>
@@ -2825,7 +2825,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="12" t="s">
         <v>49</v>
       </c>
@@ -2837,7 +2837,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>50</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>51</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
         <v>53</v>
       </c>
@@ -2871,7 +2871,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="12" t="s">
         <v>54</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="12" t="s">
         <v>56</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="12" t="s">
         <v>58</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="12" t="s">
         <v>59</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="12" t="s">
         <v>60</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="12" t="s">
         <v>61</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="12" t="s">
         <v>62</v>
       </c>
@@ -2948,7 +2948,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="12" t="s">
         <v>63</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="12" t="s">
         <v>64</v>
       </c>
@@ -2970,19 +2970,19 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="12" t="s">
         <v>65</v>
       </c>
       <c r="B18" s="25">
         <f ca="1">NOW()</f>
-        <v>46244.672876504628</v>
+        <v>46249.396070023147</v>
       </c>
       <c r="C18" s="37" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="12" t="s">
         <v>93</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="12" t="s">
         <v>90</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="12" t="s">
         <v>92</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="12" t="s">
         <v>66</v>
       </c>
@@ -3028,7 +3028,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="12" t="s">
         <v>67</v>
       </c>
@@ -3039,7 +3039,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="12" t="s">
         <v>68</v>
       </c>
@@ -3050,7 +3050,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="12" t="s">
         <v>69</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="12" t="s">
         <v>84</v>
       </c>
@@ -3081,34 +3081,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A56445-53D9-475A-B2C6-D376FC6516D5}">
   <dimension ref="A1:AA51"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8" style="61" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="84.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="82" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="43.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="68.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.4609375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.23046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.3828125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.4609375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.4609375" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="5.07421875" style="61" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.3828125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.765625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.53515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.53515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="62.61328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="61.15234375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.3828125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.765625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.4609375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.921875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.3046875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="31.07421875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="19.3828125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.23046875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="51.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="36.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="22">
         <v>1</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="50">
         <v>2</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="50">
         <v>3</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="50">
         <v>4</v>
       </c>
@@ -3464,7 +3464,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="50">
         <v>5</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="50">
         <v>6</v>
       </c>
@@ -3646,7 +3646,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="50">
         <v>7</v>
       </c>
@@ -3737,7 +3737,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="50">
         <v>8</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="50">
         <v>9</v>
       </c>
@@ -3919,7 +3919,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="50">
         <v>10</v>
       </c>
@@ -4010,7 +4010,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="50">
         <v>11</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="50">
         <v>12</v>
       </c>
@@ -4192,7 +4192,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="50">
         <v>13</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="50">
         <v>14</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="50">
         <v>15</v>
       </c>
@@ -4465,7 +4465,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="50">
         <v>16</v>
       </c>
@@ -4556,7 +4556,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="50">
         <v>17</v>
       </c>
@@ -4647,7 +4647,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="50">
         <v>18</v>
       </c>
@@ -4738,7 +4738,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="50">
         <v>19</v>
       </c>
@@ -4829,7 +4829,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="50">
         <v>20</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="50">
         <v>21</v>
       </c>
@@ -5011,7 +5011,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="50">
         <v>22</v>
       </c>
@@ -5102,7 +5102,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="50">
         <v>23</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="50">
         <v>24</v>
       </c>
@@ -5284,7 +5284,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="50">
         <v>25</v>
       </c>
@@ -5375,7 +5375,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="50">
         <v>26</v>
       </c>
@@ -5466,7 +5466,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="50">
         <v>27</v>
       </c>
@@ -5557,7 +5557,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="50">
         <v>28</v>
       </c>
@@ -5648,7 +5648,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="50">
         <v>29</v>
       </c>
@@ -5739,7 +5739,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="50">
         <v>30</v>
       </c>
@@ -5830,7 +5830,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="50">
         <v>31</v>
       </c>
@@ -5921,7 +5921,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="50">
         <v>32</v>
       </c>
@@ -6012,7 +6012,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="50">
         <v>33</v>
       </c>
@@ -6103,7 +6103,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="50">
         <v>34</v>
       </c>
@@ -6194,7 +6194,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="50">
         <v>35</v>
       </c>
@@ -6285,7 +6285,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="50">
         <v>36</v>
       </c>
@@ -6376,7 +6376,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="50">
         <v>37</v>
       </c>
@@ -6467,7 +6467,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="50">
         <v>38</v>
       </c>
@@ -6558,7 +6558,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="50">
         <v>39</v>
       </c>
@@ -6649,7 +6649,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="50">
         <v>40</v>
       </c>
@@ -6740,7 +6740,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="50">
         <v>41</v>
       </c>
@@ -6831,7 +6831,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="50">
         <v>42</v>
       </c>
@@ -6922,7 +6922,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="50">
         <v>43</v>
       </c>
@@ -7013,7 +7013,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="50">
         <v>44</v>
       </c>
@@ -7104,7 +7104,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="50">
         <v>45</v>
       </c>
@@ -7195,7 +7195,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="50">
         <v>46</v>
       </c>
@@ -7286,7 +7286,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="50">
         <v>47</v>
       </c>
@@ -7377,7 +7377,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="50">
         <v>48</v>
       </c>
@@ -7468,7 +7468,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="50">
         <v>49</v>
       </c>
@@ -7559,7 +7559,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="50">
         <v>50</v>
       </c>
@@ -7650,7 +7650,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="50">
         <v>51</v>
       </c>
@@ -7746,7 +7746,7 @@
     <sortCondition ref="E1:E804"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="AA2:AA51 A2:B51">
+  <conditionalFormatting sqref="A2:B51 AA2:AA51">
     <cfRule type="cellIs" dxfId="62" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
@@ -7756,14 +7756,14 @@
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F1048576">
+    <cfRule type="duplicateValues" dxfId="60" priority="52"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F2:F27">
-    <cfRule type="cellIs" dxfId="60" priority="58" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="58" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="59" priority="1040"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="58" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="1040"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28:F45 Q2:Q51 P28:P29 AB28:XFD29 P34:P41 AB34:XFD41 P43:P45 AB43:XFD45">
     <cfRule type="cellIs" dxfId="57" priority="119" operator="equal">
@@ -7772,8 +7772,8 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="F28:F45">
     <cfRule type="duplicateValues" dxfId="56" priority="1019"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="1021"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="1022"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="1022"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="1021"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F46:F47">
     <cfRule type="duplicateValues" dxfId="53" priority="989"/>
@@ -7785,11 +7785,11 @@
     <cfRule type="duplicateValues" dxfId="51" priority="253"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52:F1048576">
-    <cfRule type="duplicateValues" dxfId="50" priority="245"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="754"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="782"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="769"/>
     <cfRule type="duplicateValues" dxfId="48" priority="762"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="769"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="782"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="754"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="245"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="W52:W1048576 W1">
     <cfRule type="duplicateValues" dxfId="45" priority="581"/>
@@ -7801,10 +7801,10 @@
     <cfRule type="duplicateValues" dxfId="41" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2">
-    <cfRule type="cellIs" dxfId="40" priority="82" operator="equal">
+    <cfRule type="duplicateValues" dxfId="40" priority="83"/>
+    <cfRule type="cellIs" dxfId="39" priority="82" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="39" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y3">
     <cfRule type="duplicateValues" dxfId="38" priority="78"/>
@@ -7822,17 +7822,17 @@
     <cfRule type="duplicateValues" dxfId="32" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y9">
-    <cfRule type="duplicateValues" dxfId="31" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="41"/>
     <cfRule type="duplicateValues" dxfId="29" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y10:Y14">
-    <cfRule type="duplicateValues" dxfId="26" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y15:Y16">
     <cfRule type="duplicateValues" dxfId="22" priority="26"/>
@@ -7841,15 +7841,15 @@
     <cfRule type="duplicateValues" dxfId="19" priority="29"/>
     <cfRule type="duplicateValues" dxfId="18" priority="30"/>
     <cfRule type="duplicateValues" dxfId="17" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y17:Y18">
-    <cfRule type="duplicateValues" dxfId="14" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="47"/>
     <cfRule type="duplicateValues" dxfId="12" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y19:Y27">
     <cfRule type="duplicateValues" dxfId="9" priority="84"/>
@@ -7867,15 +7867,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="8" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="9" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="7" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="7"/>
+    <col min="1" max="1" width="2.84375" style="8" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="9" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="7" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -7940,7 +7940,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="3" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="3" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>2</v>
       </c>
@@ -8022,15 +8022,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" style="15" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" style="14" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="7.53515625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="19">
         <v>0</v>
       </c>
@@ -8053,7 +8053,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -8096,27 +8096,27 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A426B82-2E19-47C6-9DDF-914E7B26E6D0}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.2" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="33" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" style="32" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.3046875" style="32" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" style="32" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.28515625" style="32" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.85546875" style="32" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.28515625" style="34" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" style="34" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.3046875" style="32" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.84375" style="32" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.3046875" style="34" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.53515625" style="34" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="34" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28" style="34" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.28515625" style="34" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="34" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" style="34" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" style="34" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" style="34" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" style="33" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.28515625" style="32"/>
+    <col min="10" max="10" width="4.3046875" style="34" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.84375" style="34" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3046875" style="34" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.84375" style="34" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.3046875" style="34" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.84375" style="33" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.3046875" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="28" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="28" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="26" t="s">
         <v>10</v>
       </c>
@@ -8161,7 +8161,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:15" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="31">
         <v>1</v>
       </c>
@@ -8210,7 +8210,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:XFD1 A3:XFD1048576 A2:B2 D2:XFD2">
+  <conditionalFormatting sqref="A1:XFD1 A2:B2 A3:XFD1048576 D2:XFD2">
     <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>

--- a/Versão5/EST/Ontologia_Geotecnica.xlsx
+++ b/Versão5/EST/Ontologia_Geotecnica.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EFB9F4C-215F-4B7B-8426-2F5366EC6103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADEC542C-DDD0-4C61-A76B-ECA649CC0911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="FatosIn" sheetId="28" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Classes!$A$1:$AA$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Classes!$A$1:$AC$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Interop!$B$1:$B$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="383">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -500,9 +500,6 @@
     <t>GeoTécnico</t>
   </si>
   <si>
-    <t>ClasseIFC</t>
-  </si>
-  <si>
     <t>[ 3E ]</t>
   </si>
   <si>
@@ -1215,6 +1212,15 @@
   </si>
   <si>
     <t>"Conjunto de Informação Geotécnica do projeto A"</t>
+  </si>
+  <si>
+    <t>Parâmetro Rvt</t>
+  </si>
+  <si>
+    <t>Atributo IFC</t>
+  </si>
+  <si>
+    <t>Classe IFC</t>
   </si>
 </sst>
 </file>
@@ -1731,7 +1737,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="63">
+  <dxfs count="64">
     <dxf>
       <font>
         <b val="0"/>
@@ -1801,6 +1807,14 @@
         <i/>
         <strike val="0"/>
         <color rgb="FFFFFFFF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -2113,14 +2127,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2128,6 +2134,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -2773,15 +2787,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.3046875" style="23" customWidth="1"/>
-    <col min="2" max="2" width="39.15234375" style="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="38" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="23"/>
+    <col min="1" max="1" width="9.28515625" style="23" customWidth="1"/>
+    <col min="2" max="2" width="39.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="38" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>43</v>
       </c>
@@ -2792,7 +2806,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>45</v>
       </c>
@@ -2803,7 +2817,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>47</v>
       </c>
@@ -2814,7 +2828,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>48</v>
       </c>
@@ -2825,7 +2839,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>49</v>
       </c>
@@ -2837,7 +2851,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>50</v>
       </c>
@@ -2849,7 +2863,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>51</v>
       </c>
@@ -2860,7 +2874,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>53</v>
       </c>
@@ -2871,7 +2885,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>54</v>
       </c>
@@ -2882,7 +2896,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>56</v>
       </c>
@@ -2893,7 +2907,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>58</v>
       </c>
@@ -2904,7 +2918,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>59</v>
       </c>
@@ -2915,7 +2929,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>60</v>
       </c>
@@ -2926,7 +2940,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>61</v>
       </c>
@@ -2937,7 +2951,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>62</v>
       </c>
@@ -2948,7 +2962,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>63</v>
       </c>
@@ -2959,30 +2973,30 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>64</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C17" s="37" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>65</v>
       </c>
       <c r="B18" s="25">
         <f ca="1">NOW()</f>
-        <v>46249.396070023147</v>
+        <v>46253.68390960648</v>
       </c>
       <c r="C18" s="37" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>93</v>
       </c>
@@ -2993,7 +3007,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>90</v>
       </c>
@@ -3005,7 +3019,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
         <v>92</v>
       </c>
@@ -3017,7 +3031,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>66</v>
       </c>
@@ -3028,7 +3042,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>67</v>
       </c>
@@ -3039,29 +3053,29 @@
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>68</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C24" s="37" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>69</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C25" s="37" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>84</v>
       </c>
@@ -3080,35 +3094,37 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A56445-53D9-475A-B2C6-D376FC6516D5}">
-  <dimension ref="A1:AA51"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AC51"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.23046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.3828125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.4609375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.4609375" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="5.07421875" style="61" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.3828125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.765625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.53515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.53515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="62.61328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="61.15234375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.3828125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.765625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.4609375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.921875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.3046875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="31.07421875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="19.3828125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.23046875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="51.3828125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8" style="61" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="84.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="82" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="68.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="22" customWidth="1"/>
+    <col min="28" max="28" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="36.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22">
         <v>1</v>
       </c>
@@ -3160,55 +3176,61 @@
       <c r="Q1" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="R1" s="29" t="s">
+      <c r="R1" s="54" t="s">
+        <v>83</v>
+      </c>
+      <c r="S1" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="S1" s="29" t="s">
+      <c r="T1" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="T1" s="29" t="s">
+      <c r="U1" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="U1" s="29" t="s">
+      <c r="V1" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="V1" s="29" t="s">
+      <c r="W1" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="W1" s="51" t="s">
+      <c r="X1" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="X1" s="53" t="s">
+      <c r="Y1" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="Y1" s="53" t="s">
-        <v>142</v>
-      </c>
       <c r="Z1" s="53" t="s">
+        <v>380</v>
+      </c>
+      <c r="AA1" s="53" t="s">
+        <v>382</v>
+      </c>
+      <c r="AB1" s="53" t="s">
+        <v>381</v>
+      </c>
+      <c r="AC1" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="AA1" s="54" t="s">
-        <v>83</v>
-      </c>
     </row>
-    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="50">
         <v>2</v>
       </c>
       <c r="B2" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C2" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C2" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D2" s="55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E2" s="55" t="s">
         <v>127</v>
       </c>
       <c r="F2" s="56" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>9</v>
@@ -3248,58 +3270,64 @@
         <v>129</v>
       </c>
       <c r="R2" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="21" t="str">
-        <f t="shared" ref="S2:U2" si="4">SUBSTITUTE(C2, "_", " ")</f>
-        <v>GeoTécnicos</v>
+        <v>286</v>
+      </c>
+      <c r="S2" s="21" t="s">
+        <v>9</v>
       </c>
       <c r="T2" s="21" t="str">
+        <f t="shared" ref="T2:V2" si="4">SUBSTITUTE(C2, "_", " ")</f>
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="U2" s="21" t="str">
         <f t="shared" si="4"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U2" s="21" t="str">
+      <c r="V2" s="21" t="str">
         <f t="shared" si="4"/>
         <v>Compactação</v>
       </c>
-      <c r="V2" s="21" t="s">
+      <c r="W2" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W2" s="58" t="str">
-        <f t="shared" ref="W2:W51" si="5">CONCATENATE("Key-GEO-",A2)</f>
+      <c r="X2" s="58" t="str">
+        <f t="shared" ref="X2:X51" si="5">CONCATENATE("Key-GEO-",A2)</f>
         <v>Key-GEO-2</v>
       </c>
-      <c r="X2" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y2" s="60" t="s">
-        <v>271</v>
-      </c>
-      <c r="Z2" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA2" s="21" t="s">
-        <v>287</v>
+        <v>214</v>
+      </c>
+      <c r="Z2" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA2" s="60" t="s">
+        <v>270</v>
+      </c>
+      <c r="AB2" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC2" s="21" t="s">
+        <v>276</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="50">
         <v>3</v>
       </c>
       <c r="B3" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C3" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C3" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D3" s="55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E3" s="55" t="s">
         <v>127</v>
       </c>
       <c r="F3" s="56" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>9</v>
@@ -3336,61 +3364,67 @@
         <v>130</v>
       </c>
       <c r="Q3" s="35" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S3" s="21" t="str">
-        <f t="shared" ref="S3:S51" si="10">SUBSTITUTE(C3, "_", " ")</f>
-        <v>GeoTécnicos</v>
+        <v>287</v>
+      </c>
+      <c r="S3" s="21" t="s">
+        <v>9</v>
       </c>
       <c r="T3" s="21" t="str">
-        <f t="shared" ref="T3:T51" si="11">SUBSTITUTE(D3, "_", " ")</f>
+        <f t="shared" ref="T3:T51" si="10">SUBSTITUTE(C3, "_", " ")</f>
+        <v>GeoTécnicos</v>
+      </c>
+      <c r="U3" s="21" t="str">
+        <f t="shared" ref="U3:U51" si="11">SUBSTITUTE(D3, "_", " ")</f>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U3" s="21" t="str">
-        <f t="shared" ref="U3:U51" si="12">SUBSTITUTE(E3, "_", " ")</f>
+      <c r="V3" s="21" t="str">
+        <f t="shared" ref="V3:V51" si="12">SUBSTITUTE(E3, "_", " ")</f>
         <v>Compactação</v>
       </c>
-      <c r="V3" s="21" t="s">
+      <c r="W3" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W3" s="58" t="str">
+      <c r="X3" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-3</v>
       </c>
-      <c r="X3" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y3" s="60" t="s">
-        <v>270</v>
-      </c>
-      <c r="Z3" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA3" s="21" t="s">
-        <v>288</v>
+        <v>214</v>
+      </c>
+      <c r="Z3" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA3" s="60" t="s">
+        <v>269</v>
+      </c>
+      <c r="AB3" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC3" s="21" t="s">
+        <v>276</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="50">
         <v>4</v>
       </c>
       <c r="B4" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C4" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C4" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D4" s="55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E4" s="55" t="s">
         <v>127</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>9</v>
@@ -3427,61 +3461,67 @@
         <v>131</v>
       </c>
       <c r="Q4" s="35" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="R4" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S4" s="21" t="str">
+        <v>288</v>
+      </c>
+      <c r="S4" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T4" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T4" s="21" t="str">
+      <c r="U4" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U4" s="21" t="str">
+      <c r="V4" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Compactação</v>
       </c>
-      <c r="V4" s="21" t="s">
+      <c r="W4" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W4" s="58" t="str">
+      <c r="X4" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-4</v>
       </c>
-      <c r="X4" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y4" s="60" t="s">
-        <v>269</v>
-      </c>
-      <c r="Z4" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA4" s="21" t="s">
-        <v>289</v>
+        <v>214</v>
+      </c>
+      <c r="Z4" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA4" s="60" t="s">
+        <v>268</v>
+      </c>
+      <c r="AB4" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC4" s="21" t="s">
+        <v>276</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="50">
         <v>5</v>
       </c>
       <c r="B5" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C5" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C5" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D5" s="55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E5" s="55" t="s">
         <v>127</v>
       </c>
       <c r="F5" s="56" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>9</v>
@@ -3518,61 +3558,67 @@
         <v>132</v>
       </c>
       <c r="Q5" s="35" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="R5" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S5" s="21" t="str">
+        <v>289</v>
+      </c>
+      <c r="S5" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T5" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T5" s="21" t="str">
+      <c r="U5" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U5" s="21" t="str">
+      <c r="V5" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Compactação</v>
       </c>
-      <c r="V5" s="21" t="s">
+      <c r="W5" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W5" s="58" t="str">
+      <c r="X5" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-5</v>
       </c>
-      <c r="X5" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y5" s="60" t="s">
-        <v>268</v>
-      </c>
-      <c r="Z5" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA5" s="21" t="s">
-        <v>290</v>
+        <v>214</v>
+      </c>
+      <c r="Z5" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA5" s="60" t="s">
+        <v>267</v>
+      </c>
+      <c r="AB5" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC5" s="21" t="s">
+        <v>276</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="50">
         <v>6</v>
       </c>
       <c r="B6" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C6" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C6" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D6" s="55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E6" s="55" t="s">
         <v>127</v>
       </c>
       <c r="F6" s="56" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>9</v>
@@ -3609,61 +3655,67 @@
         <v>133</v>
       </c>
       <c r="Q6" s="35" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R6" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S6" s="21" t="str">
+        <v>290</v>
+      </c>
+      <c r="S6" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T6" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T6" s="21" t="str">
+      <c r="U6" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U6" s="21" t="str">
+      <c r="V6" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Compactação</v>
       </c>
-      <c r="V6" s="21" t="s">
+      <c r="W6" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W6" s="58" t="str">
+      <c r="X6" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-6</v>
       </c>
-      <c r="X6" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y6" s="60" t="s">
-        <v>267</v>
-      </c>
-      <c r="Z6" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA6" s="21" t="s">
-        <v>291</v>
+        <v>214</v>
+      </c>
+      <c r="Z6" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA6" s="60" t="s">
+        <v>266</v>
+      </c>
+      <c r="AB6" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC6" s="21" t="s">
+        <v>276</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="50">
         <v>7</v>
       </c>
       <c r="B7" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C7" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C7" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D7" s="55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E7" s="55" t="s">
         <v>127</v>
       </c>
       <c r="F7" s="56" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>9</v>
@@ -3697,64 +3749,70 @@
         <v>Solo Reforçado PréCarregado</v>
       </c>
       <c r="P7" s="21" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Q7" s="35" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="R7" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S7" s="21" t="str">
+        <v>291</v>
+      </c>
+      <c r="S7" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T7" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T7" s="21" t="str">
+      <c r="U7" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U7" s="21" t="str">
+      <c r="V7" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Compactação</v>
       </c>
-      <c r="V7" s="21" t="s">
+      <c r="W7" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W7" s="58" t="str">
+      <c r="X7" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-7</v>
       </c>
-      <c r="X7" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y7" s="60" t="s">
-        <v>266</v>
-      </c>
-      <c r="Z7" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA7" s="21" t="s">
-        <v>292</v>
+        <v>214</v>
+      </c>
+      <c r="Z7" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA7" s="60" t="s">
+        <v>265</v>
+      </c>
+      <c r="AB7" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC7" s="21" t="s">
+        <v>276</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="50">
         <v>8</v>
       </c>
       <c r="B8" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C8" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C8" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D8" s="55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E8" s="55" t="s">
         <v>127</v>
       </c>
       <c r="F8" s="56" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>9</v>
@@ -3788,64 +3846,70 @@
         <v>Solo Reforçado Drenado</v>
       </c>
       <c r="P8" s="21" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Q8" s="35" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="R8" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S8" s="21" t="str">
+        <v>292</v>
+      </c>
+      <c r="S8" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T8" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T8" s="21" t="str">
+      <c r="U8" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U8" s="21" t="str">
+      <c r="V8" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Compactação</v>
       </c>
-      <c r="V8" s="21" t="s">
+      <c r="W8" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W8" s="58" t="str">
+      <c r="X8" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-8</v>
       </c>
-      <c r="X8" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y8" s="60" t="s">
-        <v>265</v>
-      </c>
-      <c r="Z8" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA8" s="21" t="s">
-        <v>293</v>
+        <v>214</v>
+      </c>
+      <c r="Z8" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA8" s="60" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB8" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC8" s="21" t="s">
+        <v>276</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="50">
         <v>9</v>
       </c>
       <c r="B9" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C9" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C9" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D9" s="55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E9" s="55" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F9" s="56" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>9</v>
@@ -3882,61 +3946,67 @@
         <v>97</v>
       </c>
       <c r="Q9" s="35" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="R9" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S9" s="21" t="str">
+        <v>293</v>
+      </c>
+      <c r="S9" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T9" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T9" s="21" t="str">
+      <c r="U9" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U9" s="21" t="str">
+      <c r="V9" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Escavações</v>
       </c>
-      <c r="V9" s="21" t="s">
+      <c r="W9" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W9" s="58" t="str">
+      <c r="X9" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-9</v>
       </c>
-      <c r="X9" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y9" s="60" t="s">
-        <v>255</v>
-      </c>
-      <c r="Z9" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA9" s="21" t="s">
-        <v>294</v>
+        <v>214</v>
+      </c>
+      <c r="Z9" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA9" s="60" t="s">
+        <v>254</v>
+      </c>
+      <c r="AB9" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC9" s="21" t="s">
+        <v>276</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="50">
         <v>10</v>
       </c>
       <c r="B10" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C10" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C10" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D10" s="55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E10" s="55" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F10" s="56" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>9</v>
@@ -3973,61 +4043,67 @@
         <v>98</v>
       </c>
       <c r="Q10" s="35" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="R10" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S10" s="21" t="str">
+        <v>294</v>
+      </c>
+      <c r="S10" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T10" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T10" s="21" t="str">
+      <c r="U10" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U10" s="21" t="str">
+      <c r="V10" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Escavações</v>
       </c>
-      <c r="V10" s="21" t="s">
+      <c r="W10" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W10" s="58" t="str">
+      <c r="X10" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-10</v>
       </c>
-      <c r="X10" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y10" s="60" t="s">
-        <v>254</v>
-      </c>
-      <c r="Z10" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA10" s="21" t="s">
-        <v>295</v>
+        <v>214</v>
+      </c>
+      <c r="Z10" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA10" s="60" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB10" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC10" s="21" t="s">
+        <v>276</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="50">
         <v>11</v>
       </c>
       <c r="B11" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C11" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C11" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D11" s="55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E11" s="55" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F11" s="56" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>9</v>
@@ -4064,61 +4140,67 @@
         <v>99</v>
       </c>
       <c r="Q11" s="35" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="R11" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S11" s="21" t="str">
+        <v>295</v>
+      </c>
+      <c r="S11" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T11" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T11" s="21" t="str">
+      <c r="U11" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U11" s="21" t="str">
+      <c r="V11" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Escavações</v>
       </c>
-      <c r="V11" s="21" t="s">
+      <c r="W11" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W11" s="58" t="str">
+      <c r="X11" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-11</v>
       </c>
-      <c r="X11" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y11" s="60" t="s">
-        <v>253</v>
-      </c>
-      <c r="Z11" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA11" s="21" t="s">
-        <v>296</v>
+        <v>214</v>
+      </c>
+      <c r="Z11" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA11" s="60" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB11" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC11" s="21" t="s">
+        <v>276</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="50">
         <v>12</v>
       </c>
       <c r="B12" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C12" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C12" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D12" s="55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E12" s="55" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F12" s="56" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>9</v>
@@ -4155,61 +4237,67 @@
         <v>100</v>
       </c>
       <c r="Q12" s="35" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="R12" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S12" s="21" t="str">
+        <v>296</v>
+      </c>
+      <c r="S12" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T12" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T12" s="21" t="str">
+      <c r="U12" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U12" s="21" t="str">
+      <c r="V12" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Escavações</v>
       </c>
-      <c r="V12" s="21" t="s">
+      <c r="W12" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W12" s="58" t="str">
+      <c r="X12" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-12</v>
       </c>
-      <c r="X12" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y12" s="60" t="s">
-        <v>252</v>
-      </c>
-      <c r="Z12" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA12" s="21" t="s">
-        <v>297</v>
+        <v>214</v>
+      </c>
+      <c r="Z12" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA12" s="60" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB12" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC12" s="21" t="s">
+        <v>276</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="50">
         <v>13</v>
       </c>
       <c r="B13" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C13" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C13" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D13" s="55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E13" s="55" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F13" s="56" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>9</v>
@@ -4249,58 +4337,64 @@
         <v>102</v>
       </c>
       <c r="R13" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S13" s="21" t="str">
+        <v>297</v>
+      </c>
+      <c r="S13" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T13" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T13" s="21" t="str">
+      <c r="U13" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U13" s="21" t="str">
+      <c r="V13" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Escavações</v>
       </c>
-      <c r="V13" s="21" t="s">
+      <c r="W13" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W13" s="58" t="str">
+      <c r="X13" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-13</v>
       </c>
-      <c r="X13" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y13" s="60" t="s">
-        <v>251</v>
-      </c>
-      <c r="Z13" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA13" s="21" t="s">
-        <v>298</v>
+        <v>214</v>
+      </c>
+      <c r="Z13" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA13" s="60" t="s">
+        <v>250</v>
+      </c>
+      <c r="AB13" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC13" s="21" t="s">
+        <v>276</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="50">
         <v>14</v>
       </c>
       <c r="B14" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C14" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C14" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D14" s="55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E14" s="55" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F14" s="56" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>9</v>
@@ -4337,61 +4431,67 @@
         <v>103</v>
       </c>
       <c r="Q14" s="35" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="R14" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S14" s="21" t="str">
+        <v>298</v>
+      </c>
+      <c r="S14" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T14" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T14" s="21" t="str">
+      <c r="U14" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U14" s="21" t="str">
+      <c r="V14" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Escavações</v>
       </c>
-      <c r="V14" s="21" t="s">
+      <c r="W14" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W14" s="58" t="str">
+      <c r="X14" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-14</v>
       </c>
-      <c r="X14" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y14" s="60" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z14" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA14" s="21" t="s">
-        <v>299</v>
+        <v>214</v>
+      </c>
+      <c r="Z14" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA14" s="60" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB14" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC14" s="21" t="s">
+        <v>276</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="50">
         <v>15</v>
       </c>
       <c r="B15" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C15" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C15" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D15" s="55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E15" s="55" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F15" s="56" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>9</v>
@@ -4428,61 +4528,67 @@
         <v>104</v>
       </c>
       <c r="Q15" s="35" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="R15" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S15" s="21" t="str">
+        <v>299</v>
+      </c>
+      <c r="S15" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T15" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T15" s="21" t="str">
+      <c r="U15" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U15" s="21" t="str">
+      <c r="V15" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Escavações</v>
       </c>
-      <c r="V15" s="21" t="s">
+      <c r="W15" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W15" s="58" t="str">
+      <c r="X15" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-15</v>
       </c>
-      <c r="X15" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y15" s="60" t="s">
-        <v>249</v>
-      </c>
-      <c r="Z15" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA15" s="21" t="s">
-        <v>300</v>
+        <v>214</v>
+      </c>
+      <c r="Z15" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA15" s="60" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB15" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC15" s="21" t="s">
+        <v>276</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="50">
         <v>16</v>
       </c>
       <c r="B16" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C16" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C16" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D16" s="55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E16" s="55" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F16" s="56" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>9</v>
@@ -4519,61 +4625,67 @@
         <v>105</v>
       </c>
       <c r="Q16" s="35" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="R16" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S16" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="S16" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T16" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T16" s="21" t="str">
+      <c r="U16" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U16" s="21" t="str">
+      <c r="V16" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Escavações</v>
       </c>
-      <c r="V16" s="21" t="s">
+      <c r="W16" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W16" s="58" t="str">
+      <c r="X16" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-16</v>
       </c>
-      <c r="X16" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y16" s="60" t="s">
-        <v>248</v>
-      </c>
-      <c r="Z16" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA16" s="21" t="s">
-        <v>301</v>
+        <v>214</v>
+      </c>
+      <c r="Z16" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA16" s="60" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB16" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC16" s="21" t="s">
+        <v>276</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="50">
         <v>17</v>
       </c>
       <c r="B17" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C17" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C17" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D17" s="55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E17" s="55" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F17" s="56" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>9</v>
@@ -4610,61 +4722,67 @@
         <v>106</v>
       </c>
       <c r="Q17" s="35" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="R17" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S17" s="21" t="str">
+        <v>301</v>
+      </c>
+      <c r="S17" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T17" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T17" s="21" t="str">
+      <c r="U17" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U17" s="21" t="str">
+      <c r="V17" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Escavações</v>
       </c>
-      <c r="V17" s="21" t="s">
+      <c r="W17" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W17" s="58" t="str">
+      <c r="X17" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-17</v>
       </c>
-      <c r="X17" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y17" s="60" t="s">
-        <v>247</v>
-      </c>
-      <c r="Z17" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA17" s="21" t="s">
-        <v>302</v>
+        <v>214</v>
+      </c>
+      <c r="Z17" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA17" s="60" t="s">
+        <v>246</v>
+      </c>
+      <c r="AB17" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC17" s="21" t="s">
+        <v>276</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="50">
         <v>18</v>
       </c>
       <c r="B18" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C18" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C18" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D18" s="55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E18" s="55" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F18" s="56" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>9</v>
@@ -4701,61 +4819,67 @@
         <v>107</v>
       </c>
       <c r="Q18" s="35" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R18" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S18" s="21" t="str">
+        <v>302</v>
+      </c>
+      <c r="S18" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T18" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T18" s="21" t="str">
+      <c r="U18" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U18" s="21" t="str">
+      <c r="V18" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Escavações</v>
       </c>
-      <c r="V18" s="21" t="s">
+      <c r="W18" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W18" s="58" t="str">
+      <c r="X18" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-18</v>
       </c>
-      <c r="X18" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y18" s="60" t="s">
-        <v>246</v>
-      </c>
-      <c r="Z18" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA18" s="21" t="s">
-        <v>303</v>
+        <v>214</v>
+      </c>
+      <c r="Z18" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA18" s="60" t="s">
+        <v>245</v>
+      </c>
+      <c r="AB18" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC18" s="21" t="s">
+        <v>276</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="50">
         <v>19</v>
       </c>
       <c r="B19" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C19" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C19" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D19" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="E19" s="55" t="s">
         <v>239</v>
       </c>
-      <c r="E19" s="55" t="s">
+      <c r="F19" s="56" t="s">
         <v>240</v>
-      </c>
-      <c r="F19" s="56" t="s">
-        <v>241</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>9</v>
@@ -4792,61 +4916,67 @@
         <v>108</v>
       </c>
       <c r="Q19" s="35" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="R19" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S19" s="21" t="str">
+        <v>109</v>
+      </c>
+      <c r="S19" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T19" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T19" s="21" t="str">
+      <c r="U19" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U19" s="21" t="str">
+      <c r="V19" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="V19" s="21" t="s">
+      <c r="W19" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W19" s="58" t="str">
+      <c r="X19" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-19</v>
       </c>
-      <c r="X19" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y19" s="60" t="s">
-        <v>264</v>
-      </c>
-      <c r="Z19" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="AA19" s="21" t="s">
-        <v>109</v>
+        <v>214</v>
+      </c>
+      <c r="Z19" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA19" s="60" t="s">
+        <v>263</v>
+      </c>
+      <c r="AB19" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC19" s="21" t="s">
+        <v>277</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="50">
         <v>20</v>
       </c>
       <c r="B20" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C20" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C20" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D20" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="E20" s="55" t="s">
         <v>239</v>
       </c>
-      <c r="E20" s="55" t="s">
-        <v>240</v>
-      </c>
       <c r="F20" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>9</v>
@@ -4883,61 +5013,67 @@
         <v>110</v>
       </c>
       <c r="Q20" s="35" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="R20" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S20" s="21" t="str">
+        <v>303</v>
+      </c>
+      <c r="S20" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T20" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T20" s="21" t="str">
+      <c r="U20" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U20" s="21" t="str">
+      <c r="V20" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="V20" s="21" t="s">
+      <c r="W20" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W20" s="58" t="str">
+      <c r="X20" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-20</v>
       </c>
-      <c r="X20" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y20" s="60" t="s">
-        <v>263</v>
-      </c>
-      <c r="Z20" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="AA20" s="21" t="s">
-        <v>304</v>
+        <v>214</v>
+      </c>
+      <c r="Z20" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA20" s="60" t="s">
+        <v>262</v>
+      </c>
+      <c r="AB20" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC20" s="21" t="s">
+        <v>277</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="50">
         <v>21</v>
       </c>
       <c r="B21" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C21" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C21" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D21" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="E21" s="55" t="s">
         <v>239</v>
       </c>
-      <c r="E21" s="55" t="s">
-        <v>240</v>
-      </c>
       <c r="F21" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>9</v>
@@ -4974,61 +5110,67 @@
         <v>111</v>
       </c>
       <c r="Q21" s="35" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="R21" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S21" s="21" t="str">
+        <v>304</v>
+      </c>
+      <c r="S21" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T21" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T21" s="21" t="str">
+      <c r="U21" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U21" s="21" t="str">
+      <c r="V21" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="V21" s="21" t="s">
+      <c r="W21" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W21" s="58" t="str">
+      <c r="X21" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-21</v>
       </c>
-      <c r="X21" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y21" s="60" t="s">
-        <v>262</v>
-      </c>
-      <c r="Z21" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="AA21" s="21" t="s">
-        <v>305</v>
+        <v>214</v>
+      </c>
+      <c r="Z21" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA21" s="60" t="s">
+        <v>261</v>
+      </c>
+      <c r="AB21" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC21" s="21" t="s">
+        <v>277</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="50">
         <v>22</v>
       </c>
       <c r="B22" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C22" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C22" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D22" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="E22" s="55" t="s">
         <v>239</v>
       </c>
-      <c r="E22" s="55" t="s">
-        <v>240</v>
-      </c>
       <c r="F22" s="56" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>9</v>
@@ -5065,61 +5207,67 @@
         <v>112</v>
       </c>
       <c r="Q22" s="35" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="R22" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S22" s="21" t="str">
+        <v>305</v>
+      </c>
+      <c r="S22" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T22" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T22" s="21" t="str">
+      <c r="U22" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U22" s="21" t="str">
+      <c r="V22" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="V22" s="21" t="s">
+      <c r="W22" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W22" s="58" t="str">
+      <c r="X22" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-22</v>
       </c>
-      <c r="X22" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y22" s="60" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z22" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="AA22" s="21" t="s">
-        <v>306</v>
+        <v>214</v>
+      </c>
+      <c r="Z22" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA22" s="60" t="s">
+        <v>260</v>
+      </c>
+      <c r="AB22" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC22" s="21" t="s">
+        <v>277</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="50">
         <v>23</v>
       </c>
       <c r="B23" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C23" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C23" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D23" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="E23" s="55" t="s">
         <v>239</v>
       </c>
-      <c r="E23" s="55" t="s">
-        <v>240</v>
-      </c>
       <c r="F23" s="56" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>9</v>
@@ -5156,61 +5304,67 @@
         <v>113</v>
       </c>
       <c r="Q23" s="35" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="R23" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S23" s="21" t="str">
+        <v>306</v>
+      </c>
+      <c r="S23" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T23" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T23" s="21" t="str">
+      <c r="U23" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U23" s="21" t="str">
+      <c r="V23" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="V23" s="21" t="s">
+      <c r="W23" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W23" s="58" t="str">
+      <c r="X23" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-23</v>
       </c>
-      <c r="X23" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y23" s="60" t="s">
-        <v>260</v>
-      </c>
-      <c r="Z23" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="AA23" s="21" t="s">
-        <v>307</v>
+        <v>214</v>
+      </c>
+      <c r="Z23" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA23" s="60" t="s">
+        <v>259</v>
+      </c>
+      <c r="AB23" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC23" s="21" t="s">
+        <v>277</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="50">
         <v>24</v>
       </c>
       <c r="B24" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C24" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C24" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D24" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="E24" s="55" t="s">
         <v>239</v>
       </c>
-      <c r="E24" s="55" t="s">
-        <v>240</v>
-      </c>
       <c r="F24" s="56" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>9</v>
@@ -5247,61 +5401,67 @@
         <v>114</v>
       </c>
       <c r="Q24" s="35" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="R24" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S24" s="21" t="str">
+        <v>307</v>
+      </c>
+      <c r="S24" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T24" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T24" s="21" t="str">
+      <c r="U24" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U24" s="21" t="str">
+      <c r="V24" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="V24" s="21" t="s">
+      <c r="W24" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W24" s="58" t="str">
+      <c r="X24" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-24</v>
       </c>
-      <c r="X24" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y24" s="60" t="s">
-        <v>259</v>
-      </c>
-      <c r="Z24" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="AA24" s="21" t="s">
-        <v>308</v>
+        <v>214</v>
+      </c>
+      <c r="Z24" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA24" s="60" t="s">
+        <v>258</v>
+      </c>
+      <c r="AB24" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC24" s="21" t="s">
+        <v>277</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="50">
         <v>25</v>
       </c>
       <c r="B25" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C25" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C25" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D25" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="E25" s="55" t="s">
         <v>239</v>
       </c>
-      <c r="E25" s="55" t="s">
-        <v>240</v>
-      </c>
       <c r="F25" s="56" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>9</v>
@@ -5338,61 +5498,67 @@
         <v>115</v>
       </c>
       <c r="Q25" s="35" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="R25" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S25" s="21" t="str">
+        <v>308</v>
+      </c>
+      <c r="S25" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T25" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T25" s="21" t="str">
+      <c r="U25" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U25" s="21" t="str">
+      <c r="V25" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="V25" s="21" t="s">
+      <c r="W25" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W25" s="58" t="str">
+      <c r="X25" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-25</v>
       </c>
-      <c r="X25" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y25" s="60" t="s">
-        <v>258</v>
-      </c>
-      <c r="Z25" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="AA25" s="21" t="s">
-        <v>309</v>
+        <v>214</v>
+      </c>
+      <c r="Z25" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA25" s="60" t="s">
+        <v>257</v>
+      </c>
+      <c r="AB25" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC25" s="21" t="s">
+        <v>277</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="50">
         <v>26</v>
       </c>
       <c r="B26" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C26" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C26" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D26" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="E26" s="55" t="s">
         <v>239</v>
       </c>
-      <c r="E26" s="55" t="s">
-        <v>240</v>
-      </c>
       <c r="F26" s="56" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>9</v>
@@ -5429,61 +5595,67 @@
         <v>116</v>
       </c>
       <c r="Q26" s="35" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="R26" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S26" s="21" t="str">
+        <v>309</v>
+      </c>
+      <c r="S26" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T26" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T26" s="21" t="str">
+      <c r="U26" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U26" s="21" t="str">
+      <c r="V26" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="V26" s="21" t="s">
+      <c r="W26" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W26" s="58" t="str">
+      <c r="X26" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-26</v>
       </c>
-      <c r="X26" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y26" s="60" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z26" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="AA26" s="21" t="s">
-        <v>310</v>
+        <v>214</v>
+      </c>
+      <c r="Z26" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA26" s="60" t="s">
+        <v>256</v>
+      </c>
+      <c r="AB26" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC26" s="21" t="s">
+        <v>277</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="50">
         <v>27</v>
       </c>
       <c r="B27" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C27" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C27" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D27" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="E27" s="55" t="s">
         <v>239</v>
       </c>
-      <c r="E27" s="55" t="s">
-        <v>240</v>
-      </c>
       <c r="F27" s="56" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>9</v>
@@ -5520,61 +5692,67 @@
         <v>117</v>
       </c>
       <c r="Q27" s="35" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="R27" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S27" s="21" t="str">
+        <v>310</v>
+      </c>
+      <c r="S27" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T27" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T27" s="21" t="str">
+      <c r="U27" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="U27" s="21" t="str">
+      <c r="V27" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="V27" s="21" t="s">
+      <c r="W27" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W27" s="58" t="str">
+      <c r="X27" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-27</v>
       </c>
-      <c r="X27" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y27" s="60" t="s">
-        <v>256</v>
-      </c>
-      <c r="Z27" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="AA27" s="21" t="s">
-        <v>311</v>
+        <v>214</v>
+      </c>
+      <c r="Z27" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA27" s="60" t="s">
+        <v>255</v>
+      </c>
+      <c r="AB27" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC27" s="21" t="s">
+        <v>277</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="50">
         <v>28</v>
       </c>
       <c r="B28" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C28" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C28" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D28" s="55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F28" s="44" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>9</v>
@@ -5608,64 +5786,70 @@
         <v>Ponto Interno</v>
       </c>
       <c r="P28" s="35" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q28" s="35" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="R28" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S28" s="21" t="str">
+        <v>311</v>
+      </c>
+      <c r="S28" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T28" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T28" s="21" t="str">
+      <c r="U28" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="U28" s="21" t="str">
+      <c r="V28" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Pontos.do.Modelo</v>
       </c>
-      <c r="V28" s="21" t="s">
+      <c r="W28" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W28" s="58" t="str">
+      <c r="X28" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-28</v>
       </c>
-      <c r="X28" s="21" t="s">
-        <v>175</v>
-      </c>
       <c r="Y28" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="Z28" s="21" t="s">
-        <v>143</v>
+        <v>174</v>
+      </c>
+      <c r="Z28" s="60" t="s">
+        <v>214</v>
       </c>
       <c r="AA28" s="21" t="s">
-        <v>312</v>
+        <v>171</v>
+      </c>
+      <c r="AB28" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC28" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="50">
         <v>29</v>
       </c>
       <c r="B29" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C29" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C29" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D29" s="55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F29" s="44" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>9</v>
@@ -5699,64 +5883,70 @@
         <v>Ponto Perimetral</v>
       </c>
       <c r="P29" s="35" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q29" s="35" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="R29" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S29" s="21" t="str">
+        <v>312</v>
+      </c>
+      <c r="S29" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T29" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T29" s="21" t="str">
+      <c r="U29" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="U29" s="21" t="str">
+      <c r="V29" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Pontos.do.Modelo</v>
       </c>
-      <c r="V29" s="21" t="s">
+      <c r="W29" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W29" s="58" t="str">
+      <c r="X29" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-29</v>
       </c>
-      <c r="X29" s="21" t="s">
-        <v>179</v>
-      </c>
       <c r="Y29" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="Z29" s="21" t="s">
-        <v>143</v>
+        <v>178</v>
+      </c>
+      <c r="Z29" s="60" t="s">
+        <v>214</v>
       </c>
       <c r="AA29" s="21" t="s">
-        <v>313</v>
+        <v>171</v>
+      </c>
+      <c r="AB29" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC29" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="50">
         <v>30</v>
       </c>
       <c r="B30" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C30" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C30" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D30" s="55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F30" s="44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>9</v>
@@ -5796,58 +5986,64 @@
         <v>139</v>
       </c>
       <c r="R30" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S30" s="21" t="str">
+        <v>313</v>
+      </c>
+      <c r="S30" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T30" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T30" s="21" t="str">
+      <c r="U30" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="U30" s="21" t="str">
+      <c r="V30" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Pontos.do.Modelo</v>
       </c>
-      <c r="V30" s="21" t="s">
+      <c r="W30" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W30" s="58" t="str">
+      <c r="X30" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-30</v>
       </c>
-      <c r="X30" s="21" t="s">
-        <v>206</v>
-      </c>
       <c r="Y30" s="21" t="s">
-        <v>376</v>
-      </c>
-      <c r="Z30" s="21" t="s">
-        <v>143</v>
+        <v>205</v>
+      </c>
+      <c r="Z30" s="60" t="s">
+        <v>214</v>
       </c>
       <c r="AA30" s="21" t="s">
-        <v>314</v>
+        <v>375</v>
+      </c>
+      <c r="AB30" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC30" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="50">
         <v>31</v>
       </c>
       <c r="B31" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C31" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C31" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D31" s="55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F31" s="44" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>9</v>
@@ -5884,61 +6080,67 @@
         <v>140</v>
       </c>
       <c r="Q31" s="35" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="R31" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S31" s="21" t="str">
+        <v>314</v>
+      </c>
+      <c r="S31" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T31" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T31" s="21" t="str">
+      <c r="U31" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="U31" s="21" t="str">
+      <c r="V31" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Pontos.do.Modelo</v>
       </c>
-      <c r="V31" s="21" t="s">
+      <c r="W31" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W31" s="58" t="str">
+      <c r="X31" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-31</v>
       </c>
-      <c r="X31" s="21" t="s">
-        <v>207</v>
-      </c>
       <c r="Y31" s="21" t="s">
-        <v>376</v>
-      </c>
-      <c r="Z31" s="21" t="s">
-        <v>143</v>
+        <v>206</v>
+      </c>
+      <c r="Z31" s="60" t="s">
+        <v>214</v>
       </c>
       <c r="AA31" s="21" t="s">
-        <v>315</v>
+        <v>375</v>
+      </c>
+      <c r="AB31" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC31" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="50">
         <v>32</v>
       </c>
       <c r="B32" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C32" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C32" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D32" s="55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E32" s="55" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F32" s="44" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>9</v>
@@ -5978,58 +6180,64 @@
         <v>96</v>
       </c>
       <c r="R32" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S32" s="21" t="str">
+        <v>315</v>
+      </c>
+      <c r="S32" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T32" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T32" s="21" t="str">
+      <c r="U32" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="U32" s="21" t="str">
+      <c r="V32" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Sondagens</v>
       </c>
-      <c r="V32" s="21" t="s">
+      <c r="W32" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W32" s="58" t="str">
+      <c r="X32" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-32</v>
       </c>
-      <c r="X32" s="21" t="s">
-        <v>215</v>
-      </c>
-      <c r="Y32" s="60" t="s">
-        <v>213</v>
-      </c>
-      <c r="Z32" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="AA32" s="21" t="s">
-        <v>316</v>
+      <c r="Y32" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="Z32" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA32" s="60" t="s">
+        <v>212</v>
+      </c>
+      <c r="AB32" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC32" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="50">
         <v>33</v>
       </c>
       <c r="B33" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C33" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C33" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D33" s="55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E33" s="55" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F33" s="44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>9</v>
@@ -6069,58 +6277,64 @@
         <v>121</v>
       </c>
       <c r="R33" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S33" s="21" t="str">
+        <v>316</v>
+      </c>
+      <c r="S33" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T33" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T33" s="21" t="str">
+      <c r="U33" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="U33" s="21" t="str">
+      <c r="V33" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Sondagens</v>
       </c>
-      <c r="V33" s="21" t="s">
+      <c r="W33" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W33" s="58" t="str">
+      <c r="X33" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-33</v>
       </c>
-      <c r="X33" s="21" t="s">
-        <v>215</v>
-      </c>
-      <c r="Y33" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z33" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="AA33" s="21" t="s">
-        <v>317</v>
+      <c r="Y33" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="Z33" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA33" s="60" t="s">
+        <v>213</v>
+      </c>
+      <c r="AB33" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC33" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="50">
         <v>34</v>
       </c>
       <c r="B34" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C34" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C34" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D34" s="55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E34" s="44" t="s">
         <v>94</v>
       </c>
       <c r="F34" s="44" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>9</v>
@@ -6154,64 +6368,70 @@
         <v>Topografia Sólida</v>
       </c>
       <c r="P34" s="35" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q34" s="35" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="R34" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S34" s="21" t="str">
+        <v>317</v>
+      </c>
+      <c r="S34" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T34" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T34" s="21" t="str">
+      <c r="U34" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="U34" s="21" t="str">
+      <c r="V34" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Topografia</v>
       </c>
-      <c r="V34" s="21" t="s">
+      <c r="W34" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W34" s="58" t="str">
+      <c r="X34" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-34</v>
       </c>
-      <c r="X34" s="21" t="s">
-        <v>176</v>
-      </c>
       <c r="Y34" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="Z34" s="21" t="s">
-        <v>143</v>
+        <v>175</v>
+      </c>
+      <c r="Z34" s="60" t="s">
+        <v>214</v>
       </c>
       <c r="AA34" s="21" t="s">
-        <v>318</v>
+        <v>172</v>
+      </c>
+      <c r="AB34" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC34" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="50">
         <v>35</v>
       </c>
       <c r="B35" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C35" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C35" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D35" s="55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E35" s="44" t="s">
         <v>94</v>
       </c>
       <c r="F35" s="44" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>9</v>
@@ -6245,64 +6465,70 @@
         <v>Topografia Malha</v>
       </c>
       <c r="P35" s="35" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q35" s="35" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="R35" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S35" s="21" t="str">
+        <v>318</v>
+      </c>
+      <c r="S35" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T35" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T35" s="21" t="str">
+      <c r="U35" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="U35" s="21" t="str">
+      <c r="V35" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Topografia</v>
       </c>
-      <c r="V35" s="21" t="s">
+      <c r="W35" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W35" s="58" t="str">
+      <c r="X35" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-35</v>
       </c>
-      <c r="X35" s="21" t="s">
-        <v>178</v>
-      </c>
       <c r="Y35" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="Z35" s="21" t="s">
-        <v>143</v>
+        <v>177</v>
+      </c>
+      <c r="Z35" s="60" t="s">
+        <v>214</v>
       </c>
       <c r="AA35" s="21" t="s">
-        <v>319</v>
+        <v>172</v>
+      </c>
+      <c r="AB35" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC35" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="50">
         <v>36</v>
       </c>
       <c r="B36" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C36" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C36" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D36" s="55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E36" s="44" t="s">
         <v>94</v>
       </c>
       <c r="F36" s="44" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>9</v>
@@ -6336,64 +6562,70 @@
         <v>Topografia Sólida Núcleo</v>
       </c>
       <c r="P36" s="35" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q36" s="35" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="R36" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S36" s="21" t="str">
+        <v>319</v>
+      </c>
+      <c r="S36" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T36" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T36" s="21" t="str">
+      <c r="U36" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="U36" s="21" t="str">
+      <c r="V36" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Topografia</v>
       </c>
-      <c r="V36" s="21" t="s">
+      <c r="W36" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W36" s="58" t="str">
+      <c r="X36" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-36</v>
       </c>
-      <c r="X36" s="21" t="s">
-        <v>147</v>
-      </c>
       <c r="Y36" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="Z36" s="21" t="s">
-        <v>143</v>
+        <v>146</v>
+      </c>
+      <c r="Z36" s="60" t="s">
+        <v>214</v>
       </c>
       <c r="AA36" s="21" t="s">
-        <v>320</v>
+        <v>189</v>
+      </c>
+      <c r="AB36" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC36" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="50">
         <v>37</v>
       </c>
       <c r="B37" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C37" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C37" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D37" s="55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E37" s="44" t="s">
         <v>94</v>
       </c>
       <c r="F37" s="44" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>9</v>
@@ -6427,64 +6659,70 @@
         <v>Topografia Sólida Substrato</v>
       </c>
       <c r="P37" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q37" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="Q37" s="35" t="s">
-        <v>157</v>
-      </c>
       <c r="R37" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S37" s="21" t="str">
+        <v>320</v>
+      </c>
+      <c r="S37" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T37" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T37" s="21" t="str">
+      <c r="U37" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="U37" s="21" t="str">
+      <c r="V37" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Topografia</v>
       </c>
-      <c r="V37" s="21" t="s">
+      <c r="W37" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W37" s="58" t="str">
+      <c r="X37" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-37</v>
       </c>
-      <c r="X37" s="21" t="s">
-        <v>180</v>
-      </c>
       <c r="Y37" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="Z37" s="21" t="s">
-        <v>143</v>
+        <v>179</v>
+      </c>
+      <c r="Z37" s="60" t="s">
+        <v>214</v>
       </c>
       <c r="AA37" s="21" t="s">
-        <v>321</v>
+        <v>189</v>
+      </c>
+      <c r="AB37" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC37" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="50">
         <v>38</v>
       </c>
       <c r="B38" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C38" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C38" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D38" s="55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E38" s="44" t="s">
         <v>94</v>
       </c>
       <c r="F38" s="44" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>9</v>
@@ -6518,64 +6756,70 @@
         <v>Topografia Sólida Membrana</v>
       </c>
       <c r="P38" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q38" s="35" t="s">
         <v>158</v>
       </c>
-      <c r="Q38" s="35" t="s">
-        <v>159</v>
-      </c>
       <c r="R38" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S38" s="21" t="str">
+        <v>321</v>
+      </c>
+      <c r="S38" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T38" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T38" s="21" t="str">
+      <c r="U38" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="U38" s="21" t="str">
+      <c r="V38" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Topografia</v>
       </c>
-      <c r="V38" s="21" t="s">
+      <c r="W38" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W38" s="58" t="str">
+      <c r="X38" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-38</v>
       </c>
-      <c r="X38" s="21" t="s">
-        <v>177</v>
-      </c>
       <c r="Y38" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="Z38" s="21" t="s">
-        <v>143</v>
+        <v>176</v>
+      </c>
+      <c r="Z38" s="60" t="s">
+        <v>214</v>
       </c>
       <c r="AA38" s="21" t="s">
-        <v>322</v>
+        <v>189</v>
+      </c>
+      <c r="AB38" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC38" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="50">
         <v>39</v>
       </c>
       <c r="B39" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C39" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C39" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D39" s="55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E39" s="44" t="s">
         <v>94</v>
       </c>
       <c r="F39" s="44" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>9</v>
@@ -6609,64 +6853,70 @@
         <v>Topografia Sólida Isolamento</v>
       </c>
       <c r="P39" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q39" s="35" t="s">
         <v>160</v>
       </c>
-      <c r="Q39" s="35" t="s">
-        <v>161</v>
-      </c>
       <c r="R39" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S39" s="21" t="str">
+        <v>322</v>
+      </c>
+      <c r="S39" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T39" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T39" s="21" t="str">
+      <c r="U39" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="U39" s="21" t="str">
+      <c r="V39" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Topografia</v>
       </c>
-      <c r="V39" s="21" t="s">
+      <c r="W39" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W39" s="58" t="str">
+      <c r="X39" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-39</v>
       </c>
-      <c r="X39" s="21" t="s">
-        <v>181</v>
-      </c>
       <c r="Y39" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="Z39" s="21" t="s">
-        <v>143</v>
+        <v>180</v>
+      </c>
+      <c r="Z39" s="60" t="s">
+        <v>214</v>
       </c>
       <c r="AA39" s="21" t="s">
-        <v>323</v>
+        <v>189</v>
+      </c>
+      <c r="AB39" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC39" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="50">
         <v>40</v>
       </c>
       <c r="B40" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C40" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C40" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D40" s="55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E40" s="44" t="s">
         <v>94</v>
       </c>
       <c r="F40" s="44" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>9</v>
@@ -6700,64 +6950,70 @@
         <v>Topografia Sólida Superfície</v>
       </c>
       <c r="P40" s="35" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q40" s="35" t="s">
         <v>162</v>
       </c>
-      <c r="Q40" s="35" t="s">
-        <v>163</v>
-      </c>
       <c r="R40" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S40" s="21" t="str">
+        <v>323</v>
+      </c>
+      <c r="S40" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T40" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T40" s="21" t="str">
+      <c r="U40" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="U40" s="21" t="str">
+      <c r="V40" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Topografia</v>
       </c>
-      <c r="V40" s="21" t="s">
+      <c r="W40" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W40" s="58" t="str">
+      <c r="X40" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-40</v>
       </c>
-      <c r="X40" s="21" t="s">
-        <v>377</v>
-      </c>
       <c r="Y40" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="Z40" s="21" t="s">
-        <v>143</v>
+        <v>376</v>
+      </c>
+      <c r="Z40" s="60" t="s">
+        <v>214</v>
       </c>
       <c r="AA40" s="21" t="s">
-        <v>324</v>
+        <v>189</v>
+      </c>
+      <c r="AB40" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC40" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="50">
         <v>41</v>
       </c>
       <c r="B41" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C41" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C41" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D41" s="55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E41" s="44" t="s">
         <v>94</v>
       </c>
       <c r="F41" s="44" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>9</v>
@@ -6791,64 +7047,70 @@
         <v>Topografia Sólida Agua</v>
       </c>
       <c r="P41" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q41" s="35" t="s">
         <v>191</v>
       </c>
-      <c r="Q41" s="35" t="s">
-        <v>192</v>
-      </c>
       <c r="R41" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S41" s="21" t="str">
+        <v>324</v>
+      </c>
+      <c r="S41" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T41" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T41" s="21" t="str">
+      <c r="U41" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="U41" s="21" t="str">
+      <c r="V41" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Topografia</v>
       </c>
-      <c r="V41" s="21" t="s">
+      <c r="W41" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W41" s="58" t="str">
+      <c r="X41" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-41</v>
       </c>
-      <c r="X41" s="21" t="s">
-        <v>377</v>
-      </c>
       <c r="Y41" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="Z41" s="21" t="s">
-        <v>143</v>
+        <v>376</v>
+      </c>
+      <c r="Z41" s="60" t="s">
+        <v>214</v>
       </c>
       <c r="AA41" s="21" t="s">
-        <v>325</v>
+        <v>192</v>
+      </c>
+      <c r="AB41" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC41" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="50">
         <v>42</v>
       </c>
       <c r="B42" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C42" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C42" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D42" s="55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E42" s="44" t="s">
         <v>94</v>
       </c>
       <c r="F42" s="44" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>9</v>
@@ -6885,61 +7147,67 @@
         <v>126</v>
       </c>
       <c r="Q42" s="35" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="R42" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S42" s="21" t="str">
+        <v>325</v>
+      </c>
+      <c r="S42" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T42" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T42" s="21" t="str">
+      <c r="U42" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="U42" s="21" t="str">
+      <c r="V42" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Topografia</v>
       </c>
-      <c r="V42" s="21" t="s">
+      <c r="W42" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W42" s="58" t="str">
+      <c r="X42" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-42</v>
       </c>
-      <c r="X42" s="60" t="s">
-        <v>148</v>
-      </c>
       <c r="Y42" s="60" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z42" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="AA42" s="21" t="s">
-        <v>326</v>
+        <v>147</v>
+      </c>
+      <c r="Z42" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA42" s="60" t="s">
+        <v>193</v>
+      </c>
+      <c r="AB42" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC42" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="50">
         <v>43</v>
       </c>
       <c r="B43" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C43" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C43" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D43" s="55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E43" s="44" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F43" s="44" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>9</v>
@@ -6973,64 +7241,70 @@
         <v>Curva de 10</v>
       </c>
       <c r="P43" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q43" s="35" t="s">
         <v>165</v>
       </c>
-      <c r="Q43" s="35" t="s">
-        <v>166</v>
-      </c>
       <c r="R43" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S43" s="21" t="str">
+        <v>326</v>
+      </c>
+      <c r="S43" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T43" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T43" s="21" t="str">
+      <c r="U43" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.Altimétricos</v>
       </c>
-      <c r="U43" s="21" t="str">
+      <c r="V43" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Curvas.de.Nível</v>
       </c>
-      <c r="V43" s="21" t="s">
+      <c r="W43" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W43" s="58" t="str">
+      <c r="X43" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-43</v>
       </c>
-      <c r="X43" s="21" t="s">
-        <v>378</v>
-      </c>
       <c r="Y43" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="Z43" s="21" t="s">
-        <v>143</v>
+        <v>377</v>
+      </c>
+      <c r="Z43" s="60" t="s">
+        <v>214</v>
       </c>
       <c r="AA43" s="21" t="s">
-        <v>327</v>
+        <v>173</v>
+      </c>
+      <c r="AB43" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC43" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="50">
         <v>44</v>
       </c>
       <c r="B44" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C44" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C44" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D44" s="55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E44" s="44" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F44" s="44" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>9</v>
@@ -7064,64 +7338,70 @@
         <v>Curva de 05</v>
       </c>
       <c r="P44" s="35" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q44" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="Q44" s="35" t="s">
-        <v>168</v>
-      </c>
       <c r="R44" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S44" s="21" t="str">
+        <v>327</v>
+      </c>
+      <c r="S44" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T44" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T44" s="21" t="str">
+      <c r="U44" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.Altimétricos</v>
       </c>
-      <c r="U44" s="21" t="str">
+      <c r="V44" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Curvas.de.Nível</v>
       </c>
-      <c r="V44" s="21" t="s">
+      <c r="W44" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W44" s="58" t="str">
+      <c r="X44" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-44</v>
       </c>
-      <c r="X44" s="21" t="s">
-        <v>378</v>
-      </c>
       <c r="Y44" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="Z44" s="21" t="s">
-        <v>143</v>
+        <v>377</v>
+      </c>
+      <c r="Z44" s="60" t="s">
+        <v>214</v>
       </c>
       <c r="AA44" s="21" t="s">
-        <v>328</v>
+        <v>173</v>
+      </c>
+      <c r="AB44" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC44" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="50">
         <v>45</v>
       </c>
       <c r="B45" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C45" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C45" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D45" s="55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F45" s="44" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>9</v>
@@ -7155,64 +7435,70 @@
         <v>Curva de 01</v>
       </c>
       <c r="P45" s="35" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q45" s="35" t="s">
         <v>169</v>
       </c>
-      <c r="Q45" s="35" t="s">
-        <v>170</v>
-      </c>
       <c r="R45" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S45" s="21" t="str">
+        <v>328</v>
+      </c>
+      <c r="S45" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T45" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T45" s="21" t="str">
+      <c r="U45" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.Altimétricos</v>
       </c>
-      <c r="U45" s="21" t="str">
+      <c r="V45" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Curvas.de.Nível</v>
       </c>
-      <c r="V45" s="21" t="s">
+      <c r="W45" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W45" s="58" t="str">
+      <c r="X45" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-45</v>
       </c>
-      <c r="X45" s="21" t="s">
-        <v>379</v>
-      </c>
       <c r="Y45" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="Z45" s="21" t="s">
-        <v>143</v>
+        <v>378</v>
+      </c>
+      <c r="Z45" s="60" t="s">
+        <v>214</v>
       </c>
       <c r="AA45" s="21" t="s">
-        <v>329</v>
+        <v>173</v>
+      </c>
+      <c r="AB45" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC45" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="50">
         <v>46</v>
       </c>
       <c r="B46" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C46" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C46" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D46" s="55" t="s">
+        <v>272</v>
+      </c>
+      <c r="E46" s="55" t="s">
         <v>273</v>
       </c>
-      <c r="E46" s="55" t="s">
-        <v>274</v>
-      </c>
       <c r="F46" s="55" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>9</v>
@@ -7249,61 +7535,67 @@
         <v>135</v>
       </c>
       <c r="Q46" s="35" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="R46" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S46" s="21" t="str">
+        <v>136</v>
+      </c>
+      <c r="S46" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T46" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T46" s="21" t="str">
+      <c r="U46" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Loteamentos</v>
       </c>
-      <c r="U46" s="21" t="str">
+      <c r="V46" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Loteamento</v>
       </c>
-      <c r="V46" s="21" t="s">
+      <c r="W46" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W46" s="58" t="str">
+      <c r="X46" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-46</v>
       </c>
-      <c r="X46" s="21" t="s">
-        <v>205</v>
-      </c>
       <c r="Y46" s="21" t="s">
-        <v>376</v>
-      </c>
-      <c r="Z46" s="21" t="s">
-        <v>143</v>
+        <v>204</v>
+      </c>
+      <c r="Z46" s="60" t="s">
+        <v>214</v>
       </c>
       <c r="AA46" s="21" t="s">
-        <v>136</v>
+        <v>375</v>
+      </c>
+      <c r="AB46" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC46" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="50">
         <v>47</v>
       </c>
       <c r="B47" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C47" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C47" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D47" s="55" t="s">
+        <v>272</v>
+      </c>
+      <c r="E47" s="55" t="s">
         <v>273</v>
       </c>
-      <c r="E47" s="55" t="s">
-        <v>274</v>
-      </c>
       <c r="F47" s="55" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>9</v>
@@ -7340,61 +7632,67 @@
         <v>137</v>
       </c>
       <c r="Q47" s="35" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="R47" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S47" s="21" t="str">
+        <v>329</v>
+      </c>
+      <c r="S47" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T47" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T47" s="21" t="str">
+      <c r="U47" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.de.Loteamentos</v>
       </c>
-      <c r="U47" s="21" t="str">
+      <c r="V47" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Loteamento</v>
       </c>
-      <c r="V47" s="21" t="s">
+      <c r="W47" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W47" s="58" t="str">
+      <c r="X47" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-47</v>
       </c>
-      <c r="X47" s="43" t="s">
-        <v>208</v>
-      </c>
-      <c r="Y47" s="21" t="s">
-        <v>376</v>
-      </c>
-      <c r="Z47" s="21" t="s">
-        <v>143</v>
+      <c r="Y47" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="Z47" s="60" t="s">
+        <v>214</v>
       </c>
       <c r="AA47" s="21" t="s">
-        <v>330</v>
+        <v>375</v>
+      </c>
+      <c r="AB47" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC47" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="50">
         <v>48</v>
       </c>
       <c r="B48" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C48" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C48" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D48" s="55" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E48" s="55" t="s">
         <v>118</v>
       </c>
       <c r="F48" s="56" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>9</v>
@@ -7431,61 +7729,67 @@
         <v>119</v>
       </c>
       <c r="Q48" s="35" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="R48" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S48" s="21" t="str">
+        <v>330</v>
+      </c>
+      <c r="S48" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T48" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T48" s="21" t="str">
+      <c r="U48" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.Paisagísticos</v>
       </c>
-      <c r="U48" s="21" t="str">
+      <c r="V48" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Paisagismo</v>
       </c>
-      <c r="V48" s="21" t="s">
+      <c r="W48" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W48" s="58" t="str">
+      <c r="X48" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-48</v>
       </c>
-      <c r="X48" s="60" t="s">
-        <v>144</v>
-      </c>
       <c r="Y48" s="60" t="s">
-        <v>172</v>
-      </c>
-      <c r="Z48" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="AA48" s="21" t="s">
-        <v>331</v>
+        <v>143</v>
+      </c>
+      <c r="Z48" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA48" s="60" t="s">
+        <v>171</v>
+      </c>
+      <c r="AB48" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC48" s="21" t="s">
+        <v>279</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="50">
         <v>49</v>
       </c>
       <c r="B49" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C49" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C49" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D49" s="55" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E49" s="55" t="s">
         <v>118</v>
       </c>
       <c r="F49" s="56" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>9</v>
@@ -7525,52 +7829,58 @@
         <v>123</v>
       </c>
       <c r="R49" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S49" s="21" t="str">
+        <v>331</v>
+      </c>
+      <c r="S49" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T49" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T49" s="21" t="str">
+      <c r="U49" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.Paisagísticos</v>
       </c>
-      <c r="U49" s="21" t="str">
+      <c r="V49" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Paisagismo</v>
       </c>
-      <c r="V49" s="21" t="s">
+      <c r="W49" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W49" s="58" t="str">
+      <c r="X49" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-49</v>
       </c>
-      <c r="X49" s="60" t="s">
-        <v>215</v>
-      </c>
       <c r="Y49" s="60" t="s">
-        <v>188</v>
-      </c>
-      <c r="Z49" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="AA49" s="21" t="s">
-        <v>332</v>
+        <v>214</v>
+      </c>
+      <c r="Z49" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA49" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="AB49" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC49" s="21" t="s">
+        <v>279</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="50">
         <v>50</v>
       </c>
       <c r="B50" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C50" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C50" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D50" s="55" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E50" s="55" t="s">
         <v>118</v>
@@ -7613,61 +7923,67 @@
         <v>134</v>
       </c>
       <c r="Q50" s="35" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="R50" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S50" s="21" t="str">
+        <v>332</v>
+      </c>
+      <c r="S50" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T50" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T50" s="21" t="str">
+      <c r="U50" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.Paisagísticos</v>
       </c>
-      <c r="U50" s="21" t="str">
+      <c r="V50" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Paisagismo</v>
       </c>
-      <c r="V50" s="21" t="s">
+      <c r="W50" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W50" s="58" t="str">
+      <c r="X50" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-50</v>
       </c>
-      <c r="X50" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="Y50" s="60" t="s">
-        <v>276</v>
-      </c>
-      <c r="Z50" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="AA50" s="21" t="s">
-        <v>333</v>
+      <c r="Y50" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="Z50" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA50" s="60" t="s">
+        <v>275</v>
+      </c>
+      <c r="AB50" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC50" s="21" t="s">
+        <v>279</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="50">
         <v>51</v>
       </c>
       <c r="B51" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C51" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C51" s="59" t="s">
-        <v>375</v>
-      </c>
       <c r="D51" s="55" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E51" s="55" t="s">
         <v>118</v>
       </c>
       <c r="F51" s="56" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>9</v>
@@ -7704,158 +8020,169 @@
         <v>124</v>
       </c>
       <c r="Q51" s="35" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="R51" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="S51" s="21" t="str">
+        <v>125</v>
+      </c>
+      <c r="S51" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T51" s="21" t="str">
         <f t="shared" si="10"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="T51" s="21" t="str">
+      <c r="U51" s="21" t="str">
         <f t="shared" si="11"/>
         <v>Elementos.Paisagísticos</v>
       </c>
-      <c r="U51" s="21" t="str">
+      <c r="V51" s="21" t="str">
         <f t="shared" si="12"/>
         <v>Paisagismo</v>
       </c>
-      <c r="V51" s="21" t="s">
+      <c r="W51" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="W51" s="58" t="str">
+      <c r="X51" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-51</v>
       </c>
-      <c r="X51" s="60" t="s">
-        <v>145</v>
-      </c>
       <c r="Y51" s="60" t="s">
-        <v>189</v>
-      </c>
-      <c r="Z51" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="AA51" s="21" t="s">
-        <v>125</v>
+        <v>144</v>
+      </c>
+      <c r="Z51" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA51" s="60" t="s">
+        <v>188</v>
+      </c>
+      <c r="AB51" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC51" s="21" t="s">
+        <v>278</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA804">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC804">
     <sortCondition ref="E1:E804"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B51 AA2:AA51">
-    <cfRule type="cellIs" dxfId="62" priority="6" operator="equal">
+  <conditionalFormatting sqref="A2:B51 AB52:XFD1048576 AB1:XFD1">
+    <cfRule type="cellIs" dxfId="63" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A52:W1048576 A1:W1 C2:E2 P2 AB2:XFD2 D3:E8 C3:C51 D9:D27 Z52:XFD1048576">
-    <cfRule type="cellIs" dxfId="61" priority="252" operator="equal">
+  <conditionalFormatting sqref="A1:Q1 C2:E2 P2 AD2:XFD2 D3:E8 C3:C51 D9:D27 S1:X1 A52:X1048576">
+    <cfRule type="cellIs" dxfId="62" priority="254" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="60" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F27">
-    <cfRule type="cellIs" dxfId="59" priority="58" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="60" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="58" priority="1040"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="1042"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F28:F45 Q2:Q51 P28:P29 AB28:XFD29 P34:P41 AB34:XFD41 P43:P45 AB43:XFD45">
-    <cfRule type="cellIs" dxfId="57" priority="119" operator="equal">
+  <conditionalFormatting sqref="F28:F45 Q2:Q51 P28:P29 AD28:XFD29 P34:P41 AD34:XFD41 P43:P45 AD43:XFD45">
+    <cfRule type="cellIs" dxfId="58" priority="121" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28:F45">
-    <cfRule type="duplicateValues" dxfId="56" priority="1019"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="1022"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="1021"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="1021"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="1023"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="1024"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F46:F47">
-    <cfRule type="duplicateValues" dxfId="53" priority="989"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="991"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F51">
-    <cfRule type="duplicateValues" dxfId="52" priority="1025"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="1027"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="51" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="255"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52:F1048576">
-    <cfRule type="duplicateValues" dxfId="50" priority="782"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="769"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="762"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="754"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="245"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="247"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="756"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="764"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="771"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="784"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W52:W1048576 W1">
-    <cfRule type="duplicateValues" dxfId="45" priority="581"/>
+  <conditionalFormatting sqref="X52:X1048576 X1">
+    <cfRule type="duplicateValues" dxfId="46" priority="583"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X50">
-    <cfRule type="duplicateValues" dxfId="44" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="51"/>
+  <conditionalFormatting sqref="Y50">
+    <cfRule type="duplicateValues" dxfId="45" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="53"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y2">
-    <cfRule type="duplicateValues" dxfId="40" priority="83"/>
-    <cfRule type="cellIs" dxfId="39" priority="82" operator="equal">
+  <conditionalFormatting sqref="AA2">
+    <cfRule type="cellIs" dxfId="41" priority="84" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="40" priority="85"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA3">
+    <cfRule type="duplicateValues" dxfId="39" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="83"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA3:AA8 AA17:AA27 AA10:AA14">
+    <cfRule type="duplicateValues" dxfId="35" priority="1039"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA4:AA8 AA19:AA27 AA10:AA14">
+    <cfRule type="duplicateValues" dxfId="34" priority="1036"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA4:AA8 AA19:AA27">
+    <cfRule type="duplicateValues" dxfId="33" priority="87"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA9">
+    <cfRule type="duplicateValues" dxfId="32" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA10:AA14">
+    <cfRule type="duplicateValues" dxfId="27" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA15:AA16">
+    <cfRule type="duplicateValues" dxfId="23" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA17:AA18">
+    <cfRule type="duplicateValues" dxfId="15" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA19:AA27">
+    <cfRule type="duplicateValues" dxfId="10" priority="86"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R51">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y3">
-    <cfRule type="duplicateValues" dxfId="38" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="81"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y3:Y8 Y17:Y27 Y10:Y14">
-    <cfRule type="duplicateValues" dxfId="34" priority="1037"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y4:Y8 Y19:Y27 Y10:Y14">
-    <cfRule type="duplicateValues" dxfId="33" priority="1034"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y4:Y8 Y19:Y27">
-    <cfRule type="duplicateValues" dxfId="32" priority="85"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y9">
-    <cfRule type="duplicateValues" dxfId="31" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y10:Y14">
-    <cfRule type="duplicateValues" dxfId="26" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y15:Y16">
-    <cfRule type="duplicateValues" dxfId="22" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y17:Y18">
-    <cfRule type="duplicateValues" dxfId="14" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y19:Y27">
-    <cfRule type="duplicateValues" dxfId="9" priority="84"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z1:XFD1">
-    <cfRule type="cellIs" dxfId="8" priority="238" operator="equal">
+  <conditionalFormatting sqref="R1">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7867,15 +8194,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="8" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="9" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="7" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="7"/>
+    <col min="1" max="1" width="2.85546875" style="8" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="9" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="7" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -7940,7 +8267,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="3" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="3" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="5">
         <v>2</v>
       </c>
@@ -8022,15 +8349,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" style="15" customWidth="1"/>
-    <col min="2" max="2" width="7.53515625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="11.3046875" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" style="15" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19">
         <v>0</v>
       </c>
@@ -8053,7 +8380,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -8096,27 +8423,27 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A426B82-2E19-47C6-9DDF-914E7B26E6D0}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.2" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" style="33" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.3046875" style="32" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" style="32" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" style="32" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.3046875" style="32" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.84375" style="32" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.3046875" style="34" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.53515625" style="34" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.28515625" style="32" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.85546875" style="32" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.28515625" style="34" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5703125" style="34" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="34" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28" style="34" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.3046875" style="34" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.84375" style="34" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.3046875" style="34" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.84375" style="34" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.3046875" style="34" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.84375" style="33" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.3046875" style="32"/>
+    <col min="10" max="10" width="4.28515625" style="34" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" style="34" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" style="34" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" style="34" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.28515625" style="34" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.28515625" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="28" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" s="28" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>10</v>
       </c>
@@ -8161,33 +8488,33 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:15" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="31">
         <v>1</v>
       </c>
       <c r="B2" s="45" t="s">
+        <v>371</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>374</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="39" t="s">
+        <v>282</v>
+      </c>
+      <c r="G2" s="48" t="s">
         <v>372</v>
-      </c>
-      <c r="C2" s="59" t="s">
-        <v>375</v>
-      </c>
-      <c r="D2" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="39" t="s">
-        <v>283</v>
-      </c>
-      <c r="G2" s="48" t="s">
-        <v>373</v>
       </c>
       <c r="H2" s="46" t="s">
         <v>78</v>
       </c>
       <c r="I2" s="40" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J2" s="49" t="s">
         <v>9</v>

--- a/Versão5/EST/Ontologia_Geotecnica.xlsx
+++ b/Versão5/EST/Ontologia_Geotecnica.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADEC542C-DDD0-4C61-A76B-ECA649CC0911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE67B01E-AAE7-439A-9AD4-336D925E0E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="420">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -716,9 +716,6 @@
     <t>[ IfcGeographicElementSOIL_BORING_POINT ]</t>
   </si>
   <si>
-    <t>[ - ]</t>
-  </si>
-  <si>
     <t>Ponto.Sondagem</t>
   </si>
   <si>
@@ -1221,6 +1218,120 @@
   </si>
   <si>
     <t>Classe IFC</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>De.API</t>
+  </si>
+  <si>
+    <t>Métodos</t>
+  </si>
+  <si>
+    <t>Macros</t>
+  </si>
+  <si>
+    <t>API.Revit</t>
+  </si>
+  <si>
+    <t>Aplicação Revit</t>
+  </si>
+  <si>
+    <t>Aplicativo Revit</t>
+  </si>
+  <si>
+    <t>Revit Aplication</t>
+  </si>
+  <si>
+    <t>Geotécnica</t>
+  </si>
+  <si>
+    <t>API_Ambiente</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar ambientes do projeto"</t>
+  </si>
+  <si>
+    <t>tema</t>
+  </si>
+  <si>
+    <t>"API"</t>
+  </si>
+  <si>
+    <t>subtema</t>
+  </si>
+  <si>
+    <t>"Elementos Ambientes"</t>
+  </si>
+  <si>
+    <t>"[ Ambientes ]"</t>
+  </si>
+  <si>
+    <t>API_Andar</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar andares do projeto"</t>
+  </si>
+  <si>
+    <t>"Elementos Andares"</t>
+  </si>
+  <si>
+    <t>"[ Pavimentos ]"</t>
+  </si>
+  <si>
+    <t>API_Instância</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar instâncias do projeto"</t>
+  </si>
+  <si>
+    <t>"Elementos Instanciados"</t>
+  </si>
+  <si>
+    <t>"[ Elementos ]"</t>
+  </si>
+  <si>
+    <t>API_Simbolo</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar elementos tipificados do projeto"</t>
+  </si>
+  <si>
+    <t>"Elementos Tipificados"</t>
+  </si>
+  <si>
+    <t>"[ Tipos ]"</t>
+  </si>
+  <si>
+    <t>API_Material</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar materiais do projeto"</t>
+  </si>
+  <si>
+    <t>"Elementos Materiais"</t>
+  </si>
+  <si>
+    <t>"[ Materiais ]"</t>
+  </si>
+  <si>
+    <t>De.Geotécnica</t>
+  </si>
+  <si>
+    <t>Terreno</t>
+  </si>
+  <si>
+    <t>Solos</t>
+  </si>
+  <si>
+    <t>Geotécnico</t>
+  </si>
+  <si>
+    <t>Terreno.</t>
+  </si>
+  <si>
+    <t>Terrain.</t>
   </si>
 </sst>
 </file>
@@ -1332,7 +1443,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1431,19 +1542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.749992370372631"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1463,6 +1562,36 @@
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor rgb="FFD9F2D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -1552,7 +1681,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1639,9 +1768,6 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1657,7 +1783,7 @@
     <xf numFmtId="0" fontId="6" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1672,9 +1798,6 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1684,20 +1807,14 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1723,7 +1840,7 @@
     <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1733,11 +1850,67 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="64">
+  <dxfs count="72">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1745,6 +1918,58 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1816,24 +2041,6 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2205,6 +2412,44 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2309,16 +2554,6 @@
         <i/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2791,7 +3026,7 @@
   <cols>
     <col min="1" max="1" width="9.28515625" style="23" customWidth="1"/>
     <col min="2" max="2" width="39.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="38" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="37" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="23"/>
   </cols>
   <sheetData>
@@ -2802,7 +3037,7 @@
       <c r="B1" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="35" t="s">
         <v>86</v>
       </c>
     </row>
@@ -2813,7 +3048,7 @@
       <c r="B2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="36" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2824,7 +3059,7 @@
       <c r="B3" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="36" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2835,7 +3070,7 @@
       <c r="B4" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="36" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2847,7 +3082,7 @@
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="36" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2859,7 +3094,7 @@
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="36" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2870,7 +3105,7 @@
       <c r="B7" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="36" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2881,7 +3116,7 @@
       <c r="B8" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="36" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2892,7 +3127,7 @@
       <c r="B9" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="36" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2903,7 +3138,7 @@
       <c r="B10" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="36" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2914,7 +3149,7 @@
       <c r="B11" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="36" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2925,7 +3160,7 @@
       <c r="B12" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="36" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2936,7 +3171,7 @@
       <c r="B13" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="36" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2947,7 +3182,7 @@
       <c r="B14" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="36" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2958,7 +3193,7 @@
       <c r="B15" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="36" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2969,7 +3204,7 @@
       <c r="B16" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="36" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2978,9 +3213,9 @@
         <v>64</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="C17" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="C17" s="36" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2990,9 +3225,9 @@
       </c>
       <c r="B18" s="25">
         <f ca="1">NOW()</f>
-        <v>46253.68390960648</v>
-      </c>
-      <c r="C18" s="37" t="s">
+        <v>46260.316143055556</v>
+      </c>
+      <c r="C18" s="36" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3003,7 +3238,7 @@
       <c r="B19" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="C19" s="37" t="s">
+      <c r="C19" s="36" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3015,7 +3250,7 @@
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones integradas al español e inglés - Las traducciones deben revisarse constantemente</v>
       </c>
-      <c r="C20" s="37" t="s">
+      <c r="C20" s="36" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3027,7 +3262,7 @@
         <f>_xlfn.TRANSLATE(B19,"pt","en")</f>
         <v>Built-in Spanish and English Translations - Translations must be constantly reviewed</v>
       </c>
-      <c r="C21" s="37" t="s">
+      <c r="C21" s="36" t="s">
         <v>89</v>
       </c>
     </row>
@@ -3038,7 +3273,7 @@
       <c r="B22" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="37" t="s">
+      <c r="C22" s="36" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3049,7 +3284,7 @@
       <c r="B23" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="37" t="s">
+      <c r="C23" s="36" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3058,9 +3293,9 @@
         <v>68</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="C24" s="37" t="s">
+        <v>283</v>
+      </c>
+      <c r="C24" s="36" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3069,9 +3304,9 @@
         <v>69</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="C25" s="37" t="s">
+        <v>284</v>
+      </c>
+      <c r="C25" s="36" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3083,7 +3318,7 @@
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize GeoTechnical project elements.</v>
       </c>
-      <c r="C26" s="37" t="s">
+      <c r="C26" s="36" t="s">
         <v>89</v>
       </c>
     </row>
@@ -3094,68 +3329,68 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A56445-53D9-475A-B2C6-D376FC6516D5}">
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8" style="61" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="11" width="8" style="57" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="84.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="82" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="68.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="35.140625" customWidth="1"/>
+    <col min="17" max="17" width="35.85546875" customWidth="1"/>
+    <col min="18" max="18" width="38.140625" customWidth="1"/>
     <col min="19" max="19" width="3" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="43.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="22" customWidth="1"/>
+    <col min="21" max="21" width="13" customWidth="1"/>
+    <col min="22" max="22" width="7.85546875" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.7109375" customWidth="1"/>
+    <col min="25" max="25" width="32.140625" customWidth="1"/>
+    <col min="26" max="26" width="7.7109375" customWidth="1"/>
+    <col min="27" max="27" width="20.5703125" customWidth="1"/>
     <col min="28" max="28" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22">
         <v>1</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="47" t="s">
         <v>81</v>
       </c>
-      <c r="G1" s="52" t="s">
+      <c r="G1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="52" t="s">
+      <c r="H1" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="52" t="s">
+      <c r="I1" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="52" t="s">
+      <c r="J1" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="52" t="s">
+      <c r="K1" s="48" t="s">
         <v>4</v>
       </c>
       <c r="L1" s="29" t="s">
@@ -3176,7 +3411,7 @@
       <c r="Q1" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="R1" s="54" t="s">
+      <c r="R1" s="50" t="s">
         <v>83</v>
       </c>
       <c r="S1" s="29" t="s">
@@ -3194,43 +3429,43 @@
       <c r="W1" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="X1" s="51" t="s">
+      <c r="X1" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="Y1" s="53" t="s">
+      <c r="Y1" s="49" t="s">
         <v>79</v>
       </c>
-      <c r="Z1" s="53" t="s">
+      <c r="Z1" s="49" t="s">
+        <v>379</v>
+      </c>
+      <c r="AA1" s="49" t="s">
+        <v>381</v>
+      </c>
+      <c r="AB1" s="49" t="s">
         <v>380</v>
       </c>
-      <c r="AA1" s="53" t="s">
-        <v>382</v>
-      </c>
-      <c r="AB1" s="53" t="s">
-        <v>381</v>
-      </c>
-      <c r="AC1" s="53" t="s">
+      <c r="AC1" s="49" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50">
+      <c r="A2" s="46">
         <v>2</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C2" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C2" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D2" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="E2" s="55" t="s">
+      <c r="D2" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E2" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="56" t="s">
-        <v>217</v>
+      <c r="F2" s="52" t="s">
+        <v>216</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>9</v>
@@ -3247,30 +3482,30 @@
       <c r="K2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="57" t="str">
+      <c r="L2" s="53" t="str">
         <f t="shared" ref="L2" si="0">CONCATENATE("", C2)</f>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M2" s="57" t="str">
+      <c r="M2" s="53" t="str">
         <f t="shared" ref="M2" si="1">CONCATENATE("", D2)</f>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N2" s="57" t="str">
+      <c r="N2" s="53" t="str">
         <f t="shared" ref="N2" si="2">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
         <v>Compactação</v>
       </c>
-      <c r="O2" s="57" t="str">
+      <c r="O2" s="53" t="str">
         <f t="shared" ref="O2" si="3">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F2),"."," ")," De "," de "))</f>
         <v>Solo Reforçado</v>
       </c>
       <c r="P2" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="Q2" s="35" t="s">
+      <c r="Q2" s="34" t="s">
         <v>129</v>
       </c>
       <c r="R2" s="21" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S2" s="21" t="s">
         <v>9</v>
@@ -3288,46 +3523,46 @@
         <v>Compactação</v>
       </c>
       <c r="W2" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X2" s="58" t="str">
-        <f t="shared" ref="X2:X51" si="5">CONCATENATE("Key-GEO-",A2)</f>
+        <v>390</v>
+      </c>
+      <c r="X2" s="54" t="str">
+        <f t="shared" ref="X2:X53" si="5">CONCATENATE("Key-GEO-",A2)</f>
         <v>Key-GEO-2</v>
       </c>
-      <c r="Y2" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z2" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA2" s="60" t="s">
-        <v>270</v>
-      </c>
-      <c r="AB2" s="21" t="s">
-        <v>214</v>
+      <c r="Y2" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z2" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA2" s="56" t="s">
+        <v>269</v>
+      </c>
+      <c r="AB2" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC2" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50">
+      <c r="A3" s="46">
         <v>3</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C3" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C3" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D3" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="E3" s="55" t="s">
+      <c r="D3" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E3" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="F3" s="56" t="s">
-        <v>233</v>
+      <c r="F3" s="52" t="s">
+        <v>232</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>9</v>
@@ -3344,30 +3579,30 @@
       <c r="K3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="57" t="str">
+      <c r="L3" s="53" t="str">
         <f t="shared" ref="L3:L51" si="6">CONCATENATE("", C3)</f>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M3" s="57" t="str">
+      <c r="M3" s="53" t="str">
         <f t="shared" ref="M3:M51" si="7">CONCATENATE("", D3)</f>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N3" s="57" t="str">
+      <c r="N3" s="53" t="str">
         <f t="shared" ref="N3:N51" si="8">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E3),"."," ")," De "," de "))</f>
         <v>Compactação</v>
       </c>
-      <c r="O3" s="57" t="str">
+      <c r="O3" s="53" t="str">
         <f t="shared" ref="O3:O51" si="9">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F3),"."," ")," De "," de "))</f>
         <v>Solo Reforçado Dinamicamente</v>
       </c>
       <c r="P3" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="Q3" s="35" t="s">
-        <v>333</v>
+      <c r="Q3" s="34" t="s">
+        <v>332</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="S3" s="21" t="s">
         <v>9</v>
@@ -3385,46 +3620,46 @@
         <v>Compactação</v>
       </c>
       <c r="W3" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X3" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X3" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-3</v>
       </c>
-      <c r="Y3" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z3" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA3" s="60" t="s">
-        <v>269</v>
-      </c>
-      <c r="AB3" s="21" t="s">
-        <v>214</v>
+      <c r="Y3" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z3" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA3" s="56" t="s">
+        <v>268</v>
+      </c>
+      <c r="AB3" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC3" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="50">
+      <c r="A4" s="46">
         <v>4</v>
       </c>
-      <c r="B4" s="55" t="s">
+      <c r="B4" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C4" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C4" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D4" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="E4" s="55" t="s">
+      <c r="D4" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E4" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="F4" s="56" t="s">
-        <v>234</v>
+      <c r="F4" s="52" t="s">
+        <v>233</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>9</v>
@@ -3441,30 +3676,30 @@
       <c r="K4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="57" t="str">
+      <c r="L4" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M4" s="57" t="str">
+      <c r="M4" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N4" s="57" t="str">
+      <c r="N4" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Compactação</v>
       </c>
-      <c r="O4" s="57" t="str">
+      <c r="O4" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Solo Reforçado Groute</v>
       </c>
       <c r="P4" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="Q4" s="35" t="s">
-        <v>334</v>
+      <c r="Q4" s="34" t="s">
+        <v>333</v>
       </c>
       <c r="R4" s="21" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="S4" s="21" t="s">
         <v>9</v>
@@ -3482,46 +3717,46 @@
         <v>Compactação</v>
       </c>
       <c r="W4" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X4" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X4" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-4</v>
       </c>
-      <c r="Y4" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z4" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA4" s="60" t="s">
-        <v>268</v>
-      </c>
-      <c r="AB4" s="21" t="s">
-        <v>214</v>
+      <c r="Y4" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z4" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA4" s="56" t="s">
+        <v>267</v>
+      </c>
+      <c r="AB4" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC4" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="50">
+      <c r="A5" s="46">
         <v>5</v>
       </c>
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C5" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C5" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D5" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="E5" s="55" t="s">
+      <c r="D5" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E5" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="F5" s="56" t="s">
-        <v>218</v>
+      <c r="F5" s="52" t="s">
+        <v>217</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>9</v>
@@ -3538,30 +3773,30 @@
       <c r="K5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="57" t="str">
+      <c r="L5" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M5" s="57" t="str">
+      <c r="M5" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N5" s="57" t="str">
+      <c r="N5" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Compactação</v>
       </c>
-      <c r="O5" s="57" t="str">
+      <c r="O5" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Solo Reforçado Substituído</v>
       </c>
       <c r="P5" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="Q5" s="35" t="s">
-        <v>335</v>
+      <c r="Q5" s="34" t="s">
+        <v>334</v>
       </c>
       <c r="R5" s="21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="S5" s="21" t="s">
         <v>9</v>
@@ -3579,46 +3814,46 @@
         <v>Compactação</v>
       </c>
       <c r="W5" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X5" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X5" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-5</v>
       </c>
-      <c r="Y5" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z5" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA5" s="60" t="s">
-        <v>267</v>
-      </c>
-      <c r="AB5" s="21" t="s">
-        <v>214</v>
+      <c r="Y5" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z5" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA5" s="56" t="s">
+        <v>266</v>
+      </c>
+      <c r="AB5" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC5" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="50">
+      <c r="A6" s="46">
         <v>6</v>
       </c>
-      <c r="B6" s="55" t="s">
+      <c r="B6" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C6" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C6" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D6" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="E6" s="55" t="s">
+      <c r="D6" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E6" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="F6" s="56" t="s">
-        <v>235</v>
+      <c r="F6" s="52" t="s">
+        <v>234</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>9</v>
@@ -3635,30 +3870,30 @@
       <c r="K6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="57" t="str">
+      <c r="L6" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M6" s="57" t="str">
+      <c r="M6" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N6" s="57" t="str">
+      <c r="N6" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Compactação</v>
       </c>
-      <c r="O6" s="57" t="str">
+      <c r="O6" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Solo Reforçado Rolado</v>
       </c>
       <c r="P6" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="Q6" s="35" t="s">
-        <v>336</v>
+      <c r="Q6" s="34" t="s">
+        <v>335</v>
       </c>
       <c r="R6" s="21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="S6" s="21" t="s">
         <v>9</v>
@@ -3676,46 +3911,46 @@
         <v>Compactação</v>
       </c>
       <c r="W6" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X6" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X6" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-6</v>
       </c>
-      <c r="Y6" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z6" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA6" s="60" t="s">
-        <v>266</v>
-      </c>
-      <c r="AB6" s="21" t="s">
-        <v>214</v>
+      <c r="Y6" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z6" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA6" s="56" t="s">
+        <v>265</v>
+      </c>
+      <c r="AB6" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC6" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="50">
+      <c r="A7" s="46">
         <v>7</v>
       </c>
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C7" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C7" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D7" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="E7" s="55" t="s">
+      <c r="D7" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E7" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="F7" s="56" t="s">
-        <v>236</v>
+      <c r="F7" s="52" t="s">
+        <v>235</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>9</v>
@@ -3732,30 +3967,30 @@
       <c r="K7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L7" s="57" t="str">
+      <c r="L7" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M7" s="57" t="str">
+      <c r="M7" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N7" s="57" t="str">
+      <c r="N7" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Compactação</v>
       </c>
-      <c r="O7" s="57" t="str">
+      <c r="O7" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Solo Reforçado PréCarregado</v>
       </c>
       <c r="P7" s="21" t="s">
-        <v>370</v>
-      </c>
-      <c r="Q7" s="35" t="s">
-        <v>337</v>
+        <v>369</v>
+      </c>
+      <c r="Q7" s="34" t="s">
+        <v>336</v>
       </c>
       <c r="R7" s="21" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="S7" s="21" t="s">
         <v>9</v>
@@ -3773,46 +4008,46 @@
         <v>Compactação</v>
       </c>
       <c r="W7" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X7" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X7" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-7</v>
       </c>
-      <c r="Y7" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z7" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA7" s="60" t="s">
-        <v>265</v>
-      </c>
-      <c r="AB7" s="21" t="s">
-        <v>214</v>
+      <c r="Y7" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z7" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA7" s="56" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB7" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC7" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="50">
+      <c r="A8" s="46">
         <v>8</v>
       </c>
-      <c r="B8" s="55" t="s">
+      <c r="B8" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C8" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C8" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D8" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="E8" s="55" t="s">
+      <c r="D8" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E8" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="F8" s="56" t="s">
-        <v>237</v>
+      <c r="F8" s="52" t="s">
+        <v>236</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>9</v>
@@ -3829,30 +4064,30 @@
       <c r="K8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L8" s="57" t="str">
+      <c r="L8" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M8" s="57" t="str">
+      <c r="M8" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N8" s="57" t="str">
+      <c r="N8" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Compactação</v>
       </c>
-      <c r="O8" s="57" t="str">
+      <c r="O8" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Solo Reforçado Drenado</v>
       </c>
       <c r="P8" s="21" t="s">
-        <v>369</v>
-      </c>
-      <c r="Q8" s="35" t="s">
         <v>368</v>
       </c>
+      <c r="Q8" s="34" t="s">
+        <v>367</v>
+      </c>
       <c r="R8" s="21" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="S8" s="21" t="s">
         <v>9</v>
@@ -3870,46 +4105,46 @@
         <v>Compactação</v>
       </c>
       <c r="W8" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X8" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X8" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-8</v>
       </c>
-      <c r="Y8" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z8" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA8" s="60" t="s">
-        <v>264</v>
-      </c>
-      <c r="AB8" s="21" t="s">
-        <v>214</v>
+      <c r="Y8" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z8" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA8" s="56" t="s">
+        <v>263</v>
+      </c>
+      <c r="AB8" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC8" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="50">
-        <v>9</v>
-      </c>
-      <c r="B9" s="55" t="s">
+      <c r="A9" s="46">
+        <v>9</v>
+      </c>
+      <c r="B9" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C9" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C9" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D9" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="E9" s="55" t="s">
-        <v>281</v>
-      </c>
-      <c r="F9" s="56" t="s">
-        <v>219</v>
+      <c r="D9" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E9" s="51" t="s">
+        <v>280</v>
+      </c>
+      <c r="F9" s="52" t="s">
+        <v>218</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>9</v>
@@ -3926,30 +4161,30 @@
       <c r="K9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L9" s="57" t="str">
+      <c r="L9" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M9" s="57" t="str">
+      <c r="M9" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N9" s="57" t="str">
+      <c r="N9" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Escavações</v>
       </c>
-      <c r="O9" s="57" t="str">
+      <c r="O9" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Escavação</v>
       </c>
       <c r="P9" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="Q9" s="35" t="s">
-        <v>338</v>
+      <c r="Q9" s="34" t="s">
+        <v>337</v>
       </c>
       <c r="R9" s="21" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="S9" s="21" t="s">
         <v>9</v>
@@ -3967,46 +4202,46 @@
         <v>Escavações</v>
       </c>
       <c r="W9" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X9" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X9" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-9</v>
       </c>
-      <c r="Y9" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z9" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA9" s="60" t="s">
-        <v>254</v>
-      </c>
-      <c r="AB9" s="21" t="s">
-        <v>214</v>
+      <c r="Y9" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z9" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA9" s="56" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB9" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC9" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="50">
+      <c r="A10" s="46">
         <v>10</v>
       </c>
-      <c r="B10" s="55" t="s">
+      <c r="B10" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C10" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C10" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D10" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="E10" s="55" t="s">
-        <v>281</v>
-      </c>
-      <c r="F10" s="56" t="s">
-        <v>220</v>
+      <c r="D10" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E10" s="51" t="s">
+        <v>280</v>
+      </c>
+      <c r="F10" s="52" t="s">
+        <v>219</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>9</v>
@@ -4023,30 +4258,30 @@
       <c r="K10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L10" s="57" t="str">
+      <c r="L10" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M10" s="57" t="str">
+      <c r="M10" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N10" s="57" t="str">
+      <c r="N10" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Escavações</v>
       </c>
-      <c r="O10" s="57" t="str">
+      <c r="O10" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Escavação Base</v>
       </c>
       <c r="P10" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="Q10" s="35" t="s">
-        <v>339</v>
+      <c r="Q10" s="34" t="s">
+        <v>338</v>
       </c>
       <c r="R10" s="21" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="S10" s="21" t="s">
         <v>9</v>
@@ -4064,46 +4299,46 @@
         <v>Escavações</v>
       </c>
       <c r="W10" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X10" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X10" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-10</v>
       </c>
-      <c r="Y10" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z10" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA10" s="60" t="s">
-        <v>253</v>
-      </c>
-      <c r="AB10" s="21" t="s">
-        <v>214</v>
+      <c r="Y10" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z10" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA10" s="56" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB10" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC10" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50">
+      <c r="A11" s="46">
         <v>11</v>
       </c>
-      <c r="B11" s="55" t="s">
+      <c r="B11" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C11" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C11" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D11" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="E11" s="55" t="s">
-        <v>281</v>
-      </c>
-      <c r="F11" s="56" t="s">
-        <v>221</v>
+      <c r="D11" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>280</v>
+      </c>
+      <c r="F11" s="52" t="s">
+        <v>220</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>9</v>
@@ -4120,30 +4355,30 @@
       <c r="K11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L11" s="57" t="str">
+      <c r="L11" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M11" s="57" t="str">
+      <c r="M11" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N11" s="57" t="str">
+      <c r="N11" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Escavações</v>
       </c>
-      <c r="O11" s="57" t="str">
+      <c r="O11" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Escavação Corte</v>
       </c>
       <c r="P11" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="Q11" s="35" t="s">
-        <v>340</v>
+      <c r="Q11" s="34" t="s">
+        <v>339</v>
       </c>
       <c r="R11" s="21" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="S11" s="21" t="s">
         <v>9</v>
@@ -4161,46 +4396,46 @@
         <v>Escavações</v>
       </c>
       <c r="W11" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X11" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X11" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-11</v>
       </c>
-      <c r="Y11" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z11" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA11" s="60" t="s">
-        <v>252</v>
-      </c>
-      <c r="AB11" s="21" t="s">
-        <v>214</v>
+      <c r="Y11" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z11" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA11" s="56" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB11" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC11" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="50">
+      <c r="A12" s="46">
         <v>12</v>
       </c>
-      <c r="B12" s="55" t="s">
+      <c r="B12" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C12" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C12" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D12" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="E12" s="55" t="s">
-        <v>281</v>
-      </c>
-      <c r="F12" s="56" t="s">
-        <v>222</v>
+      <c r="D12" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E12" s="51" t="s">
+        <v>280</v>
+      </c>
+      <c r="F12" s="52" t="s">
+        <v>221</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>9</v>
@@ -4217,30 +4452,30 @@
       <c r="K12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L12" s="57" t="str">
+      <c r="L12" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M12" s="57" t="str">
+      <c r="M12" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N12" s="57" t="str">
+      <c r="N12" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Escavações</v>
       </c>
-      <c r="O12" s="57" t="str">
+      <c r="O12" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Escavação Dragagem</v>
       </c>
       <c r="P12" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="Q12" s="35" t="s">
-        <v>341</v>
+      <c r="Q12" s="34" t="s">
+        <v>340</v>
       </c>
       <c r="R12" s="21" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="S12" s="21" t="s">
         <v>9</v>
@@ -4258,46 +4493,46 @@
         <v>Escavações</v>
       </c>
       <c r="W12" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X12" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X12" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-12</v>
       </c>
-      <c r="Y12" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z12" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA12" s="60" t="s">
-        <v>251</v>
-      </c>
-      <c r="AB12" s="21" t="s">
-        <v>214</v>
+      <c r="Y12" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z12" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA12" s="56" t="s">
+        <v>250</v>
+      </c>
+      <c r="AB12" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC12" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="50">
+      <c r="A13" s="46">
         <v>13</v>
       </c>
-      <c r="B13" s="55" t="s">
+      <c r="B13" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C13" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C13" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D13" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="E13" s="55" t="s">
-        <v>281</v>
-      </c>
-      <c r="F13" s="56" t="s">
-        <v>227</v>
+      <c r="D13" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E13" s="51" t="s">
+        <v>280</v>
+      </c>
+      <c r="F13" s="52" t="s">
+        <v>226</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>9</v>
@@ -4314,30 +4549,30 @@
       <c r="K13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L13" s="57" t="str">
+      <c r="L13" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M13" s="57" t="str">
+      <c r="M13" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N13" s="57" t="str">
+      <c r="N13" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Escavações</v>
       </c>
-      <c r="O13" s="57" t="str">
+      <c r="O13" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Escavação Terreno</v>
       </c>
       <c r="P13" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="Q13" s="35" t="s">
+      <c r="Q13" s="34" t="s">
         <v>102</v>
       </c>
       <c r="R13" s="21" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="S13" s="21" t="s">
         <v>9</v>
@@ -4355,46 +4590,46 @@
         <v>Escavações</v>
       </c>
       <c r="W13" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X13" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X13" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-13</v>
       </c>
-      <c r="Y13" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z13" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA13" s="60" t="s">
-        <v>250</v>
-      </c>
-      <c r="AB13" s="21" t="s">
-        <v>214</v>
+      <c r="Y13" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z13" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA13" s="56" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB13" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC13" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50">
+      <c r="A14" s="46">
         <v>14</v>
       </c>
-      <c r="B14" s="55" t="s">
+      <c r="B14" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C14" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C14" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D14" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="E14" s="55" t="s">
-        <v>281</v>
-      </c>
-      <c r="F14" s="56" t="s">
-        <v>226</v>
+      <c r="D14" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E14" s="51" t="s">
+        <v>280</v>
+      </c>
+      <c r="F14" s="52" t="s">
+        <v>225</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>9</v>
@@ -4411,30 +4646,30 @@
       <c r="K14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L14" s="57" t="str">
+      <c r="L14" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M14" s="57" t="str">
+      <c r="M14" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N14" s="57" t="str">
+      <c r="N14" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Escavações</v>
       </c>
-      <c r="O14" s="57" t="str">
+      <c r="O14" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Escavação SobreEscavação</v>
       </c>
       <c r="P14" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="Q14" s="35" t="s">
-        <v>342</v>
+      <c r="Q14" s="34" t="s">
+        <v>341</v>
       </c>
       <c r="R14" s="21" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="S14" s="21" t="s">
         <v>9</v>
@@ -4452,46 +4687,46 @@
         <v>Escavações</v>
       </c>
       <c r="W14" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X14" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X14" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-14</v>
       </c>
-      <c r="Y14" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z14" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA14" s="60" t="s">
-        <v>249</v>
-      </c>
-      <c r="AB14" s="21" t="s">
-        <v>214</v>
+      <c r="Y14" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z14" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA14" s="56" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB14" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC14" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="50">
+      <c r="A15" s="46">
         <v>15</v>
       </c>
-      <c r="B15" s="55" t="s">
+      <c r="B15" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C15" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C15" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D15" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="E15" s="55" t="s">
-        <v>281</v>
-      </c>
-      <c r="F15" s="56" t="s">
-        <v>223</v>
+      <c r="D15" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E15" s="51" t="s">
+        <v>280</v>
+      </c>
+      <c r="F15" s="52" t="s">
+        <v>222</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>9</v>
@@ -4508,30 +4743,30 @@
       <c r="K15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L15" s="57" t="str">
+      <c r="L15" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M15" s="57" t="str">
+      <c r="M15" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N15" s="57" t="str">
+      <c r="N15" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Escavações</v>
       </c>
-      <c r="O15" s="57" t="str">
+      <c r="O15" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Escavação Fresagem</v>
       </c>
       <c r="P15" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="Q15" s="35" t="s">
-        <v>343</v>
+      <c r="Q15" s="34" t="s">
+        <v>342</v>
       </c>
       <c r="R15" s="21" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="S15" s="21" t="s">
         <v>9</v>
@@ -4549,46 +4784,46 @@
         <v>Escavações</v>
       </c>
       <c r="W15" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X15" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X15" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-15</v>
       </c>
-      <c r="Y15" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z15" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA15" s="60" t="s">
-        <v>248</v>
-      </c>
-      <c r="AB15" s="21" t="s">
-        <v>214</v>
+      <c r="Y15" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z15" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA15" s="56" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB15" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC15" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="50">
+      <c r="A16" s="46">
         <v>16</v>
       </c>
-      <c r="B16" s="55" t="s">
+      <c r="B16" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C16" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C16" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D16" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="E16" s="55" t="s">
-        <v>281</v>
-      </c>
-      <c r="F16" s="56" t="s">
-        <v>244</v>
+      <c r="D16" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E16" s="51" t="s">
+        <v>280</v>
+      </c>
+      <c r="F16" s="52" t="s">
+        <v>243</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>9</v>
@@ -4605,30 +4840,30 @@
       <c r="K16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L16" s="57" t="str">
+      <c r="L16" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M16" s="57" t="str">
+      <c r="M16" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N16" s="57" t="str">
+      <c r="N16" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Escavações</v>
       </c>
-      <c r="O16" s="57" t="str">
+      <c r="O16" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Escavação Banqueta</v>
       </c>
       <c r="P16" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="Q16" s="35" t="s">
-        <v>344</v>
+      <c r="Q16" s="34" t="s">
+        <v>343</v>
       </c>
       <c r="R16" s="21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="S16" s="21" t="s">
         <v>9</v>
@@ -4646,46 +4881,46 @@
         <v>Escavações</v>
       </c>
       <c r="W16" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X16" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X16" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-16</v>
       </c>
-      <c r="Y16" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z16" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA16" s="60" t="s">
-        <v>247</v>
-      </c>
-      <c r="AB16" s="21" t="s">
-        <v>214</v>
+      <c r="Y16" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z16" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA16" s="56" t="s">
+        <v>246</v>
+      </c>
+      <c r="AB16" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC16" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="50">
+      <c r="A17" s="46">
         <v>17</v>
       </c>
-      <c r="B17" s="55" t="s">
+      <c r="B17" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C17" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C17" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D17" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="E17" s="55" t="s">
-        <v>281</v>
-      </c>
-      <c r="F17" s="56" t="s">
-        <v>224</v>
+      <c r="D17" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E17" s="51" t="s">
+        <v>280</v>
+      </c>
+      <c r="F17" s="52" t="s">
+        <v>223</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>9</v>
@@ -4702,30 +4937,30 @@
       <c r="K17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L17" s="57" t="str">
+      <c r="L17" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M17" s="57" t="str">
+      <c r="M17" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N17" s="57" t="str">
+      <c r="N17" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Escavações</v>
       </c>
-      <c r="O17" s="57" t="str">
+      <c r="O17" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Escavação Remoção</v>
       </c>
       <c r="P17" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="Q17" s="35" t="s">
-        <v>345</v>
+      <c r="Q17" s="34" t="s">
+        <v>344</v>
       </c>
       <c r="R17" s="21" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="S17" s="21" t="s">
         <v>9</v>
@@ -4743,46 +4978,46 @@
         <v>Escavações</v>
       </c>
       <c r="W17" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X17" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X17" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-17</v>
       </c>
-      <c r="Y17" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z17" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA17" s="60" t="s">
-        <v>246</v>
-      </c>
-      <c r="AB17" s="21" t="s">
-        <v>214</v>
+      <c r="Y17" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z17" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA17" s="56" t="s">
+        <v>245</v>
+      </c>
+      <c r="AB17" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC17" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="18" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="50">
+      <c r="A18" s="46">
         <v>18</v>
       </c>
-      <c r="B18" s="55" t="s">
+      <c r="B18" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C18" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C18" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D18" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="E18" s="55" t="s">
-        <v>281</v>
-      </c>
-      <c r="F18" s="56" t="s">
-        <v>225</v>
+      <c r="D18" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E18" s="51" t="s">
+        <v>280</v>
+      </c>
+      <c r="F18" s="52" t="s">
+        <v>224</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>9</v>
@@ -4799,30 +5034,30 @@
       <c r="K18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L18" s="57" t="str">
+      <c r="L18" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M18" s="57" t="str">
+      <c r="M18" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N18" s="57" t="str">
+      <c r="N18" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Escavações</v>
       </c>
-      <c r="O18" s="57" t="str">
+      <c r="O18" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Escavação Trincheira</v>
       </c>
       <c r="P18" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="Q18" s="35" t="s">
-        <v>346</v>
+      <c r="Q18" s="34" t="s">
+        <v>345</v>
       </c>
       <c r="R18" s="21" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="S18" s="21" t="s">
         <v>9</v>
@@ -4840,47 +5075,47 @@
         <v>Escavações</v>
       </c>
       <c r="W18" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X18" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X18" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-18</v>
       </c>
-      <c r="Y18" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z18" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA18" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="AB18" s="21" t="s">
-        <v>214</v>
+      <c r="Y18" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z18" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA18" s="56" t="s">
+        <v>244</v>
+      </c>
+      <c r="AB18" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC18" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="19" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50">
+      <c r="A19" s="46">
         <v>19</v>
       </c>
-      <c r="B19" s="55" t="s">
+      <c r="B19" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C19" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C19" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D19" s="55" t="s">
+      <c r="D19" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E19" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="E19" s="55" t="s">
+      <c r="F19" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="F19" s="56" t="s">
-        <v>240</v>
-      </c>
       <c r="G19" s="6" t="s">
         <v>9</v>
       </c>
@@ -4896,27 +5131,27 @@
       <c r="K19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L19" s="57" t="str">
+      <c r="L19" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M19" s="57" t="str">
+      <c r="M19" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N19" s="57" t="str">
+      <c r="N19" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="O19" s="57" t="str">
+      <c r="O19" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Terrapleno</v>
       </c>
       <c r="P19" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="Q19" s="35" t="s">
-        <v>347</v>
+      <c r="Q19" s="34" t="s">
+        <v>346</v>
       </c>
       <c r="R19" s="21" t="s">
         <v>109</v>
@@ -4937,46 +5172,46 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W19" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X19" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X19" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-19</v>
       </c>
-      <c r="Y19" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z19" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA19" s="60" t="s">
-        <v>263</v>
-      </c>
-      <c r="AB19" s="21" t="s">
-        <v>214</v>
+      <c r="Y19" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z19" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA19" s="56" t="s">
+        <v>262</v>
+      </c>
+      <c r="AB19" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC19" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="20" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="50">
+      <c r="A20" s="46">
         <v>20</v>
       </c>
-      <c r="B20" s="55" t="s">
+      <c r="B20" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C20" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C20" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D20" s="55" t="s">
+      <c r="D20" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E20" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="E20" s="55" t="s">
-        <v>239</v>
-      </c>
-      <c r="F20" s="56" t="s">
-        <v>241</v>
+      <c r="F20" s="52" t="s">
+        <v>240</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>9</v>
@@ -4993,30 +5228,30 @@
       <c r="K20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L20" s="57" t="str">
+      <c r="L20" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M20" s="57" t="str">
+      <c r="M20" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N20" s="57" t="str">
+      <c r="N20" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="O20" s="57" t="str">
+      <c r="O20" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Aterro Terrapleno</v>
       </c>
       <c r="P20" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="Q20" s="35" t="s">
-        <v>348</v>
+      <c r="Q20" s="34" t="s">
+        <v>347</v>
       </c>
       <c r="R20" s="21" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="S20" s="21" t="s">
         <v>9</v>
@@ -5034,46 +5269,46 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W20" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X20" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X20" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-20</v>
       </c>
-      <c r="Y20" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z20" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA20" s="60" t="s">
-        <v>262</v>
-      </c>
-      <c r="AB20" s="21" t="s">
-        <v>214</v>
+      <c r="Y20" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z20" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA20" s="56" t="s">
+        <v>261</v>
+      </c>
+      <c r="AB20" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC20" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="50">
+      <c r="A21" s="46">
         <v>21</v>
       </c>
-      <c r="B21" s="55" t="s">
+      <c r="B21" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C21" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C21" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D21" s="55" t="s">
+      <c r="D21" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E21" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="E21" s="55" t="s">
-        <v>239</v>
-      </c>
-      <c r="F21" s="56" t="s">
-        <v>242</v>
+      <c r="F21" s="52" t="s">
+        <v>241</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>9</v>
@@ -5090,30 +5325,30 @@
       <c r="K21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L21" s="57" t="str">
+      <c r="L21" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M21" s="57" t="str">
+      <c r="M21" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N21" s="57" t="str">
+      <c r="N21" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="O21" s="57" t="str">
+      <c r="O21" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Aterro Reenchimento</v>
       </c>
       <c r="P21" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="Q21" s="35" t="s">
-        <v>349</v>
+      <c r="Q21" s="34" t="s">
+        <v>348</v>
       </c>
       <c r="R21" s="21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="S21" s="21" t="s">
         <v>9</v>
@@ -5131,46 +5366,46 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W21" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X21" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X21" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-21</v>
       </c>
-      <c r="Y21" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z21" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA21" s="60" t="s">
-        <v>261</v>
-      </c>
-      <c r="AB21" s="21" t="s">
-        <v>214</v>
+      <c r="Y21" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z21" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA21" s="56" t="s">
+        <v>260</v>
+      </c>
+      <c r="AB21" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC21" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="22" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="50">
+      <c r="A22" s="46">
         <v>22</v>
       </c>
-      <c r="B22" s="55" t="s">
+      <c r="B22" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C22" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C22" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D22" s="55" t="s">
+      <c r="D22" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E22" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="E22" s="55" t="s">
-        <v>239</v>
-      </c>
-      <c r="F22" s="56" t="s">
-        <v>228</v>
+      <c r="F22" s="52" t="s">
+        <v>227</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>9</v>
@@ -5187,30 +5422,30 @@
       <c r="K22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L22" s="57" t="str">
+      <c r="L22" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M22" s="57" t="str">
+      <c r="M22" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N22" s="57" t="str">
+      <c r="N22" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="O22" s="57" t="str">
+      <c r="O22" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Aterro Contrapeso</v>
       </c>
       <c r="P22" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="Q22" s="35" t="s">
-        <v>350</v>
+      <c r="Q22" s="34" t="s">
+        <v>349</v>
       </c>
       <c r="R22" s="21" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="S22" s="21" t="s">
         <v>9</v>
@@ -5228,46 +5463,46 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W22" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X22" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X22" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-22</v>
       </c>
-      <c r="Y22" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z22" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA22" s="60" t="s">
-        <v>260</v>
-      </c>
-      <c r="AB22" s="21" t="s">
-        <v>214</v>
+      <c r="Y22" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z22" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA22" s="56" t="s">
+        <v>259</v>
+      </c>
+      <c r="AB22" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC22" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="23" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="50">
+      <c r="A23" s="46">
         <v>23</v>
       </c>
-      <c r="B23" s="55" t="s">
+      <c r="B23" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C23" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C23" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D23" s="55" t="s">
+      <c r="D23" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E23" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="E23" s="55" t="s">
-        <v>239</v>
-      </c>
-      <c r="F23" s="56" t="s">
-        <v>229</v>
+      <c r="F23" s="52" t="s">
+        <v>228</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>9</v>
@@ -5284,30 +5519,30 @@
       <c r="K23" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L23" s="57" t="str">
+      <c r="L23" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M23" s="57" t="str">
+      <c r="M23" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N23" s="57" t="str">
+      <c r="N23" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="O23" s="57" t="str">
+      <c r="O23" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Aterro Preenchimento</v>
       </c>
       <c r="P23" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="Q23" s="35" t="s">
-        <v>351</v>
+      <c r="Q23" s="34" t="s">
+        <v>350</v>
       </c>
       <c r="R23" s="21" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="S23" s="21" t="s">
         <v>9</v>
@@ -5325,46 +5560,46 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W23" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X23" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X23" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-23</v>
       </c>
-      <c r="Y23" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z23" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA23" s="60" t="s">
-        <v>259</v>
-      </c>
-      <c r="AB23" s="21" t="s">
-        <v>214</v>
+      <c r="Y23" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z23" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA23" s="56" t="s">
+        <v>258</v>
+      </c>
+      <c r="AB23" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC23" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="24" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="50">
+      <c r="A24" s="46">
         <v>24</v>
       </c>
-      <c r="B24" s="55" t="s">
+      <c r="B24" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C24" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C24" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D24" s="55" t="s">
+      <c r="D24" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E24" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="E24" s="55" t="s">
-        <v>239</v>
-      </c>
-      <c r="F24" s="56" t="s">
-        <v>230</v>
+      <c r="F24" s="52" t="s">
+        <v>229</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>9</v>
@@ -5381,30 +5616,30 @@
       <c r="K24" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L24" s="57" t="str">
+      <c r="L24" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M24" s="57" t="str">
+      <c r="M24" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N24" s="57" t="str">
+      <c r="N24" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="O24" s="57" t="str">
+      <c r="O24" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Aterro Inclinado</v>
       </c>
       <c r="P24" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="Q24" s="35" t="s">
-        <v>352</v>
+      <c r="Q24" s="34" t="s">
+        <v>351</v>
       </c>
       <c r="R24" s="21" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="S24" s="21" t="s">
         <v>9</v>
@@ -5422,46 +5657,46 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W24" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X24" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X24" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-24</v>
       </c>
-      <c r="Y24" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z24" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA24" s="60" t="s">
-        <v>258</v>
-      </c>
-      <c r="AB24" s="21" t="s">
-        <v>214</v>
+      <c r="Y24" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z24" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA24" s="56" t="s">
+        <v>257</v>
+      </c>
+      <c r="AB24" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC24" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="50">
+      <c r="A25" s="46">
         <v>25</v>
       </c>
-      <c r="B25" s="55" t="s">
+      <c r="B25" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C25" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C25" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D25" s="55" t="s">
+      <c r="D25" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E25" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="E25" s="55" t="s">
-        <v>239</v>
-      </c>
-      <c r="F25" s="56" t="s">
-        <v>243</v>
+      <c r="F25" s="52" t="s">
+        <v>242</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>9</v>
@@ -5478,30 +5713,30 @@
       <c r="K25" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L25" s="57" t="str">
+      <c r="L25" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M25" s="57" t="str">
+      <c r="M25" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N25" s="57" t="str">
+      <c r="N25" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="O25" s="57" t="str">
+      <c r="O25" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Aterro Subterrâneo</v>
       </c>
       <c r="P25" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="Q25" s="35" t="s">
-        <v>353</v>
+      <c r="Q25" s="34" t="s">
+        <v>352</v>
       </c>
       <c r="R25" s="21" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="S25" s="21" t="s">
         <v>9</v>
@@ -5519,46 +5754,46 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W25" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X25" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X25" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-25</v>
       </c>
-      <c r="Y25" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z25" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA25" s="60" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB25" s="21" t="s">
-        <v>214</v>
+      <c r="Y25" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z25" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA25" s="56" t="s">
+        <v>256</v>
+      </c>
+      <c r="AB25" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC25" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="50">
+      <c r="A26" s="46">
         <v>26</v>
       </c>
-      <c r="B26" s="55" t="s">
+      <c r="B26" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C26" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C26" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D26" s="55" t="s">
+      <c r="D26" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E26" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="E26" s="55" t="s">
-        <v>239</v>
-      </c>
-      <c r="F26" s="56" t="s">
-        <v>231</v>
+      <c r="F26" s="52" t="s">
+        <v>230</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>9</v>
@@ -5575,30 +5810,30 @@
       <c r="K26" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L26" s="57" t="str">
+      <c r="L26" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M26" s="57" t="str">
+      <c r="M26" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N26" s="57" t="str">
+      <c r="N26" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="O26" s="57" t="str">
+      <c r="O26" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Aterro Camada</v>
       </c>
       <c r="P26" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="Q26" s="35" t="s">
-        <v>354</v>
+      <c r="Q26" s="34" t="s">
+        <v>353</v>
       </c>
       <c r="R26" s="21" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="S26" s="21" t="s">
         <v>9</v>
@@ -5616,46 +5851,46 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W26" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X26" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X26" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-26</v>
       </c>
-      <c r="Y26" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z26" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA26" s="60" t="s">
-        <v>256</v>
-      </c>
-      <c r="AB26" s="21" t="s">
-        <v>214</v>
+      <c r="Y26" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z26" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA26" s="56" t="s">
+        <v>255</v>
+      </c>
+      <c r="AB26" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC26" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="27" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="50">
+      <c r="A27" s="46">
         <v>27</v>
       </c>
-      <c r="B27" s="55" t="s">
+      <c r="B27" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C27" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C27" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D27" s="55" t="s">
+      <c r="D27" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E27" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="E27" s="55" t="s">
-        <v>239</v>
-      </c>
-      <c r="F27" s="56" t="s">
-        <v>232</v>
+      <c r="F27" s="52" t="s">
+        <v>231</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>9</v>
@@ -5672,30 +5907,30 @@
       <c r="K27" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L27" s="57" t="str">
+      <c r="L27" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M27" s="57" t="str">
+      <c r="M27" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Solo</v>
       </c>
-      <c r="N27" s="57" t="str">
+      <c r="N27" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Terraplenagens</v>
       </c>
-      <c r="O27" s="57" t="str">
+      <c r="O27" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Aterro Transição</v>
       </c>
       <c r="P27" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="Q27" s="35" t="s">
-        <v>355</v>
+      <c r="Q27" s="34" t="s">
+        <v>354</v>
       </c>
       <c r="R27" s="21" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="S27" s="21" t="s">
         <v>9</v>
@@ -5713,45 +5948,45 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W27" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X27" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X27" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-27</v>
       </c>
-      <c r="Y27" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z27" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA27" s="60" t="s">
-        <v>255</v>
-      </c>
-      <c r="AB27" s="21" t="s">
-        <v>214</v>
+      <c r="Y27" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z27" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA27" s="56" t="s">
+        <v>254</v>
+      </c>
+      <c r="AB27" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC27" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="28" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="50">
+      <c r="A28" s="46">
         <v>28</v>
       </c>
-      <c r="B28" s="55" t="s">
+      <c r="B28" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C28" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C28" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D28" s="55" t="s">
-        <v>271</v>
-      </c>
-      <c r="E28" s="44" t="s">
+      <c r="D28" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="E28" s="42" t="s">
         <v>203</v>
       </c>
-      <c r="F28" s="44" t="s">
+      <c r="F28" s="42" t="s">
         <v>148</v>
       </c>
       <c r="G28" s="6" t="s">
@@ -5769,30 +6004,30 @@
       <c r="K28" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L28" s="57" t="str">
+      <c r="L28" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M28" s="57" t="str">
+      <c r="M28" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N28" s="57" t="str">
+      <c r="N28" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Pontos do Modelo</v>
       </c>
-      <c r="O28" s="57" t="str">
+      <c r="O28" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Ponto Interno</v>
       </c>
-      <c r="P28" s="35" t="s">
+      <c r="P28" s="34" t="s">
         <v>149</v>
       </c>
-      <c r="Q28" s="35" t="s">
-        <v>356</v>
+      <c r="Q28" s="34" t="s">
+        <v>355</v>
       </c>
       <c r="R28" s="21" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="S28" s="21" t="s">
         <v>9</v>
@@ -5810,45 +6045,45 @@
         <v>Pontos.do.Modelo</v>
       </c>
       <c r="W28" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X28" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X28" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-28</v>
       </c>
       <c r="Y28" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="Z28" s="60" t="s">
-        <v>214</v>
+      <c r="Z28" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA28" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="AB28" s="21" t="s">
-        <v>214</v>
+      <c r="AB28" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC28" s="21" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="50">
+      <c r="A29" s="46">
         <v>29</v>
       </c>
-      <c r="B29" s="55" t="s">
+      <c r="B29" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C29" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C29" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D29" s="55" t="s">
-        <v>271</v>
-      </c>
-      <c r="E29" s="44" t="s">
+      <c r="D29" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="E29" s="42" t="s">
         <v>203</v>
       </c>
-      <c r="F29" s="44" t="s">
+      <c r="F29" s="42" t="s">
         <v>150</v>
       </c>
       <c r="G29" s="6" t="s">
@@ -5866,30 +6101,30 @@
       <c r="K29" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L29" s="57" t="str">
+      <c r="L29" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M29" s="57" t="str">
+      <c r="M29" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N29" s="57" t="str">
+      <c r="N29" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Pontos do Modelo</v>
       </c>
-      <c r="O29" s="57" t="str">
+      <c r="O29" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Ponto Perimetral</v>
       </c>
-      <c r="P29" s="35" t="s">
+      <c r="P29" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="Q29" s="35" t="s">
-        <v>357</v>
+      <c r="Q29" s="34" t="s">
+        <v>356</v>
       </c>
       <c r="R29" s="21" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S29" s="21" t="s">
         <v>9</v>
@@ -5907,45 +6142,45 @@
         <v>Pontos.do.Modelo</v>
       </c>
       <c r="W29" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X29" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X29" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-29</v>
       </c>
       <c r="Y29" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="Z29" s="60" t="s">
-        <v>214</v>
+      <c r="Z29" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA29" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="AB29" s="21" t="s">
-        <v>214</v>
+      <c r="AB29" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC29" s="21" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="50">
+      <c r="A30" s="46">
         <v>30</v>
       </c>
-      <c r="B30" s="55" t="s">
+      <c r="B30" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C30" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C30" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D30" s="55" t="s">
-        <v>271</v>
-      </c>
-      <c r="E30" s="44" t="s">
+      <c r="D30" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="E30" s="42" t="s">
         <v>203</v>
       </c>
-      <c r="F30" s="44" t="s">
+      <c r="F30" s="42" t="s">
         <v>210</v>
       </c>
       <c r="G30" s="6" t="s">
@@ -5963,30 +6198,30 @@
       <c r="K30" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L30" s="57" t="str">
+      <c r="L30" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M30" s="57" t="str">
+      <c r="M30" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N30" s="57" t="str">
+      <c r="N30" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Pontos do Modelo</v>
       </c>
-      <c r="O30" s="57" t="str">
+      <c r="O30" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Ponto Região</v>
       </c>
       <c r="P30" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="Q30" s="35" t="s">
+      <c r="Q30" s="34" t="s">
         <v>139</v>
       </c>
       <c r="R30" s="21" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="S30" s="21" t="s">
         <v>9</v>
@@ -6004,45 +6239,45 @@
         <v>Pontos.do.Modelo</v>
       </c>
       <c r="W30" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X30" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X30" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-30</v>
       </c>
       <c r="Y30" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="Z30" s="60" t="s">
-        <v>214</v>
+      <c r="Z30" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA30" s="21" t="s">
-        <v>375</v>
-      </c>
-      <c r="AB30" s="21" t="s">
-        <v>214</v>
+        <v>374</v>
+      </c>
+      <c r="AB30" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC30" s="21" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="50">
+      <c r="A31" s="46">
         <v>31</v>
       </c>
-      <c r="B31" s="55" t="s">
+      <c r="B31" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C31" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C31" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D31" s="55" t="s">
-        <v>271</v>
-      </c>
-      <c r="E31" s="44" t="s">
+      <c r="D31" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="E31" s="42" t="s">
         <v>203</v>
       </c>
-      <c r="F31" s="44" t="s">
+      <c r="F31" s="42" t="s">
         <v>211</v>
       </c>
       <c r="G31" s="6" t="s">
@@ -6060,30 +6295,30 @@
       <c r="K31" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L31" s="57" t="str">
+      <c r="L31" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M31" s="57" t="str">
+      <c r="M31" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N31" s="57" t="str">
+      <c r="N31" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Pontos do Modelo</v>
       </c>
-      <c r="O31" s="57" t="str">
+      <c r="O31" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Ponto Superfície</v>
       </c>
       <c r="P31" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="Q31" s="35" t="s">
-        <v>358</v>
+      <c r="Q31" s="34" t="s">
+        <v>357</v>
       </c>
       <c r="R31" s="21" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="S31" s="21" t="s">
         <v>9</v>
@@ -6101,46 +6336,46 @@
         <v>Pontos.do.Modelo</v>
       </c>
       <c r="W31" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X31" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X31" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-31</v>
       </c>
       <c r="Y31" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="Z31" s="60" t="s">
-        <v>214</v>
+      <c r="Z31" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA31" s="21" t="s">
-        <v>375</v>
-      </c>
-      <c r="AB31" s="21" t="s">
-        <v>214</v>
+        <v>374</v>
+      </c>
+      <c r="AB31" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC31" s="21" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="32" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="50">
+      <c r="A32" s="46">
         <v>32</v>
       </c>
-      <c r="B32" s="55" t="s">
+      <c r="B32" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C32" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C32" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D32" s="55" t="s">
-        <v>271</v>
-      </c>
-      <c r="E32" s="55" t="s">
+      <c r="D32" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="E32" s="51" t="s">
         <v>170</v>
       </c>
-      <c r="F32" s="44" t="s">
-        <v>215</v>
+      <c r="F32" s="42" t="s">
+        <v>214</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>9</v>
@@ -6157,30 +6392,30 @@
       <c r="K32" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L32" s="57" t="str">
+      <c r="L32" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M32" s="57" t="str">
+      <c r="M32" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N32" s="57" t="str">
+      <c r="N32" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Sondagens</v>
       </c>
-      <c r="O32" s="57" t="str">
+      <c r="O32" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Ponto Sondagem</v>
       </c>
       <c r="P32" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="Q32" s="35" t="s">
+      <c r="Q32" s="34" t="s">
         <v>96</v>
       </c>
       <c r="R32" s="21" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="S32" s="21" t="s">
         <v>9</v>
@@ -6198,46 +6433,46 @@
         <v>Sondagens</v>
       </c>
       <c r="W32" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X32" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X32" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-32</v>
       </c>
-      <c r="Y32" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z32" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA32" s="60" t="s">
+      <c r="Y32" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z32" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA32" s="56" t="s">
         <v>212</v>
       </c>
-      <c r="AB32" s="21" t="s">
-        <v>214</v>
+      <c r="AB32" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC32" s="21" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="50">
+      <c r="A33" s="46">
         <v>33</v>
       </c>
-      <c r="B33" s="55" t="s">
+      <c r="B33" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C33" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C33" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D33" s="55" t="s">
-        <v>271</v>
-      </c>
-      <c r="E33" s="55" t="s">
+      <c r="D33" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="E33" s="51" t="s">
         <v>170</v>
       </c>
-      <c r="F33" s="44" t="s">
-        <v>216</v>
+      <c r="F33" s="42" t="s">
+        <v>215</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>9</v>
@@ -6254,30 +6489,30 @@
       <c r="K33" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L33" s="57" t="str">
+      <c r="L33" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M33" s="57" t="str">
+      <c r="M33" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N33" s="57" t="str">
+      <c r="N33" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Sondagens</v>
       </c>
-      <c r="O33" s="57" t="str">
+      <c r="O33" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Ponto Sondagem Definido</v>
       </c>
       <c r="P33" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="Q33" s="35" t="s">
+      <c r="Q33" s="34" t="s">
         <v>121</v>
       </c>
       <c r="R33" s="21" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="S33" s="21" t="s">
         <v>9</v>
@@ -6295,45 +6530,45 @@
         <v>Sondagens</v>
       </c>
       <c r="W33" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X33" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X33" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-33</v>
       </c>
-      <c r="Y33" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z33" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA33" s="60" t="s">
+      <c r="Y33" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z33" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA33" s="56" t="s">
         <v>213</v>
       </c>
-      <c r="AB33" s="21" t="s">
-        <v>214</v>
+      <c r="AB33" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC33" s="21" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="34" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="50">
+      <c r="A34" s="46">
         <v>34</v>
       </c>
-      <c r="B34" s="55" t="s">
+      <c r="B34" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C34" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C34" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D34" s="55" t="s">
-        <v>271</v>
-      </c>
-      <c r="E34" s="44" t="s">
+      <c r="D34" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="E34" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="F34" s="44" t="s">
+      <c r="F34" s="42" t="s">
         <v>194</v>
       </c>
       <c r="G34" s="6" t="s">
@@ -6351,30 +6586,30 @@
       <c r="K34" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L34" s="57" t="str">
+      <c r="L34" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M34" s="57" t="str">
+      <c r="M34" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N34" s="57" t="str">
+      <c r="N34" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Topografia</v>
       </c>
-      <c r="O34" s="57" t="str">
+      <c r="O34" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Topografia Sólida</v>
       </c>
-      <c r="P34" s="35" t="s">
+      <c r="P34" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="Q34" s="35" t="s">
-        <v>359</v>
+      <c r="Q34" s="34" t="s">
+        <v>358</v>
       </c>
       <c r="R34" s="21" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="S34" s="21" t="s">
         <v>9</v>
@@ -6392,45 +6627,45 @@
         <v>Topografia</v>
       </c>
       <c r="W34" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X34" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X34" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-34</v>
       </c>
       <c r="Y34" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="Z34" s="60" t="s">
-        <v>214</v>
+      <c r="Z34" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA34" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="AB34" s="21" t="s">
-        <v>214</v>
+      <c r="AB34" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC34" s="21" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="50">
+      <c r="A35" s="46">
         <v>35</v>
       </c>
-      <c r="B35" s="55" t="s">
+      <c r="B35" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C35" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C35" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D35" s="55" t="s">
-        <v>271</v>
-      </c>
-      <c r="E35" s="44" t="s">
+      <c r="D35" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="E35" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="F35" s="44" t="s">
+      <c r="F35" s="42" t="s">
         <v>195</v>
       </c>
       <c r="G35" s="6" t="s">
@@ -6448,30 +6683,30 @@
       <c r="K35" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L35" s="57" t="str">
+      <c r="L35" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M35" s="57" t="str">
+      <c r="M35" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N35" s="57" t="str">
+      <c r="N35" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Topografia</v>
       </c>
-      <c r="O35" s="57" t="str">
+      <c r="O35" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Topografia Malha</v>
       </c>
-      <c r="P35" s="35" t="s">
+      <c r="P35" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="Q35" s="35" t="s">
-        <v>360</v>
+      <c r="Q35" s="34" t="s">
+        <v>359</v>
       </c>
       <c r="R35" s="21" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="S35" s="21" t="s">
         <v>9</v>
@@ -6489,45 +6724,45 @@
         <v>Topografia</v>
       </c>
       <c r="W35" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X35" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X35" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-35</v>
       </c>
       <c r="Y35" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="Z35" s="60" t="s">
-        <v>214</v>
+      <c r="Z35" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA35" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="AB35" s="21" t="s">
-        <v>214</v>
+      <c r="AB35" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC35" s="21" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="50">
+      <c r="A36" s="46">
         <v>36</v>
       </c>
-      <c r="B36" s="55" t="s">
+      <c r="B36" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C36" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C36" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D36" s="55" t="s">
-        <v>271</v>
-      </c>
-      <c r="E36" s="44" t="s">
+      <c r="D36" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="E36" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="F36" s="44" t="s">
+      <c r="F36" s="42" t="s">
         <v>196</v>
       </c>
       <c r="G36" s="6" t="s">
@@ -6545,30 +6780,30 @@
       <c r="K36" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L36" s="57" t="str">
+      <c r="L36" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M36" s="57" t="str">
+      <c r="M36" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N36" s="57" t="str">
+      <c r="N36" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Topografia</v>
       </c>
-      <c r="O36" s="57" t="str">
+      <c r="O36" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Topografia Sólida Núcleo</v>
       </c>
-      <c r="P36" s="35" t="s">
+      <c r="P36" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="Q36" s="35" t="s">
-        <v>361</v>
+      <c r="Q36" s="34" t="s">
+        <v>360</v>
       </c>
       <c r="R36" s="21" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="S36" s="21" t="s">
         <v>9</v>
@@ -6586,45 +6821,45 @@
         <v>Topografia</v>
       </c>
       <c r="W36" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X36" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X36" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-36</v>
       </c>
       <c r="Y36" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="Z36" s="60" t="s">
-        <v>214</v>
+      <c r="Z36" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA36" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="AB36" s="21" t="s">
-        <v>214</v>
+      <c r="AB36" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC36" s="21" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="37" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="50">
+      <c r="A37" s="46">
         <v>37</v>
       </c>
-      <c r="B37" s="55" t="s">
+      <c r="B37" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C37" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C37" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D37" s="55" t="s">
-        <v>271</v>
-      </c>
-      <c r="E37" s="44" t="s">
+      <c r="D37" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="E37" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="F37" s="44" t="s">
+      <c r="F37" s="42" t="s">
         <v>197</v>
       </c>
       <c r="G37" s="6" t="s">
@@ -6642,30 +6877,30 @@
       <c r="K37" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L37" s="57" t="str">
+      <c r="L37" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M37" s="57" t="str">
+      <c r="M37" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N37" s="57" t="str">
+      <c r="N37" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Topografia</v>
       </c>
-      <c r="O37" s="57" t="str">
+      <c r="O37" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Topografia Sólida Substrato</v>
       </c>
-      <c r="P37" s="35" t="s">
+      <c r="P37" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="Q37" s="35" t="s">
+      <c r="Q37" s="34" t="s">
         <v>156</v>
       </c>
       <c r="R37" s="21" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="S37" s="21" t="s">
         <v>9</v>
@@ -6683,45 +6918,45 @@
         <v>Topografia</v>
       </c>
       <c r="W37" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X37" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X37" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-37</v>
       </c>
       <c r="Y37" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="Z37" s="60" t="s">
-        <v>214</v>
+      <c r="Z37" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA37" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="AB37" s="21" t="s">
-        <v>214</v>
+      <c r="AB37" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC37" s="21" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="50">
+      <c r="A38" s="46">
         <v>38</v>
       </c>
-      <c r="B38" s="55" t="s">
+      <c r="B38" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C38" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C38" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D38" s="55" t="s">
-        <v>271</v>
-      </c>
-      <c r="E38" s="44" t="s">
+      <c r="D38" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="E38" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="F38" s="44" t="s">
+      <c r="F38" s="42" t="s">
         <v>199</v>
       </c>
       <c r="G38" s="6" t="s">
@@ -6739,30 +6974,30 @@
       <c r="K38" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L38" s="57" t="str">
+      <c r="L38" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M38" s="57" t="str">
+      <c r="M38" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N38" s="57" t="str">
+      <c r="N38" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Topografia</v>
       </c>
-      <c r="O38" s="57" t="str">
+      <c r="O38" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Topografia Sólida Membrana</v>
       </c>
-      <c r="P38" s="35" t="s">
+      <c r="P38" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="Q38" s="35" t="s">
+      <c r="Q38" s="34" t="s">
         <v>158</v>
       </c>
       <c r="R38" s="21" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="S38" s="21" t="s">
         <v>9</v>
@@ -6780,45 +7015,45 @@
         <v>Topografia</v>
       </c>
       <c r="W38" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X38" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X38" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-38</v>
       </c>
       <c r="Y38" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="Z38" s="60" t="s">
-        <v>214</v>
+      <c r="Z38" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA38" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="AB38" s="21" t="s">
-        <v>214</v>
+      <c r="AB38" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC38" s="21" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="50">
+      <c r="A39" s="46">
         <v>39</v>
       </c>
-      <c r="B39" s="55" t="s">
+      <c r="B39" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C39" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C39" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D39" s="55" t="s">
-        <v>271</v>
-      </c>
-      <c r="E39" s="44" t="s">
+      <c r="D39" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="E39" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="F39" s="44" t="s">
+      <c r="F39" s="42" t="s">
         <v>198</v>
       </c>
       <c r="G39" s="6" t="s">
@@ -6836,30 +7071,30 @@
       <c r="K39" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L39" s="57" t="str">
+      <c r="L39" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M39" s="57" t="str">
+      <c r="M39" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N39" s="57" t="str">
+      <c r="N39" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Topografia</v>
       </c>
-      <c r="O39" s="57" t="str">
+      <c r="O39" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Topografia Sólida Isolamento</v>
       </c>
-      <c r="P39" s="35" t="s">
+      <c r="P39" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="Q39" s="35" t="s">
+      <c r="Q39" s="34" t="s">
         <v>160</v>
       </c>
       <c r="R39" s="21" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="S39" s="21" t="s">
         <v>9</v>
@@ -6877,45 +7112,45 @@
         <v>Topografia</v>
       </c>
       <c r="W39" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X39" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X39" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-39</v>
       </c>
       <c r="Y39" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="Z39" s="60" t="s">
-        <v>214</v>
+      <c r="Z39" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA39" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="AB39" s="21" t="s">
-        <v>214</v>
+      <c r="AB39" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC39" s="21" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="40" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="50">
+      <c r="A40" s="46">
         <v>40</v>
       </c>
-      <c r="B40" s="55" t="s">
+      <c r="B40" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C40" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C40" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D40" s="55" t="s">
-        <v>271</v>
-      </c>
-      <c r="E40" s="44" t="s">
+      <c r="D40" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="E40" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="F40" s="44" t="s">
+      <c r="F40" s="42" t="s">
         <v>202</v>
       </c>
       <c r="G40" s="6" t="s">
@@ -6933,30 +7168,30 @@
       <c r="K40" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L40" s="57" t="str">
+      <c r="L40" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M40" s="57" t="str">
+      <c r="M40" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N40" s="57" t="str">
+      <c r="N40" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Topografia</v>
       </c>
-      <c r="O40" s="57" t="str">
+      <c r="O40" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Topografia Sólida Superfície</v>
       </c>
-      <c r="P40" s="35" t="s">
+      <c r="P40" s="34" t="s">
         <v>161</v>
       </c>
-      <c r="Q40" s="35" t="s">
+      <c r="Q40" s="34" t="s">
         <v>162</v>
       </c>
       <c r="R40" s="21" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="S40" s="21" t="s">
         <v>9</v>
@@ -6974,45 +7209,45 @@
         <v>Topografia</v>
       </c>
       <c r="W40" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X40" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X40" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-40</v>
       </c>
       <c r="Y40" s="21" t="s">
-        <v>376</v>
-      </c>
-      <c r="Z40" s="60" t="s">
-        <v>214</v>
+        <v>375</v>
+      </c>
+      <c r="Z40" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA40" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="AB40" s="21" t="s">
-        <v>214</v>
+      <c r="AB40" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC40" s="21" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="41" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="50">
+      <c r="A41" s="46">
         <v>41</v>
       </c>
-      <c r="B41" s="55" t="s">
+      <c r="B41" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C41" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C41" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D41" s="55" t="s">
-        <v>271</v>
-      </c>
-      <c r="E41" s="44" t="s">
+      <c r="D41" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="E41" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="F41" s="44" t="s">
+      <c r="F41" s="42" t="s">
         <v>200</v>
       </c>
       <c r="G41" s="6" t="s">
@@ -7030,30 +7265,30 @@
       <c r="K41" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L41" s="57" t="str">
+      <c r="L41" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M41" s="57" t="str">
+      <c r="M41" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N41" s="57" t="str">
+      <c r="N41" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Topografia</v>
       </c>
-      <c r="O41" s="57" t="str">
+      <c r="O41" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Topografia Sólida Agua</v>
       </c>
-      <c r="P41" s="35" t="s">
+      <c r="P41" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="Q41" s="35" t="s">
+      <c r="Q41" s="34" t="s">
         <v>191</v>
       </c>
       <c r="R41" s="21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="S41" s="21" t="s">
         <v>9</v>
@@ -7071,45 +7306,45 @@
         <v>Topografia</v>
       </c>
       <c r="W41" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X41" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X41" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-41</v>
       </c>
       <c r="Y41" s="21" t="s">
-        <v>376</v>
-      </c>
-      <c r="Z41" s="60" t="s">
-        <v>214</v>
+        <v>375</v>
+      </c>
+      <c r="Z41" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA41" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="AB41" s="21" t="s">
-        <v>214</v>
+      <c r="AB41" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC41" s="21" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="42" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="50">
+      <c r="A42" s="46">
         <v>42</v>
       </c>
-      <c r="B42" s="55" t="s">
+      <c r="B42" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C42" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C42" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D42" s="55" t="s">
-        <v>271</v>
-      </c>
-      <c r="E42" s="44" t="s">
+      <c r="D42" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="E42" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="F42" s="44" t="s">
+      <c r="F42" s="42" t="s">
         <v>201</v>
       </c>
       <c r="G42" s="6" t="s">
@@ -7127,30 +7362,30 @@
       <c r="K42" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L42" s="57" t="str">
+      <c r="L42" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M42" s="57" t="str">
+      <c r="M42" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Topografia</v>
       </c>
-      <c r="N42" s="57" t="str">
+      <c r="N42" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Topografia</v>
       </c>
-      <c r="O42" s="57" t="str">
+      <c r="O42" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Topografia Sólida Vazio</v>
       </c>
       <c r="P42" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="Q42" s="35" t="s">
-        <v>362</v>
+      <c r="Q42" s="34" t="s">
+        <v>361</v>
       </c>
       <c r="R42" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="S42" s="21" t="s">
         <v>9</v>
@@ -7168,45 +7403,45 @@
         <v>Topografia</v>
       </c>
       <c r="W42" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X42" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X42" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-42</v>
       </c>
-      <c r="Y42" s="60" t="s">
+      <c r="Y42" s="56" t="s">
         <v>147</v>
       </c>
-      <c r="Z42" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA42" s="60" t="s">
+      <c r="Z42" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA42" s="56" t="s">
         <v>193</v>
       </c>
-      <c r="AB42" s="21" t="s">
-        <v>214</v>
+      <c r="AB42" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC42" s="21" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="43" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="50">
+      <c r="A43" s="46">
         <v>43</v>
       </c>
-      <c r="B43" s="55" t="s">
+      <c r="B43" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C43" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C43" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D43" s="55" t="s">
+      <c r="D43" s="51" t="s">
         <v>181</v>
       </c>
-      <c r="E43" s="44" t="s">
+      <c r="E43" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="F43" s="44" t="s">
+      <c r="F43" s="42" t="s">
         <v>184</v>
       </c>
       <c r="G43" s="6" t="s">
@@ -7224,30 +7459,30 @@
       <c r="K43" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L43" s="57" t="str">
+      <c r="L43" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M43" s="57" t="str">
+      <c r="M43" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.Altimétricos</v>
       </c>
-      <c r="N43" s="57" t="str">
+      <c r="N43" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Curvas de Nível</v>
       </c>
-      <c r="O43" s="57" t="str">
+      <c r="O43" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Curva de 10</v>
       </c>
-      <c r="P43" s="35" t="s">
+      <c r="P43" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="Q43" s="35" t="s">
+      <c r="Q43" s="34" t="s">
         <v>165</v>
       </c>
       <c r="R43" s="21" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="S43" s="21" t="s">
         <v>9</v>
@@ -7265,45 +7500,45 @@
         <v>Curvas.de.Nível</v>
       </c>
       <c r="W43" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X43" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X43" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-43</v>
       </c>
       <c r="Y43" s="21" t="s">
-        <v>377</v>
-      </c>
-      <c r="Z43" s="60" t="s">
-        <v>214</v>
+        <v>376</v>
+      </c>
+      <c r="Z43" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA43" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="AB43" s="21" t="s">
-        <v>214</v>
+      <c r="AB43" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC43" s="21" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="44" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="50">
+      <c r="A44" s="46">
         <v>44</v>
       </c>
-      <c r="B44" s="55" t="s">
+      <c r="B44" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C44" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C44" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D44" s="55" t="s">
+      <c r="D44" s="51" t="s">
         <v>181</v>
       </c>
-      <c r="E44" s="44" t="s">
+      <c r="E44" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="F44" s="44" t="s">
+      <c r="F44" s="42" t="s">
         <v>185</v>
       </c>
       <c r="G44" s="6" t="s">
@@ -7321,30 +7556,30 @@
       <c r="K44" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L44" s="57" t="str">
+      <c r="L44" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M44" s="57" t="str">
+      <c r="M44" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.Altimétricos</v>
       </c>
-      <c r="N44" s="57" t="str">
+      <c r="N44" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Curvas de Nível</v>
       </c>
-      <c r="O44" s="57" t="str">
+      <c r="O44" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Curva de 05</v>
       </c>
-      <c r="P44" s="35" t="s">
+      <c r="P44" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="Q44" s="35" t="s">
+      <c r="Q44" s="34" t="s">
         <v>167</v>
       </c>
       <c r="R44" s="21" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="S44" s="21" t="s">
         <v>9</v>
@@ -7362,45 +7597,45 @@
         <v>Curvas.de.Nível</v>
       </c>
       <c r="W44" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X44" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X44" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-44</v>
       </c>
       <c r="Y44" s="21" t="s">
-        <v>377</v>
-      </c>
-      <c r="Z44" s="60" t="s">
-        <v>214</v>
+        <v>376</v>
+      </c>
+      <c r="Z44" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA44" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="AB44" s="21" t="s">
-        <v>214</v>
+      <c r="AB44" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC44" s="21" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="45" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="50">
+      <c r="A45" s="46">
         <v>45</v>
       </c>
-      <c r="B45" s="55" t="s">
+      <c r="B45" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C45" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C45" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D45" s="55" t="s">
+      <c r="D45" s="51" t="s">
         <v>181</v>
       </c>
-      <c r="E45" s="44" t="s">
+      <c r="E45" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="F45" s="44" t="s">
+      <c r="F45" s="42" t="s">
         <v>186</v>
       </c>
       <c r="G45" s="6" t="s">
@@ -7418,30 +7653,30 @@
       <c r="K45" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L45" s="57" t="str">
+      <c r="L45" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M45" s="57" t="str">
+      <c r="M45" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.Altimétricos</v>
       </c>
-      <c r="N45" s="57" t="str">
+      <c r="N45" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Curvas de Nível</v>
       </c>
-      <c r="O45" s="57" t="str">
+      <c r="O45" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Curva de 01</v>
       </c>
-      <c r="P45" s="35" t="s">
+      <c r="P45" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="Q45" s="35" t="s">
+      <c r="Q45" s="34" t="s">
         <v>169</v>
       </c>
       <c r="R45" s="21" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="S45" s="21" t="s">
         <v>9</v>
@@ -7459,45 +7694,45 @@
         <v>Curvas.de.Nível</v>
       </c>
       <c r="W45" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X45" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X45" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-45</v>
       </c>
       <c r="Y45" s="21" t="s">
-        <v>378</v>
-      </c>
-      <c r="Z45" s="60" t="s">
-        <v>214</v>
+        <v>377</v>
+      </c>
+      <c r="Z45" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA45" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="AB45" s="21" t="s">
-        <v>214</v>
+      <c r="AB45" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC45" s="21" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="50">
+      <c r="A46" s="46">
         <v>46</v>
       </c>
-      <c r="B46" s="55" t="s">
+      <c r="B46" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C46" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C46" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D46" s="55" t="s">
+      <c r="D46" s="51" t="s">
+        <v>271</v>
+      </c>
+      <c r="E46" s="51" t="s">
         <v>272</v>
       </c>
-      <c r="E46" s="55" t="s">
-        <v>273</v>
-      </c>
-      <c r="F46" s="55" t="s">
+      <c r="F46" s="51" t="s">
         <v>208</v>
       </c>
       <c r="G46" s="6" t="s">
@@ -7515,27 +7750,27 @@
       <c r="K46" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L46" s="57" t="str">
+      <c r="L46" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M46" s="57" t="str">
+      <c r="M46" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Loteamentos</v>
       </c>
-      <c r="N46" s="57" t="str">
+      <c r="N46" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Loteamento</v>
       </c>
-      <c r="O46" s="57" t="str">
+      <c r="O46" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Divisa</v>
       </c>
       <c r="P46" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="Q46" s="35" t="s">
-        <v>363</v>
+      <c r="Q46" s="34" t="s">
+        <v>362</v>
       </c>
       <c r="R46" s="21" t="s">
         <v>136</v>
@@ -7556,45 +7791,45 @@
         <v>Loteamento</v>
       </c>
       <c r="W46" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X46" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X46" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-46</v>
       </c>
       <c r="Y46" s="21" t="s">
         <v>204</v>
       </c>
-      <c r="Z46" s="60" t="s">
-        <v>214</v>
+      <c r="Z46" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA46" s="21" t="s">
-        <v>375</v>
-      </c>
-      <c r="AB46" s="21" t="s">
-        <v>214</v>
+        <v>374</v>
+      </c>
+      <c r="AB46" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC46" s="21" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="50">
+      <c r="A47" s="46">
         <v>47</v>
       </c>
-      <c r="B47" s="55" t="s">
+      <c r="B47" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C47" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C47" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D47" s="55" t="s">
+      <c r="D47" s="51" t="s">
+        <v>271</v>
+      </c>
+      <c r="E47" s="51" t="s">
         <v>272</v>
       </c>
-      <c r="E47" s="55" t="s">
-        <v>273</v>
-      </c>
-      <c r="F47" s="55" t="s">
+      <c r="F47" s="51" t="s">
         <v>209</v>
       </c>
       <c r="G47" s="6" t="s">
@@ -7612,30 +7847,30 @@
       <c r="K47" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L47" s="57" t="str">
+      <c r="L47" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M47" s="57" t="str">
+      <c r="M47" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.de.Loteamentos</v>
       </c>
-      <c r="N47" s="57" t="str">
+      <c r="N47" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Loteamento</v>
       </c>
-      <c r="O47" s="57" t="str">
+      <c r="O47" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Divisa Segmento</v>
       </c>
       <c r="P47" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="Q47" s="35" t="s">
-        <v>364</v>
+      <c r="Q47" s="34" t="s">
+        <v>363</v>
       </c>
       <c r="R47" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="S47" s="21" t="s">
         <v>9</v>
@@ -7653,46 +7888,46 @@
         <v>Loteamento</v>
       </c>
       <c r="W47" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X47" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X47" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-47</v>
       </c>
-      <c r="Y47" s="43" t="s">
+      <c r="Y47" s="41" t="s">
         <v>207</v>
       </c>
-      <c r="Z47" s="60" t="s">
-        <v>214</v>
+      <c r="Z47" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA47" s="21" t="s">
-        <v>375</v>
-      </c>
-      <c r="AB47" s="21" t="s">
-        <v>214</v>
+        <v>374</v>
+      </c>
+      <c r="AB47" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC47" s="21" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="48" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="50">
+      <c r="A48" s="46">
         <v>48</v>
       </c>
-      <c r="B48" s="55" t="s">
+      <c r="B48" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C48" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C48" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D48" s="55" t="s">
+      <c r="D48" s="51" t="s">
         <v>182</v>
       </c>
-      <c r="E48" s="55" t="s">
+      <c r="E48" s="51" t="s">
         <v>118</v>
       </c>
-      <c r="F48" s="56" t="s">
-        <v>274</v>
+      <c r="F48" s="52" t="s">
+        <v>273</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>9</v>
@@ -7709,30 +7944,30 @@
       <c r="K48" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L48" s="57" t="str">
+      <c r="L48" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M48" s="57" t="str">
+      <c r="M48" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.Paisagísticos</v>
       </c>
-      <c r="N48" s="57" t="str">
+      <c r="N48" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Paisagismo</v>
       </c>
-      <c r="O48" s="57" t="str">
+      <c r="O48" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Paisagístico</v>
       </c>
       <c r="P48" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="Q48" s="35" t="s">
-        <v>365</v>
+      <c r="Q48" s="34" t="s">
+        <v>364</v>
       </c>
       <c r="R48" s="21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="S48" s="21" t="s">
         <v>9</v>
@@ -7750,46 +7985,46 @@
         <v>Paisagismo</v>
       </c>
       <c r="W48" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X48" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X48" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-48</v>
       </c>
-      <c r="Y48" s="60" t="s">
+      <c r="Y48" s="56" t="s">
         <v>143</v>
       </c>
-      <c r="Z48" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA48" s="60" t="s">
+      <c r="Z48" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA48" s="56" t="s">
         <v>171</v>
       </c>
-      <c r="AB48" s="21" t="s">
-        <v>214</v>
+      <c r="AB48" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC48" s="21" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="49" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="50">
+      <c r="A49" s="46">
         <v>49</v>
       </c>
-      <c r="B49" s="55" t="s">
+      <c r="B49" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C49" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C49" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D49" s="55" t="s">
+      <c r="D49" s="51" t="s">
         <v>182</v>
       </c>
-      <c r="E49" s="55" t="s">
+      <c r="E49" s="51" t="s">
         <v>118</v>
       </c>
-      <c r="F49" s="56" t="s">
-        <v>280</v>
+      <c r="F49" s="52" t="s">
+        <v>279</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>9</v>
@@ -7806,30 +8041,30 @@
       <c r="K49" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L49" s="57" t="str">
+      <c r="L49" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M49" s="57" t="str">
+      <c r="M49" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.Paisagísticos</v>
       </c>
-      <c r="N49" s="57" t="str">
+      <c r="N49" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Paisagismo</v>
       </c>
-      <c r="O49" s="57" t="str">
+      <c r="O49" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Pavimentação</v>
       </c>
       <c r="P49" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="Q49" s="35" t="s">
+      <c r="Q49" s="34" t="s">
         <v>123</v>
       </c>
       <c r="R49" s="21" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="S49" s="21" t="s">
         <v>9</v>
@@ -7847,45 +8082,45 @@
         <v>Paisagismo</v>
       </c>
       <c r="W49" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X49" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X49" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-49</v>
       </c>
-      <c r="Y49" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z49" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA49" s="60" t="s">
+      <c r="Y49" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z49" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA49" s="56" t="s">
         <v>187</v>
       </c>
-      <c r="AB49" s="21" t="s">
-        <v>214</v>
+      <c r="AB49" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC49" s="21" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="50" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="50">
+      <c r="A50" s="46">
         <v>50</v>
       </c>
-      <c r="B50" s="55" t="s">
+      <c r="B50" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C50" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C50" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D50" s="55" t="s">
+      <c r="D50" s="51" t="s">
         <v>182</v>
       </c>
-      <c r="E50" s="55" t="s">
+      <c r="E50" s="51" t="s">
         <v>118</v>
       </c>
-      <c r="F50" s="55" t="s">
+      <c r="F50" s="51" t="s">
         <v>80</v>
       </c>
       <c r="G50" s="6" t="s">
@@ -7903,30 +8138,30 @@
       <c r="K50" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L50" s="57" t="str">
+      <c r="L50" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M50" s="57" t="str">
+      <c r="M50" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.Paisagísticos</v>
       </c>
-      <c r="N50" s="57" t="str">
+      <c r="N50" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Paisagismo</v>
       </c>
-      <c r="O50" s="57" t="str">
+      <c r="O50" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Estacionamento</v>
       </c>
       <c r="P50" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="Q50" s="35" t="s">
-        <v>366</v>
+      <c r="Q50" s="34" t="s">
+        <v>365</v>
       </c>
       <c r="R50" s="21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="S50" s="21" t="s">
         <v>9</v>
@@ -7944,45 +8179,45 @@
         <v>Paisagismo</v>
       </c>
       <c r="W50" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X50" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X50" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-50</v>
       </c>
       <c r="Y50" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="Z50" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA50" s="60" t="s">
-        <v>275</v>
-      </c>
-      <c r="AB50" s="21" t="s">
-        <v>214</v>
+      <c r="Z50" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA50" s="56" t="s">
+        <v>274</v>
+      </c>
+      <c r="AB50" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC50" s="21" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="51" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="50">
+      <c r="A51" s="46">
         <v>51</v>
       </c>
-      <c r="B51" s="55" t="s">
+      <c r="B51" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="C51" s="55" t="s">
         <v>373</v>
       </c>
-      <c r="C51" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D51" s="55" t="s">
+      <c r="D51" s="51" t="s">
         <v>182</v>
       </c>
-      <c r="E51" s="55" t="s">
+      <c r="E51" s="51" t="s">
         <v>118</v>
       </c>
-      <c r="F51" s="56" t="s">
+      <c r="F51" s="52" t="s">
         <v>145</v>
       </c>
       <c r="G51" s="6" t="s">
@@ -8000,27 +8235,27 @@
       <c r="K51" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L51" s="57" t="str">
+      <c r="L51" s="53" t="str">
         <f t="shared" si="6"/>
         <v>GeoTécnicos</v>
       </c>
-      <c r="M51" s="57" t="str">
+      <c r="M51" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Elementos.Paisagísticos</v>
       </c>
-      <c r="N51" s="57" t="str">
+      <c r="N51" s="53" t="str">
         <f t="shared" si="8"/>
         <v>Paisagismo</v>
       </c>
-      <c r="O51" s="57" t="str">
+      <c r="O51" s="53" t="str">
         <f t="shared" si="9"/>
         <v>Vegetação</v>
       </c>
       <c r="P51" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="Q51" s="35" t="s">
-        <v>367</v>
+      <c r="Q51" s="34" t="s">
+        <v>366</v>
       </c>
       <c r="R51" s="21" t="s">
         <v>125</v>
@@ -8041,148 +8276,345 @@
         <v>Paisagismo</v>
       </c>
       <c r="W51" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="X51" s="58" t="str">
+        <v>390</v>
+      </c>
+      <c r="X51" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-51</v>
       </c>
-      <c r="Y51" s="60" t="s">
+      <c r="Y51" s="56" t="s">
         <v>144</v>
       </c>
-      <c r="Z51" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA51" s="60" t="s">
+      <c r="Z51" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA51" s="56" t="s">
         <v>188</v>
       </c>
-      <c r="AB51" s="21" t="s">
-        <v>214</v>
+      <c r="AB51" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC51" s="21" t="s">
-        <v>278</v>
+        <v>277</v>
+      </c>
+    </row>
+    <row r="52" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="46">
+        <v>52</v>
+      </c>
+      <c r="B52" s="58" t="s">
+        <v>382</v>
+      </c>
+      <c r="C52" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="D52" s="59" t="s">
+        <v>417</v>
+      </c>
+      <c r="E52" s="59" t="s">
+        <v>416</v>
+      </c>
+      <c r="F52" s="59" t="s">
+        <v>415</v>
+      </c>
+      <c r="G52" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H52" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I52" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J52" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K52" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L52" s="61" t="str">
+        <f t="shared" ref="L52" si="13">SUBSTITUTE(CONCATENATE("", C52), ".", " ")</f>
+        <v>De Geotécnica</v>
+      </c>
+      <c r="M52" s="61" t="str">
+        <f t="shared" ref="M52" si="14">SUBSTITUTE(CONCATENATE("", D52), ".", " ")</f>
+        <v>Geotécnico</v>
+      </c>
+      <c r="N52" s="61" t="str">
+        <f t="shared" ref="N52" si="15">SUBSTITUTE(CONCATENATE("", E52), ".", " ")</f>
+        <v>Solos</v>
+      </c>
+      <c r="O52" s="61" t="str">
+        <f t="shared" ref="O52:P52" si="16">SUBSTITUTE(CONCATENATE("", F52), ".", " ")</f>
+        <v>Terreno</v>
+      </c>
+      <c r="P52" s="61" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q52" s="61" t="s">
+        <v>418</v>
+      </c>
+      <c r="R52" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="S52" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="T52" s="18" t="str">
+        <f t="shared" ref="T52" si="17">SUBSTITUTE(C52, ".", " ")</f>
+        <v>De Geotécnica</v>
+      </c>
+      <c r="U52" s="18" t="str">
+        <f t="shared" ref="U52" si="18">SUBSTITUTE(D52, ".", " ")</f>
+        <v>Geotécnico</v>
+      </c>
+      <c r="V52" s="21" t="str">
+        <f t="shared" ref="V52" si="19">SUBSTITUTE(E52, ".", " ")</f>
+        <v>Solos</v>
+      </c>
+      <c r="W52" s="21" t="s">
+        <v>390</v>
+      </c>
+      <c r="X52" s="54" t="str">
+        <f t="shared" ref="X52" si="20">CONCATENATE("Key-GEO-",A52)</f>
+        <v>Key-GEO-52</v>
+      </c>
+      <c r="Y52" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z52" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA52" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB52" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC52" s="62" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="46">
+        <v>53</v>
+      </c>
+      <c r="B53" s="58" t="s">
+        <v>382</v>
+      </c>
+      <c r="C53" s="59" t="s">
+        <v>383</v>
+      </c>
+      <c r="D53" s="59" t="s">
+        <v>384</v>
+      </c>
+      <c r="E53" s="59" t="s">
+        <v>385</v>
+      </c>
+      <c r="F53" s="59" t="s">
+        <v>386</v>
+      </c>
+      <c r="G53" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H53" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I53" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J53" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K53" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L53" s="61" t="str">
+        <f t="shared" ref="L53:O53" si="21">SUBSTITUTE(CONCATENATE("", C53), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M53" s="61" t="str">
+        <f t="shared" si="21"/>
+        <v>Métodos</v>
+      </c>
+      <c r="N53" s="61" t="str">
+        <f t="shared" si="21"/>
+        <v>Macros</v>
+      </c>
+      <c r="O53" s="61" t="str">
+        <f t="shared" si="21"/>
+        <v>API Revit</v>
+      </c>
+      <c r="P53" s="18" t="s">
+        <v>387</v>
+      </c>
+      <c r="Q53" s="18" t="s">
+        <v>388</v>
+      </c>
+      <c r="R53" s="18" t="s">
+        <v>389</v>
+      </c>
+      <c r="S53" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="T53" s="18" t="str">
+        <f t="shared" ref="T53:V53" si="22">SUBSTITUTE(C53, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U53" s="18" t="str">
+        <f t="shared" si="22"/>
+        <v>Métodos</v>
+      </c>
+      <c r="V53" s="21" t="str">
+        <f t="shared" si="22"/>
+        <v>Macros</v>
+      </c>
+      <c r="W53" s="21" t="s">
+        <v>390</v>
+      </c>
+      <c r="X53" s="54" t="str">
+        <f t="shared" si="5"/>
+        <v>Key-GEO-53</v>
+      </c>
+      <c r="Y53" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z53" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA53" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB53" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC53" s="62" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC804">
-    <sortCondition ref="E1:E804"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC805">
+    <sortCondition ref="E1:E805"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B51 AB52:XFD1048576 AB1:XFD1">
-    <cfRule type="cellIs" dxfId="63" priority="8" operator="equal">
+  <conditionalFormatting sqref="A2:B53">
+    <cfRule type="cellIs" dxfId="71" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:Q1 C2:E2 P2 AD2:XFD2 D3:E8 C3:C51 D9:D27 S1:X1 A52:X1048576">
-    <cfRule type="cellIs" dxfId="62" priority="254" operator="equal">
+  <conditionalFormatting sqref="A54:X1048576 A1:Q1 S1:X1 C2:E2 P2 AD2:XFD2 D3:E8 C3:C51 D9:D27">
+    <cfRule type="cellIs" dxfId="70" priority="258" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="61" priority="54"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F2:F27">
-    <cfRule type="cellIs" dxfId="60" priority="60" operator="equal">
+    <cfRule type="duplicateValues" dxfId="69" priority="1046"/>
+    <cfRule type="cellIs" dxfId="68" priority="64" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="59" priority="1042"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28:F45 Q2:Q51 P28:P29 AD28:XFD29 P34:P41 AD34:XFD41 P43:P45 AD43:XFD45">
-    <cfRule type="cellIs" dxfId="58" priority="121" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="125" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28:F45">
-    <cfRule type="duplicateValues" dxfId="57" priority="1021"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="1023"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="1024"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="1028"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="1027"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="1025"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F46:F47">
-    <cfRule type="duplicateValues" dxfId="54" priority="991"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="995"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F51">
-    <cfRule type="duplicateValues" dxfId="53" priority="1027"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="1031"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F52:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="52" priority="255"/>
+  <conditionalFormatting sqref="F52:F53">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F52:F1048576">
-    <cfRule type="duplicateValues" dxfId="51" priority="247"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="756"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="764"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="771"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="784"/>
+  <conditionalFormatting sqref="F54:F1048576 F1">
+    <cfRule type="duplicateValues" dxfId="60" priority="259"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X52:X1048576 X1">
-    <cfRule type="duplicateValues" dxfId="46" priority="583"/>
+  <conditionalFormatting sqref="F54:F1048576 F1:F51">
+    <cfRule type="duplicateValues" dxfId="59" priority="58"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y50">
-    <cfRule type="duplicateValues" dxfId="45" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="53"/>
+  <conditionalFormatting sqref="F54:F1048576">
+    <cfRule type="duplicateValues" dxfId="58" priority="788"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="775"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="768"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="760"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="251"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2">
-    <cfRule type="cellIs" dxfId="41" priority="84" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-    <cfRule type="duplicateValues" dxfId="40" priority="85"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA3">
-    <cfRule type="duplicateValues" dxfId="39" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="83"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA3:AA8 AA17:AA27 AA10:AA14">
-    <cfRule type="duplicateValues" dxfId="35" priority="1039"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA4:AA8 AA19:AA27 AA10:AA14">
-    <cfRule type="duplicateValues" dxfId="34" priority="1036"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA4:AA8 AA19:AA27">
-    <cfRule type="duplicateValues" dxfId="33" priority="87"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA9">
-    <cfRule type="duplicateValues" dxfId="32" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA10:AA14">
-    <cfRule type="duplicateValues" dxfId="27" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA15:AA16">
-    <cfRule type="duplicateValues" dxfId="23" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA17:AA18">
-    <cfRule type="duplicateValues" dxfId="15" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="49"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA19:AA27">
-    <cfRule type="duplicateValues" dxfId="10" priority="86"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R51">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+  <conditionalFormatting sqref="R1:R53">
+    <cfRule type="cellIs" dxfId="53" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+  <conditionalFormatting sqref="X54:X1048576 X1">
+    <cfRule type="duplicateValues" dxfId="52" priority="587"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y50">
+    <cfRule type="duplicateValues" dxfId="51" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2">
+    <cfRule type="duplicateValues" dxfId="47" priority="89"/>
+    <cfRule type="cellIs" dxfId="46" priority="88" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA3">
+    <cfRule type="duplicateValues" dxfId="45" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="84"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA3:AA8 AA17:AA27 AA10:AA14">
+    <cfRule type="duplicateValues" dxfId="41" priority="1043"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA4:AA8 AA19:AA27 AA10:AA14">
+    <cfRule type="duplicateValues" dxfId="40" priority="1040"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA4:AA8 AA19:AA27">
+    <cfRule type="duplicateValues" dxfId="39" priority="91"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA9">
+    <cfRule type="duplicateValues" dxfId="38" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA10:AA14">
+    <cfRule type="duplicateValues" dxfId="33" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA15:AA16">
+    <cfRule type="duplicateValues" dxfId="29" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA17:AA18">
+    <cfRule type="duplicateValues" dxfId="21" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA19:AA27">
+    <cfRule type="duplicateValues" dxfId="16" priority="90"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB1:XFD1 AB54:XFD1048576">
+    <cfRule type="cellIs" dxfId="15" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8334,7 +8766,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8406,15 +8838,15 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="13" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -8422,28 +8854,30 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A426B82-2E19-47C6-9DDF-914E7B26E6D0}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:AG7"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="33" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" style="32" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6" style="32" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.28515625" style="32" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.85546875" style="32" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.28515625" style="34" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" style="34" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" style="34" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28" style="34" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.28515625" style="34" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="34" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" style="34" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" style="34" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" style="34" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" style="33" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.28515625" style="32"/>
+    <col min="1" max="1" width="2.5703125" style="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" style="31" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" style="31" customWidth="1"/>
+    <col min="4" max="5" width="3.140625" style="31" customWidth="1"/>
+    <col min="6" max="6" width="3.140625" style="33" customWidth="1"/>
+    <col min="7" max="7" width="3.140625" style="31" customWidth="1"/>
+    <col min="8" max="8" width="3.5703125" style="33" customWidth="1"/>
+    <col min="9" max="9" width="6.85546875" style="33" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" style="33" customWidth="1"/>
+    <col min="11" max="11" width="37.85546875" style="33" customWidth="1"/>
+    <col min="12" max="12" width="3.42578125" style="31" customWidth="1"/>
+    <col min="13" max="13" width="3.85546875" style="31" customWidth="1"/>
+    <col min="14" max="14" width="5.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" style="31" customWidth="1"/>
+    <col min="16" max="16" width="6.42578125" style="31" customWidth="1"/>
+    <col min="17" max="17" width="7.7109375" style="31" customWidth="1"/>
+    <col min="18" max="33" width="3.85546875" style="31" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.28515625" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="28" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" s="28" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>10</v>
       </c>
@@ -8453,16 +8887,18 @@
       <c r="C1" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="40" t="s">
         <v>44</v>
       </c>
       <c r="F1" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="G1" s="27"/>
+      <c r="G1" s="40" t="s">
+        <v>44</v>
+      </c>
       <c r="H1" s="27" t="s">
         <v>72</v>
       </c>
@@ -8475,79 +8911,721 @@
       <c r="K1" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="27" t="s">
+      <c r="L1" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="M1" s="27" t="s">
+      <c r="M1" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="N1" s="27" t="s">
+      <c r="N1" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="O1" s="26" t="s">
+      <c r="O1" s="40" t="s">
         <v>44</v>
       </c>
+      <c r="P1" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q1" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="R1" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="S1" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="T1" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="U1" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="V1" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="W1" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="X1" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y1" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z1" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA1" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB1" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC1" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD1" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE1" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF1" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG1" s="40" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="2" spans="1:15" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31">
+    <row r="2" spans="1:33" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="30">
         <v>1</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="43" t="s">
+        <v>370</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="D2" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="38" t="s">
+        <v>281</v>
+      </c>
+      <c r="I2" s="45" t="s">
         <v>371</v>
       </c>
-      <c r="C2" s="59" t="s">
-        <v>374</v>
-      </c>
-      <c r="D2" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="39" t="s">
-        <v>282</v>
-      </c>
-      <c r="G2" s="48" t="s">
-        <v>372</v>
-      </c>
-      <c r="H2" s="46" t="s">
+      <c r="J2" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="I2" s="40" t="s">
-        <v>379</v>
-      </c>
-      <c r="J2" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="N2" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="O2" s="30" t="s">
+      <c r="K2" s="39" t="s">
+        <v>378</v>
+      </c>
+      <c r="L2" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="P2" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q2" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="R2" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="T2" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="V2" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="X2" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y2" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z2" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA2" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB2" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC2" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD2" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE2" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF2" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG2" s="73" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="30">
+        <v>2</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>391</v>
+      </c>
+      <c r="C3" s="59" t="s">
+        <v>386</v>
+      </c>
+      <c r="D3" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="K3" s="67" t="s">
+        <v>392</v>
+      </c>
+      <c r="L3" s="69" t="s">
+        <v>393</v>
+      </c>
+      <c r="M3" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="N3" s="69" t="s">
+        <v>395</v>
+      </c>
+      <c r="O3" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="P3" s="71" t="str">
+        <f t="shared" ref="P3:P7" si="0">IF(Q3="null", "null", "método.revit")</f>
+        <v>método.revit</v>
+      </c>
+      <c r="Q3" s="72" t="s">
+        <v>397</v>
+      </c>
+      <c r="R3" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="S3" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="T3" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="U3" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="V3" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="W3" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="X3" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y3" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z3" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA3" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB3" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC3" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD3" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE3" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF3" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG3" s="73" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="30">
+        <v>3</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>398</v>
+      </c>
+      <c r="C4" s="59" t="s">
+        <v>386</v>
+      </c>
+      <c r="D4" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="K4" s="67" t="s">
+        <v>399</v>
+      </c>
+      <c r="L4" s="69" t="s">
+        <v>393</v>
+      </c>
+      <c r="M4" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="N4" s="69" t="s">
+        <v>395</v>
+      </c>
+      <c r="O4" s="45" t="s">
+        <v>400</v>
+      </c>
+      <c r="P4" s="71" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q4" s="72" t="s">
+        <v>401</v>
+      </c>
+      <c r="R4" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="S4" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="T4" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="U4" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="V4" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="W4" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="X4" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y4" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z4" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA4" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB4" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC4" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD4" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE4" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF4" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG4" s="73" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="30">
+        <v>4</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="C5" s="59" t="s">
+        <v>386</v>
+      </c>
+      <c r="D5" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="K5" s="67" t="s">
+        <v>403</v>
+      </c>
+      <c r="L5" s="69" t="s">
+        <v>393</v>
+      </c>
+      <c r="M5" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="N5" s="69" t="s">
+        <v>395</v>
+      </c>
+      <c r="O5" s="45" t="s">
+        <v>404</v>
+      </c>
+      <c r="P5" s="71" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q5" s="72" t="s">
+        <v>405</v>
+      </c>
+      <c r="R5" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="S5" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="T5" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="U5" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="V5" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="W5" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="X5" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y5" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z5" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA5" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB5" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC5" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD5" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE5" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF5" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG5" s="73" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="30">
+        <v>5</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>406</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>386</v>
+      </c>
+      <c r="D6" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="K6" s="67" t="s">
+        <v>407</v>
+      </c>
+      <c r="L6" s="69" t="s">
+        <v>393</v>
+      </c>
+      <c r="M6" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="N6" s="69" t="s">
+        <v>395</v>
+      </c>
+      <c r="O6" s="45" t="s">
+        <v>408</v>
+      </c>
+      <c r="P6" s="71" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q6" s="72" t="s">
+        <v>409</v>
+      </c>
+      <c r="R6" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="S6" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="T6" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="U6" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="V6" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="W6" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="X6" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y6" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z6" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA6" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB6" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC6" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD6" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE6" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF6" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG6" s="73" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="30">
+        <v>6</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>410</v>
+      </c>
+      <c r="C7" s="59" t="s">
+        <v>386</v>
+      </c>
+      <c r="D7" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="K7" s="67" t="s">
+        <v>411</v>
+      </c>
+      <c r="L7" s="69" t="s">
+        <v>393</v>
+      </c>
+      <c r="M7" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="N7" s="69" t="s">
+        <v>395</v>
+      </c>
+      <c r="O7" s="45" t="s">
+        <v>412</v>
+      </c>
+      <c r="P7" s="71" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q7" s="72" t="s">
+        <v>413</v>
+      </c>
+      <c r="R7" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="S7" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="T7" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="U7" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="V7" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="W7" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="X7" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y7" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z7" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA7" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB7" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC7" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD7" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE7" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF7" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG7" s="73" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:XFD1 A2:B2 A3:XFD1048576 D2:XFD2">
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
+  <conditionalFormatting sqref="A1:XFD1 A2:B2 A8:XFD1048576 H2:O2 AH2:XFD2 A3:A7">
+    <cfRule type="cellIs" dxfId="10" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="1020"/>
+  <conditionalFormatting sqref="B1:B2 B8:B1048576">
+    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1030"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:B7">
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="11" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:G7">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:I7">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:Q2">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:AG7">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/EST/Ontologia_Geotecnica.xlsx
+++ b/Versão5/EST/Ontologia_Geotecnica.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE67B01E-AAE7-439A-9AD4-336D925E0E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC4145B-11B8-4E4F-9DB3-A598840BFAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -1900,17 +1900,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="72">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="71">
     <dxf>
       <font>
         <b val="0"/>
@@ -3022,15 +3012,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="23" customWidth="1"/>
-    <col min="2" max="2" width="39.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="37" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="23"/>
+    <col min="1" max="1" width="9.3046875" style="23" customWidth="1"/>
+    <col min="2" max="2" width="39.15234375" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="37" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="10" t="s">
         <v>43</v>
       </c>
@@ -3041,7 +3031,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="11" t="s">
         <v>45</v>
       </c>
@@ -3052,7 +3042,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="11" t="s">
         <v>47</v>
       </c>
@@ -3063,7 +3053,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="12" t="s">
         <v>48</v>
       </c>
@@ -3074,7 +3064,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="12" t="s">
         <v>49</v>
       </c>
@@ -3086,7 +3076,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>50</v>
       </c>
@@ -3098,7 +3088,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>51</v>
       </c>
@@ -3109,7 +3099,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
         <v>53</v>
       </c>
@@ -3120,7 +3110,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="12" t="s">
         <v>54</v>
       </c>
@@ -3131,7 +3121,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="12" t="s">
         <v>56</v>
       </c>
@@ -3142,7 +3132,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="12" t="s">
         <v>58</v>
       </c>
@@ -3153,7 +3143,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="12" t="s">
         <v>59</v>
       </c>
@@ -3164,7 +3154,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="12" t="s">
         <v>60</v>
       </c>
@@ -3175,7 +3165,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="12" t="s">
         <v>61</v>
       </c>
@@ -3186,7 +3176,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="12" t="s">
         <v>62</v>
       </c>
@@ -3197,7 +3187,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="12" t="s">
         <v>63</v>
       </c>
@@ -3208,7 +3198,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="12" t="s">
         <v>64</v>
       </c>
@@ -3219,19 +3209,19 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="12" t="s">
         <v>65</v>
       </c>
       <c r="B18" s="25">
         <f ca="1">NOW()</f>
-        <v>46260.316143055556</v>
+        <v>46264.567591550927</v>
       </c>
       <c r="C18" s="36" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="12" t="s">
         <v>93</v>
       </c>
@@ -3242,7 +3232,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="12" t="s">
         <v>90</v>
       </c>
@@ -3254,7 +3244,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="12" t="s">
         <v>92</v>
       </c>
@@ -3266,7 +3256,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="12" t="s">
         <v>66</v>
       </c>
@@ -3277,7 +3267,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="12" t="s">
         <v>67</v>
       </c>
@@ -3288,7 +3278,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="12" t="s">
         <v>68</v>
       </c>
@@ -3299,7 +3289,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="12" t="s">
         <v>69</v>
       </c>
@@ -3310,7 +3300,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="12" t="s">
         <v>84</v>
       </c>
@@ -3330,36 +3320,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A56445-53D9-475A-B2C6-D376FC6516D5}">
   <dimension ref="A1:AC53"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" customWidth="1"/>
+    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.69140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.69140625" customWidth="1"/>
+    <col min="5" max="5" width="9.3828125" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="11" width="8" style="57" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="35.140625" customWidth="1"/>
-    <col min="17" max="17" width="35.85546875" customWidth="1"/>
-    <col min="18" max="18" width="38.140625" customWidth="1"/>
+    <col min="12" max="12" width="7.69140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.84375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.84375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.3828125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="35.15234375" customWidth="1"/>
+    <col min="17" max="17" width="35.84375" customWidth="1"/>
+    <col min="18" max="18" width="38.15234375" customWidth="1"/>
     <col min="19" max="19" width="3" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.69140625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13" customWidth="1"/>
-    <col min="22" max="22" width="7.85546875" customWidth="1"/>
-    <col min="23" max="23" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.7109375" customWidth="1"/>
-    <col min="25" max="25" width="32.140625" customWidth="1"/>
-    <col min="26" max="26" width="7.7109375" customWidth="1"/>
-    <col min="27" max="27" width="20.5703125" customWidth="1"/>
-    <col min="28" max="28" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.28515625" customWidth="1"/>
+    <col min="22" max="22" width="7.84375" customWidth="1"/>
+    <col min="23" max="23" width="6.69140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.69140625" customWidth="1"/>
+    <col min="25" max="25" width="32.15234375" customWidth="1"/>
+    <col min="26" max="26" width="7.69140625" customWidth="1"/>
+    <col min="27" max="27" width="20.53515625" customWidth="1"/>
+    <col min="28" max="28" width="6.84375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.3046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="36.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="22">
         <v>1</v>
       </c>
@@ -3448,7 +3438,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="46">
         <v>2</v>
       </c>
@@ -3545,7 +3535,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="46">
         <v>3</v>
       </c>
@@ -3642,7 +3632,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="46">
         <v>4</v>
       </c>
@@ -3739,7 +3729,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="46">
         <v>5</v>
       </c>
@@ -3836,7 +3826,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="46">
         <v>6</v>
       </c>
@@ -3933,7 +3923,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="46">
         <v>7</v>
       </c>
@@ -4030,7 +4020,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="46">
         <v>8</v>
       </c>
@@ -4127,7 +4117,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="46">
         <v>9</v>
       </c>
@@ -4224,7 +4214,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="46">
         <v>10</v>
       </c>
@@ -4321,7 +4311,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="46">
         <v>11</v>
       </c>
@@ -4418,7 +4408,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="46">
         <v>12</v>
       </c>
@@ -4515,7 +4505,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="46">
         <v>13</v>
       </c>
@@ -4612,7 +4602,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="46">
         <v>14</v>
       </c>
@@ -4709,7 +4699,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="46">
         <v>15</v>
       </c>
@@ -4806,7 +4796,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="46">
         <v>16</v>
       </c>
@@ -4903,7 +4893,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="46">
         <v>17</v>
       </c>
@@ -5000,7 +4990,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="46">
         <v>18</v>
       </c>
@@ -5097,7 +5087,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="46">
         <v>19</v>
       </c>
@@ -5194,7 +5184,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="46">
         <v>20</v>
       </c>
@@ -5291,7 +5281,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="46">
         <v>21</v>
       </c>
@@ -5388,7 +5378,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="46">
         <v>22</v>
       </c>
@@ -5485,7 +5475,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="46">
         <v>23</v>
       </c>
@@ -5582,7 +5572,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="46">
         <v>24</v>
       </c>
@@ -5679,7 +5669,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="46">
         <v>25</v>
       </c>
@@ -5776,7 +5766,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="46">
         <v>26</v>
       </c>
@@ -5873,7 +5863,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="46">
         <v>27</v>
       </c>
@@ -5970,7 +5960,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="46">
         <v>28</v>
       </c>
@@ -6067,7 +6057,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="46">
         <v>29</v>
       </c>
@@ -6164,7 +6154,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="46">
         <v>30</v>
       </c>
@@ -6261,7 +6251,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="46">
         <v>31</v>
       </c>
@@ -6358,7 +6348,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="46">
         <v>32</v>
       </c>
@@ -6455,7 +6445,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="46">
         <v>33</v>
       </c>
@@ -6552,7 +6542,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="46">
         <v>34</v>
       </c>
@@ -6649,7 +6639,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="46">
         <v>35</v>
       </c>
@@ -6746,7 +6736,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="46">
         <v>36</v>
       </c>
@@ -6843,7 +6833,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="46">
         <v>37</v>
       </c>
@@ -6940,7 +6930,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="46">
         <v>38</v>
       </c>
@@ -7037,7 +7027,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="46">
         <v>39</v>
       </c>
@@ -7134,7 +7124,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="46">
         <v>40</v>
       </c>
@@ -7231,7 +7221,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="46">
         <v>41</v>
       </c>
@@ -7328,7 +7318,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="46">
         <v>42</v>
       </c>
@@ -7425,7 +7415,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="46">
         <v>43</v>
       </c>
@@ -7522,7 +7512,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="46">
         <v>44</v>
       </c>
@@ -7619,7 +7609,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="46">
         <v>45</v>
       </c>
@@ -7716,7 +7706,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="46">
         <v>46</v>
       </c>
@@ -7813,7 +7803,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="46">
         <v>47</v>
       </c>
@@ -7910,7 +7900,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="46">
         <v>48</v>
       </c>
@@ -8007,7 +7997,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="46">
         <v>49</v>
       </c>
@@ -8104,7 +8094,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="46">
         <v>50</v>
       </c>
@@ -8201,7 +8191,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="46">
         <v>51</v>
       </c>
@@ -8298,7 +8288,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="52" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="46">
         <v>52</v>
       </c>
@@ -8345,7 +8335,7 @@
         <v>Solos</v>
       </c>
       <c r="O52" s="61" t="str">
-        <f t="shared" ref="O52:P52" si="16">SUBSTITUTE(CONCATENATE("", F52), ".", " ")</f>
+        <f t="shared" ref="O52" si="16">SUBSTITUTE(CONCATENATE("", F52), ".", " ")</f>
         <v>Terreno</v>
       </c>
       <c r="P52" s="61" t="s">
@@ -8395,7 +8385,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="46">
         <v>53</v>
       </c>
@@ -8406,10 +8396,10 @@
         <v>383</v>
       </c>
       <c r="D53" s="59" t="s">
+        <v>385</v>
+      </c>
+      <c r="E53" s="59" t="s">
         <v>384</v>
-      </c>
-      <c r="E53" s="59" t="s">
-        <v>385</v>
       </c>
       <c r="F53" s="59" t="s">
         <v>386</v>
@@ -8435,11 +8425,11 @@
       </c>
       <c r="M53" s="61" t="str">
         <f t="shared" si="21"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N53" s="61" t="str">
         <f t="shared" si="21"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O53" s="61" t="str">
         <f t="shared" si="21"/>
@@ -8463,11 +8453,11 @@
       </c>
       <c r="U53" s="18" t="str">
         <f t="shared" si="22"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V53" s="21" t="str">
         <f t="shared" si="22"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W53" s="21" t="s">
         <v>390</v>
@@ -8498,123 +8488,123 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:B53">
-    <cfRule type="cellIs" dxfId="71" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:X1048576 A1:Q1 S1:X1 C2:E2 P2 AD2:XFD2 D3:E8 C3:C51 D9:D27">
-    <cfRule type="cellIs" dxfId="70" priority="258" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="258" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F27">
-    <cfRule type="duplicateValues" dxfId="69" priority="1046"/>
-    <cfRule type="cellIs" dxfId="68" priority="64" operator="equal">
+    <cfRule type="duplicateValues" dxfId="68" priority="1046"/>
+    <cfRule type="cellIs" dxfId="67" priority="64" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28:F45 Q2:Q51 P28:P29 AD28:XFD29 P34:P41 AD34:XFD41 P43:P45 AD43:XFD45">
-    <cfRule type="cellIs" dxfId="67" priority="125" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="125" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28:F45">
-    <cfRule type="duplicateValues" dxfId="66" priority="1028"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="1027"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="1025"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="1028"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="1027"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="1025"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F46:F47">
-    <cfRule type="duplicateValues" dxfId="63" priority="995"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="995"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F51">
-    <cfRule type="duplicateValues" dxfId="62" priority="1031"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="1031"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52:F53">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F54:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="60" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="259"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F54:F1048576 F1:F51">
-    <cfRule type="duplicateValues" dxfId="59" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F54:F1048576">
-    <cfRule type="duplicateValues" dxfId="58" priority="788"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="775"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="768"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="760"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="788"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="775"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="768"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="760"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="251"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R53">
-    <cfRule type="cellIs" dxfId="53" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X54:X1048576 X1">
-    <cfRule type="duplicateValues" dxfId="52" priority="587"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="587"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y50">
-    <cfRule type="duplicateValues" dxfId="51" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="duplicateValues" dxfId="47" priority="89"/>
-    <cfRule type="cellIs" dxfId="46" priority="88" operator="equal">
+    <cfRule type="duplicateValues" dxfId="46" priority="89"/>
+    <cfRule type="cellIs" dxfId="45" priority="88" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA3">
-    <cfRule type="duplicateValues" dxfId="45" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA3:AA8 AA17:AA27 AA10:AA14">
-    <cfRule type="duplicateValues" dxfId="41" priority="1043"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="1043"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA4:AA8 AA19:AA27 AA10:AA14">
-    <cfRule type="duplicateValues" dxfId="40" priority="1040"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="1040"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA4:AA8 AA19:AA27">
-    <cfRule type="duplicateValues" dxfId="39" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA9">
-    <cfRule type="duplicateValues" dxfId="38" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA10:AA14">
-    <cfRule type="duplicateValues" dxfId="33" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA15:AA16">
-    <cfRule type="duplicateValues" dxfId="29" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA17:AA18">
-    <cfRule type="duplicateValues" dxfId="21" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA19:AA27">
-    <cfRule type="duplicateValues" dxfId="16" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1:XFD1 AB54:XFD1048576">
-    <cfRule type="cellIs" dxfId="15" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8626,15 +8616,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="8" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="9" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="7" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="7"/>
+    <col min="1" max="1" width="2.84375" style="8" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="9" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="7" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -8699,7 +8689,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="3" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="3" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>2</v>
       </c>
@@ -8766,7 +8756,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8781,15 +8771,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" style="15" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" style="14" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="7.53515625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="19">
         <v>0</v>
       </c>
@@ -8812,7 +8802,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -8838,15 +8828,15 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="13" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -8855,29 +8845,29 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A426B82-2E19-47C6-9DDF-914E7B26E6D0}">
   <dimension ref="A1:AG7"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.2" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" style="31" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" style="31" customWidth="1"/>
-    <col min="4" max="5" width="3.140625" style="31" customWidth="1"/>
-    <col min="6" max="6" width="3.140625" style="33" customWidth="1"/>
-    <col min="7" max="7" width="3.140625" style="31" customWidth="1"/>
-    <col min="8" max="8" width="3.5703125" style="33" customWidth="1"/>
-    <col min="9" max="9" width="6.85546875" style="33" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" style="33" customWidth="1"/>
-    <col min="11" max="11" width="37.85546875" style="33" customWidth="1"/>
-    <col min="12" max="12" width="3.42578125" style="31" customWidth="1"/>
-    <col min="13" max="13" width="3.85546875" style="31" customWidth="1"/>
-    <col min="14" max="14" width="5.28515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" style="31" customWidth="1"/>
-    <col min="16" max="16" width="6.42578125" style="31" customWidth="1"/>
-    <col min="17" max="17" width="7.7109375" style="31" customWidth="1"/>
-    <col min="18" max="33" width="3.85546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.28515625" style="31"/>
+    <col min="1" max="1" width="2.53515625" style="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.3828125" style="31" customWidth="1"/>
+    <col min="3" max="3" width="6.3828125" style="31" customWidth="1"/>
+    <col min="4" max="5" width="3.15234375" style="31" customWidth="1"/>
+    <col min="6" max="6" width="3.15234375" style="33" customWidth="1"/>
+    <col min="7" max="7" width="3.15234375" style="31" customWidth="1"/>
+    <col min="8" max="8" width="3.53515625" style="33" customWidth="1"/>
+    <col min="9" max="9" width="6.84375" style="33" customWidth="1"/>
+    <col min="10" max="10" width="4.69140625" style="33" customWidth="1"/>
+    <col min="11" max="11" width="37.84375" style="33" customWidth="1"/>
+    <col min="12" max="12" width="3.3828125" style="31" customWidth="1"/>
+    <col min="13" max="13" width="3.84375" style="31" customWidth="1"/>
+    <col min="14" max="14" width="5.3046875" style="31" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.69140625" style="31" customWidth="1"/>
+    <col min="16" max="16" width="6.3828125" style="31" customWidth="1"/>
+    <col min="17" max="17" width="7.69140625" style="31" customWidth="1"/>
+    <col min="18" max="33" width="3.84375" style="31" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.3046875" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="28" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" s="28" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="26" t="s">
         <v>10</v>
       </c>
@@ -8978,7 +8968,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:33" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="30">
         <v>1</v>
       </c>
@@ -9079,7 +9069,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="30">
         <v>2</v>
       </c>
@@ -9181,7 +9171,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="30">
         <v>3</v>
       </c>
@@ -9283,7 +9273,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="30">
         <v>4</v>
       </c>
@@ -9385,7 +9375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="30">
         <v>5</v>
       </c>
@@ -9487,7 +9477,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="30">
         <v>6</v>
       </c>
@@ -9592,40 +9582,40 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1 A2:B2 A8:XFD1048576 H2:O2 AH2:XFD2 A3:A7">
-    <cfRule type="cellIs" dxfId="10" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B2 B8:B1048576">
-    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="1030"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1030"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B7">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="cellIs" dxfId="5" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:G7">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:I7">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:Q2">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:AG7">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/EST/Ontologia_Geotecnica.xlsx
+++ b/Versão5/EST/Ontologia_Geotecnica.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC4145B-11B8-4E4F-9DB3-A598840BFAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036E1875-145F-4ACA-8F6D-AFE491A02D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="438">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -1232,18 +1232,6 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
-  </si>
-  <si>
-    <t>Aplicativo Revit</t>
-  </si>
-  <si>
-    <t>Revit Aplication</t>
-  </si>
-  <si>
     <t>Geotécnica</t>
   </si>
   <si>
@@ -1332,6 +1320,72 @@
   </si>
   <si>
     <t>Terrain.</t>
+  </si>
+  <si>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -1443,7 +1497,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1594,6 +1648,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE89F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -1681,7 +1741,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1896,19 +1956,14 @@
     <xf numFmtId="0" fontId="4" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="71">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="72">
     <dxf>
       <font>
         <b val="0"/>
@@ -2540,6 +2595,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i/>
         <color theme="0" tint="-0.499984740745262"/>
@@ -2552,6 +2617,16 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3012,15 +3087,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.3046875" style="23" customWidth="1"/>
-    <col min="2" max="2" width="39.15234375" style="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="37" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="23"/>
+    <col min="1" max="1" width="9.28515625" style="23" customWidth="1"/>
+    <col min="2" max="2" width="39.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="37" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>43</v>
       </c>
@@ -3031,7 +3106,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>45</v>
       </c>
@@ -3042,7 +3117,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>47</v>
       </c>
@@ -3053,7 +3128,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>48</v>
       </c>
@@ -3064,7 +3139,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>49</v>
       </c>
@@ -3076,7 +3151,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>50</v>
       </c>
@@ -3088,7 +3163,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>51</v>
       </c>
@@ -3099,7 +3174,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>53</v>
       </c>
@@ -3110,7 +3185,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>54</v>
       </c>
@@ -3121,7 +3196,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>56</v>
       </c>
@@ -3132,7 +3207,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>58</v>
       </c>
@@ -3143,7 +3218,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>59</v>
       </c>
@@ -3154,7 +3229,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>60</v>
       </c>
@@ -3165,7 +3240,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>61</v>
       </c>
@@ -3176,7 +3251,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>62</v>
       </c>
@@ -3187,7 +3262,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>63</v>
       </c>
@@ -3198,7 +3273,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>64</v>
       </c>
@@ -3209,19 +3284,19 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>65</v>
       </c>
       <c r="B18" s="25">
         <f ca="1">NOW()</f>
-        <v>46264.567591550927</v>
+        <v>46268.697182870368</v>
       </c>
       <c r="C18" s="36" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>93</v>
       </c>
@@ -3232,7 +3307,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>90</v>
       </c>
@@ -3244,7 +3319,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
         <v>92</v>
       </c>
@@ -3256,7 +3331,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>66</v>
       </c>
@@ -3267,7 +3342,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>67</v>
       </c>
@@ -3278,7 +3353,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>68</v>
       </c>
@@ -3289,7 +3364,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>69</v>
       </c>
@@ -3300,7 +3375,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>84</v>
       </c>
@@ -3319,37 +3394,38 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A56445-53D9-475A-B2C6-D376FC6516D5}">
-  <dimension ref="A1:AC53"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AD57"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.69140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.69140625" customWidth="1"/>
-    <col min="5" max="5" width="9.3828125" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="11" width="8" style="57" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.69140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.84375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.84375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.3828125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="35.15234375" customWidth="1"/>
-    <col min="17" max="17" width="35.84375" customWidth="1"/>
-    <col min="18" max="18" width="38.15234375" customWidth="1"/>
+    <col min="12" max="12" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="35.140625" customWidth="1"/>
+    <col min="17" max="17" width="35.85546875" customWidth="1"/>
+    <col min="18" max="18" width="38.140625" customWidth="1"/>
     <col min="19" max="19" width="3" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.69140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13" customWidth="1"/>
-    <col min="22" max="22" width="7.84375" customWidth="1"/>
-    <col min="23" max="23" width="6.69140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.69140625" customWidth="1"/>
-    <col min="25" max="25" width="32.15234375" customWidth="1"/>
-    <col min="26" max="26" width="7.69140625" customWidth="1"/>
-    <col min="27" max="27" width="20.53515625" customWidth="1"/>
-    <col min="28" max="28" width="6.84375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.3046875" customWidth="1"/>
+    <col min="22" max="22" width="7.85546875" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.7109375" customWidth="1"/>
+    <col min="25" max="25" width="32.140625" customWidth="1"/>
+    <col min="26" max="26" width="7.7109375" customWidth="1"/>
+    <col min="27" max="27" width="20.5703125" customWidth="1"/>
+    <col min="28" max="28" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.28515625" customWidth="1"/>
+    <col min="30" max="30" width="6.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="36.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:30" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22">
         <v>1</v>
       </c>
@@ -3437,8 +3513,11 @@
       <c r="AC1" s="49" t="s">
         <v>82</v>
       </c>
+      <c r="AD1" s="49" t="s">
+        <v>437</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46">
         <v>2</v>
       </c>
@@ -3513,10 +3592,10 @@
         <v>Compactação</v>
       </c>
       <c r="W2" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X2" s="54" t="str">
-        <f t="shared" ref="X2:X53" si="5">CONCATENATE("Key-GEO-",A2)</f>
+        <f t="shared" ref="X2:X51" si="5">CONCATENATE("Key-GEO-",A2)</f>
         <v>Key-GEO-2</v>
       </c>
       <c r="Y2" s="62" t="s">
@@ -3534,8 +3613,11 @@
       <c r="AC2" s="21" t="s">
         <v>275</v>
       </c>
+      <c r="AD2" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="46">
         <v>3</v>
       </c>
@@ -3610,7 +3692,7 @@
         <v>Compactação</v>
       </c>
       <c r="W3" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X3" s="54" t="str">
         <f t="shared" si="5"/>
@@ -3631,8 +3713,11 @@
       <c r="AC3" s="21" t="s">
         <v>275</v>
       </c>
+      <c r="AD3" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="46">
         <v>4</v>
       </c>
@@ -3707,7 +3792,7 @@
         <v>Compactação</v>
       </c>
       <c r="W4" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X4" s="54" t="str">
         <f t="shared" si="5"/>
@@ -3728,8 +3813,11 @@
       <c r="AC4" s="21" t="s">
         <v>275</v>
       </c>
+      <c r="AD4" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="46">
         <v>5</v>
       </c>
@@ -3804,7 +3892,7 @@
         <v>Compactação</v>
       </c>
       <c r="W5" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X5" s="54" t="str">
         <f t="shared" si="5"/>
@@ -3825,8 +3913,11 @@
       <c r="AC5" s="21" t="s">
         <v>275</v>
       </c>
+      <c r="AD5" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="46">
         <v>6</v>
       </c>
@@ -3901,7 +3992,7 @@
         <v>Compactação</v>
       </c>
       <c r="W6" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X6" s="54" t="str">
         <f t="shared" si="5"/>
@@ -3922,8 +4013,11 @@
       <c r="AC6" s="21" t="s">
         <v>275</v>
       </c>
+      <c r="AD6" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="46">
         <v>7</v>
       </c>
@@ -3998,7 +4092,7 @@
         <v>Compactação</v>
       </c>
       <c r="W7" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X7" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4019,8 +4113,11 @@
       <c r="AC7" s="21" t="s">
         <v>275</v>
       </c>
+      <c r="AD7" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="46">
         <v>8</v>
       </c>
@@ -4095,7 +4192,7 @@
         <v>Compactação</v>
       </c>
       <c r="W8" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X8" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4116,8 +4213,11 @@
       <c r="AC8" s="21" t="s">
         <v>275</v>
       </c>
+      <c r="AD8" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="46">
         <v>9</v>
       </c>
@@ -4192,7 +4292,7 @@
         <v>Escavações</v>
       </c>
       <c r="W9" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X9" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4213,8 +4313,11 @@
       <c r="AC9" s="21" t="s">
         <v>275</v>
       </c>
+      <c r="AD9" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="46">
         <v>10</v>
       </c>
@@ -4289,7 +4392,7 @@
         <v>Escavações</v>
       </c>
       <c r="W10" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X10" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4310,8 +4413,11 @@
       <c r="AC10" s="21" t="s">
         <v>275</v>
       </c>
+      <c r="AD10" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="46">
         <v>11</v>
       </c>
@@ -4386,7 +4492,7 @@
         <v>Escavações</v>
       </c>
       <c r="W11" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X11" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4407,8 +4513,11 @@
       <c r="AC11" s="21" t="s">
         <v>275</v>
       </c>
+      <c r="AD11" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="46">
         <v>12</v>
       </c>
@@ -4483,7 +4592,7 @@
         <v>Escavações</v>
       </c>
       <c r="W12" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X12" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4504,8 +4613,11 @@
       <c r="AC12" s="21" t="s">
         <v>275</v>
       </c>
+      <c r="AD12" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="46">
         <v>13</v>
       </c>
@@ -4580,7 +4692,7 @@
         <v>Escavações</v>
       </c>
       <c r="W13" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X13" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4601,8 +4713,11 @@
       <c r="AC13" s="21" t="s">
         <v>275</v>
       </c>
+      <c r="AD13" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="46">
         <v>14</v>
       </c>
@@ -4677,7 +4792,7 @@
         <v>Escavações</v>
       </c>
       <c r="W14" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X14" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4698,8 +4813,11 @@
       <c r="AC14" s="21" t="s">
         <v>275</v>
       </c>
+      <c r="AD14" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="46">
         <v>15</v>
       </c>
@@ -4774,7 +4892,7 @@
         <v>Escavações</v>
       </c>
       <c r="W15" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X15" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4795,8 +4913,11 @@
       <c r="AC15" s="21" t="s">
         <v>275</v>
       </c>
+      <c r="AD15" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="46">
         <v>16</v>
       </c>
@@ -4871,7 +4992,7 @@
         <v>Escavações</v>
       </c>
       <c r="W16" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X16" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4892,8 +5013,11 @@
       <c r="AC16" s="21" t="s">
         <v>275</v>
       </c>
+      <c r="AD16" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="46">
         <v>17</v>
       </c>
@@ -4968,7 +5092,7 @@
         <v>Escavações</v>
       </c>
       <c r="W17" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X17" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4989,8 +5113,11 @@
       <c r="AC17" s="21" t="s">
         <v>275</v>
       </c>
+      <c r="AD17" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="46">
         <v>18</v>
       </c>
@@ -5065,7 +5192,7 @@
         <v>Escavações</v>
       </c>
       <c r="W18" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X18" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5086,8 +5213,11 @@
       <c r="AC18" s="21" t="s">
         <v>275</v>
       </c>
+      <c r="AD18" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="46">
         <v>19</v>
       </c>
@@ -5162,7 +5292,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W19" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X19" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5183,8 +5313,11 @@
       <c r="AC19" s="21" t="s">
         <v>276</v>
       </c>
+      <c r="AD19" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="46">
         <v>20</v>
       </c>
@@ -5259,7 +5392,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W20" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X20" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5280,8 +5413,11 @@
       <c r="AC20" s="21" t="s">
         <v>276</v>
       </c>
+      <c r="AD20" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="46">
         <v>21</v>
       </c>
@@ -5356,7 +5492,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W21" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X21" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5377,8 +5513,11 @@
       <c r="AC21" s="21" t="s">
         <v>276</v>
       </c>
+      <c r="AD21" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="46">
         <v>22</v>
       </c>
@@ -5453,7 +5592,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W22" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X22" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5474,8 +5613,11 @@
       <c r="AC22" s="21" t="s">
         <v>276</v>
       </c>
+      <c r="AD22" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="46">
         <v>23</v>
       </c>
@@ -5550,7 +5692,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W23" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X23" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5571,8 +5713,11 @@
       <c r="AC23" s="21" t="s">
         <v>276</v>
       </c>
+      <c r="AD23" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="46">
         <v>24</v>
       </c>
@@ -5647,7 +5792,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W24" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X24" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5668,8 +5813,11 @@
       <c r="AC24" s="21" t="s">
         <v>276</v>
       </c>
+      <c r="AD24" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="46">
         <v>25</v>
       </c>
@@ -5744,7 +5892,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W25" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X25" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5765,8 +5913,11 @@
       <c r="AC25" s="21" t="s">
         <v>276</v>
       </c>
+      <c r="AD25" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="46">
         <v>26</v>
       </c>
@@ -5841,7 +5992,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W26" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X26" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5862,8 +6013,11 @@
       <c r="AC26" s="21" t="s">
         <v>276</v>
       </c>
+      <c r="AD26" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="27" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="46">
         <v>27</v>
       </c>
@@ -5938,7 +6092,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W27" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X27" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5959,8 +6113,11 @@
       <c r="AC27" s="21" t="s">
         <v>276</v>
       </c>
+      <c r="AD27" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="46">
         <v>28</v>
       </c>
@@ -6035,7 +6192,7 @@
         <v>Pontos.do.Modelo</v>
       </c>
       <c r="W28" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X28" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6056,8 +6213,11 @@
       <c r="AC28" s="21" t="s">
         <v>142</v>
       </c>
+      <c r="AD28" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="46">
         <v>29</v>
       </c>
@@ -6132,7 +6292,7 @@
         <v>Pontos.do.Modelo</v>
       </c>
       <c r="W29" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X29" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6153,8 +6313,11 @@
       <c r="AC29" s="21" t="s">
         <v>142</v>
       </c>
+      <c r="AD29" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="46">
         <v>30</v>
       </c>
@@ -6229,7 +6392,7 @@
         <v>Pontos.do.Modelo</v>
       </c>
       <c r="W30" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X30" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6250,8 +6413,11 @@
       <c r="AC30" s="21" t="s">
         <v>142</v>
       </c>
+      <c r="AD30" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="31" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="46">
         <v>31</v>
       </c>
@@ -6326,7 +6492,7 @@
         <v>Pontos.do.Modelo</v>
       </c>
       <c r="W31" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X31" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6347,8 +6513,11 @@
       <c r="AC31" s="21" t="s">
         <v>142</v>
       </c>
+      <c r="AD31" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="32" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="46">
         <v>32</v>
       </c>
@@ -6423,7 +6592,7 @@
         <v>Sondagens</v>
       </c>
       <c r="W32" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X32" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6444,8 +6613,11 @@
       <c r="AC32" s="21" t="s">
         <v>142</v>
       </c>
+      <c r="AD32" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="33" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="46">
         <v>33</v>
       </c>
@@ -6520,7 +6692,7 @@
         <v>Sondagens</v>
       </c>
       <c r="W33" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X33" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6541,8 +6713,11 @@
       <c r="AC33" s="21" t="s">
         <v>142</v>
       </c>
+      <c r="AD33" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="34" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="46">
         <v>34</v>
       </c>
@@ -6617,7 +6792,7 @@
         <v>Topografia</v>
       </c>
       <c r="W34" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X34" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6638,8 +6813,11 @@
       <c r="AC34" s="21" t="s">
         <v>142</v>
       </c>
+      <c r="AD34" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="35" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="46">
         <v>35</v>
       </c>
@@ -6714,7 +6892,7 @@
         <v>Topografia</v>
       </c>
       <c r="W35" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X35" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6735,8 +6913,11 @@
       <c r="AC35" s="21" t="s">
         <v>142</v>
       </c>
+      <c r="AD35" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="36" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="46">
         <v>36</v>
       </c>
@@ -6811,7 +6992,7 @@
         <v>Topografia</v>
       </c>
       <c r="W36" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X36" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6832,8 +7013,11 @@
       <c r="AC36" s="21" t="s">
         <v>142</v>
       </c>
+      <c r="AD36" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="37" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="46">
         <v>37</v>
       </c>
@@ -6908,7 +7092,7 @@
         <v>Topografia</v>
       </c>
       <c r="W37" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X37" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6929,8 +7113,11 @@
       <c r="AC37" s="21" t="s">
         <v>142</v>
       </c>
+      <c r="AD37" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="38" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="46">
         <v>38</v>
       </c>
@@ -7005,7 +7192,7 @@
         <v>Topografia</v>
       </c>
       <c r="W38" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X38" s="54" t="str">
         <f t="shared" si="5"/>
@@ -7026,8 +7213,11 @@
       <c r="AC38" s="21" t="s">
         <v>142</v>
       </c>
+      <c r="AD38" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="39" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="46">
         <v>39</v>
       </c>
@@ -7102,7 +7292,7 @@
         <v>Topografia</v>
       </c>
       <c r="W39" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X39" s="54" t="str">
         <f t="shared" si="5"/>
@@ -7123,8 +7313,11 @@
       <c r="AC39" s="21" t="s">
         <v>142</v>
       </c>
+      <c r="AD39" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="40" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="46">
         <v>40</v>
       </c>
@@ -7199,7 +7392,7 @@
         <v>Topografia</v>
       </c>
       <c r="W40" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X40" s="54" t="str">
         <f t="shared" si="5"/>
@@ -7220,8 +7413,11 @@
       <c r="AC40" s="21" t="s">
         <v>142</v>
       </c>
+      <c r="AD40" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="41" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="46">
         <v>41</v>
       </c>
@@ -7296,7 +7492,7 @@
         <v>Topografia</v>
       </c>
       <c r="W41" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X41" s="54" t="str">
         <f t="shared" si="5"/>
@@ -7317,8 +7513,11 @@
       <c r="AC41" s="21" t="s">
         <v>142</v>
       </c>
+      <c r="AD41" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="42" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="46">
         <v>42</v>
       </c>
@@ -7393,7 +7592,7 @@
         <v>Topografia</v>
       </c>
       <c r="W42" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X42" s="54" t="str">
         <f t="shared" si="5"/>
@@ -7414,8 +7613,11 @@
       <c r="AC42" s="21" t="s">
         <v>142</v>
       </c>
+      <c r="AD42" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="43" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="46">
         <v>43</v>
       </c>
@@ -7490,7 +7692,7 @@
         <v>Curvas.de.Nível</v>
       </c>
       <c r="W43" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X43" s="54" t="str">
         <f t="shared" si="5"/>
@@ -7511,8 +7713,11 @@
       <c r="AC43" s="21" t="s">
         <v>142</v>
       </c>
+      <c r="AD43" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="44" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="46">
         <v>44</v>
       </c>
@@ -7587,7 +7792,7 @@
         <v>Curvas.de.Nível</v>
       </c>
       <c r="W44" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X44" s="54" t="str">
         <f t="shared" si="5"/>
@@ -7608,8 +7813,11 @@
       <c r="AC44" s="21" t="s">
         <v>142</v>
       </c>
+      <c r="AD44" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="45" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="46">
         <v>45</v>
       </c>
@@ -7684,7 +7892,7 @@
         <v>Curvas.de.Nível</v>
       </c>
       <c r="W45" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X45" s="54" t="str">
         <f t="shared" si="5"/>
@@ -7705,8 +7913,11 @@
       <c r="AC45" s="21" t="s">
         <v>142</v>
       </c>
+      <c r="AD45" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="46" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="46">
         <v>46</v>
       </c>
@@ -7781,7 +7992,7 @@
         <v>Loteamento</v>
       </c>
       <c r="W46" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X46" s="54" t="str">
         <f t="shared" si="5"/>
@@ -7802,8 +8013,11 @@
       <c r="AC46" s="21" t="s">
         <v>142</v>
       </c>
+      <c r="AD46" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="47" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="46">
         <v>47</v>
       </c>
@@ -7878,7 +8092,7 @@
         <v>Loteamento</v>
       </c>
       <c r="W47" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X47" s="54" t="str">
         <f t="shared" si="5"/>
@@ -7899,8 +8113,11 @@
       <c r="AC47" s="21" t="s">
         <v>142</v>
       </c>
+      <c r="AD47" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="48" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="46">
         <v>48</v>
       </c>
@@ -7975,7 +8192,7 @@
         <v>Paisagismo</v>
       </c>
       <c r="W48" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X48" s="54" t="str">
         <f t="shared" si="5"/>
@@ -7996,8 +8213,11 @@
       <c r="AC48" s="21" t="s">
         <v>278</v>
       </c>
+      <c r="AD48" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="49" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="46">
         <v>49</v>
       </c>
@@ -8072,7 +8292,7 @@
         <v>Paisagismo</v>
       </c>
       <c r="W49" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X49" s="54" t="str">
         <f t="shared" si="5"/>
@@ -8093,8 +8313,11 @@
       <c r="AC49" s="21" t="s">
         <v>278</v>
       </c>
+      <c r="AD49" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="50" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="46">
         <v>50</v>
       </c>
@@ -8169,7 +8392,7 @@
         <v>Paisagismo</v>
       </c>
       <c r="W50" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X50" s="54" t="str">
         <f t="shared" si="5"/>
@@ -8190,8 +8413,11 @@
       <c r="AC50" s="21" t="s">
         <v>278</v>
       </c>
+      <c r="AD50" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="51" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="46">
         <v>51</v>
       </c>
@@ -8266,7 +8492,7 @@
         <v>Paisagismo</v>
       </c>
       <c r="W51" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X51" s="54" t="str">
         <f t="shared" si="5"/>
@@ -8287,8 +8513,11 @@
       <c r="AC51" s="21" t="s">
         <v>277</v>
       </c>
+      <c r="AD51" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="52" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="46">
         <v>52</v>
       </c>
@@ -8296,16 +8525,16 @@
         <v>382</v>
       </c>
       <c r="C52" s="59" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="D52" s="59" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="E52" s="59" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F52" s="59" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="G52" s="60" t="s">
         <v>9</v>
@@ -8323,7 +8552,7 @@
         <v>9</v>
       </c>
       <c r="L52" s="61" t="str">
-        <f t="shared" ref="L52" si="13">SUBSTITUTE(CONCATENATE("", C52), ".", " ")</f>
+        <f t="shared" ref="L52:O57" si="13">SUBSTITUTE(CONCATENATE("", C52), ".", " ")</f>
         <v>De Geotécnica</v>
       </c>
       <c r="M52" s="61" t="str">
@@ -8339,19 +8568,19 @@
         <v>Terreno</v>
       </c>
       <c r="P52" s="61" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="Q52" s="61" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="R52" s="18" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="S52" s="18" t="s">
         <v>9</v>
       </c>
       <c r="T52" s="18" t="str">
-        <f t="shared" ref="T52" si="17">SUBSTITUTE(C52, ".", " ")</f>
+        <f t="shared" ref="T52:V57" si="17">SUBSTITUTE(C52, ".", " ")</f>
         <v>De Geotécnica</v>
       </c>
       <c r="U52" s="18" t="str">
@@ -8363,10 +8592,10 @@
         <v>Solos</v>
       </c>
       <c r="W52" s="21" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X52" s="54" t="str">
-        <f t="shared" ref="X52" si="20">CONCATENATE("Key-GEO-",A52)</f>
+        <f t="shared" ref="X52:X57" si="20">CONCATENATE("Key-GEO-",A52)</f>
         <v>Key-GEO-52</v>
       </c>
       <c r="Y52" s="62" t="s">
@@ -8384,8 +8613,11 @@
       <c r="AC52" s="62" t="s">
         <v>9</v>
       </c>
+      <c r="AD52" s="62" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="53" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="46">
         <v>53</v>
       </c>
@@ -8402,83 +8634,486 @@
         <v>384</v>
       </c>
       <c r="F53" s="59" t="s">
+        <v>416</v>
+      </c>
+      <c r="G53" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H53" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I53" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J53" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K53" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L53" s="61" t="str">
+        <f t="shared" si="13"/>
+        <v>De API</v>
+      </c>
+      <c r="M53" s="61" t="str">
+        <f t="shared" si="13"/>
+        <v>Macros</v>
+      </c>
+      <c r="N53" s="61" t="str">
+        <f t="shared" si="13"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O53" s="61" t="str">
+        <f t="shared" si="13"/>
+        <v>Função Auxiliar</v>
+      </c>
+      <c r="P53" s="18" t="s">
+        <v>417</v>
+      </c>
+      <c r="Q53" s="18" t="s">
+        <v>418</v>
+      </c>
+      <c r="R53" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="S53" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="T53" s="18" t="str">
+        <f t="shared" si="17"/>
+        <v>De API</v>
+      </c>
+      <c r="U53" s="18" t="str">
+        <f t="shared" si="17"/>
+        <v>Macros</v>
+      </c>
+      <c r="V53" s="21" t="str">
+        <f t="shared" si="17"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W53" s="21" t="s">
         <v>386</v>
       </c>
-      <c r="G53" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="H53" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="I53" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="J53" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="K53" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="L53" s="61" t="str">
-        <f t="shared" ref="L53:O53" si="21">SUBSTITUTE(CONCATENATE("", C53), ".", " ")</f>
+      <c r="X53" s="54" t="str">
+        <f t="shared" si="20"/>
+        <v>Key-GEO-53</v>
+      </c>
+      <c r="Y53" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z53" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA53" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB53" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC53" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD53" s="62" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="46">
+        <v>54</v>
+      </c>
+      <c r="B54" s="58" t="s">
+        <v>382</v>
+      </c>
+      <c r="C54" s="59" t="s">
+        <v>383</v>
+      </c>
+      <c r="D54" s="59" t="s">
+        <v>385</v>
+      </c>
+      <c r="E54" s="59" t="s">
+        <v>384</v>
+      </c>
+      <c r="F54" s="59" t="s">
+        <v>420</v>
+      </c>
+      <c r="G54" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H54" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I54" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J54" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K54" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L54" s="61" t="str">
+        <f t="shared" si="13"/>
         <v>De API</v>
       </c>
-      <c r="M53" s="61" t="str">
-        <f t="shared" si="21"/>
+      <c r="M54" s="61" t="str">
+        <f t="shared" si="13"/>
         <v>Macros</v>
       </c>
-      <c r="N53" s="61" t="str">
-        <f t="shared" si="21"/>
+      <c r="N54" s="61" t="str">
+        <f t="shared" si="13"/>
         <v>Métodos</v>
       </c>
-      <c r="O53" s="61" t="str">
-        <f t="shared" si="21"/>
-        <v>API Revit</v>
-      </c>
-      <c r="P53" s="18" t="s">
-        <v>387</v>
-      </c>
-      <c r="Q53" s="18" t="s">
-        <v>388</v>
-      </c>
-      <c r="R53" s="18" t="s">
-        <v>389</v>
-      </c>
-      <c r="S53" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="T53" s="18" t="str">
-        <f t="shared" ref="T53:V53" si="22">SUBSTITUTE(C53, ".", " ")</f>
+      <c r="O54" s="61" t="str">
+        <f t="shared" si="13"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P54" s="18" t="s">
+        <v>421</v>
+      </c>
+      <c r="Q54" s="18" t="s">
+        <v>422</v>
+      </c>
+      <c r="R54" s="18" t="s">
+        <v>423</v>
+      </c>
+      <c r="S54" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="T54" s="18" t="str">
+        <f t="shared" si="17"/>
         <v>De API</v>
       </c>
-      <c r="U53" s="18" t="str">
-        <f t="shared" si="22"/>
+      <c r="U54" s="18" t="str">
+        <f t="shared" si="17"/>
         <v>Macros</v>
       </c>
-      <c r="V53" s="21" t="str">
-        <f t="shared" si="22"/>
+      <c r="V54" s="21" t="str">
+        <f t="shared" si="17"/>
         <v>Métodos</v>
       </c>
-      <c r="W53" s="21" t="s">
-        <v>390</v>
-      </c>
-      <c r="X53" s="54" t="str">
-        <f t="shared" si="5"/>
-        <v>Key-GEO-53</v>
-      </c>
-      <c r="Y53" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z53" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA53" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB53" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC53" s="62" t="s">
+      <c r="W54" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="X54" s="54" t="str">
+        <f t="shared" si="20"/>
+        <v>Key-GEO-54</v>
+      </c>
+      <c r="Y54" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z54" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA54" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB54" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC54" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD54" s="62" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="46">
+        <v>55</v>
+      </c>
+      <c r="B55" s="58" t="s">
+        <v>382</v>
+      </c>
+      <c r="C55" s="59" t="s">
+        <v>383</v>
+      </c>
+      <c r="D55" s="59" t="s">
+        <v>385</v>
+      </c>
+      <c r="E55" s="59" t="s">
+        <v>384</v>
+      </c>
+      <c r="F55" s="59" t="s">
+        <v>424</v>
+      </c>
+      <c r="G55" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H55" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I55" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J55" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K55" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L55" s="61" t="str">
+        <f t="shared" si="13"/>
+        <v>De API</v>
+      </c>
+      <c r="M55" s="61" t="str">
+        <f t="shared" si="13"/>
+        <v>Macros</v>
+      </c>
+      <c r="N55" s="61" t="str">
+        <f t="shared" si="13"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O55" s="61" t="str">
+        <f t="shared" si="13"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P55" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="Q55" s="18" t="s">
+        <v>426</v>
+      </c>
+      <c r="R55" s="18" t="s">
+        <v>427</v>
+      </c>
+      <c r="S55" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="T55" s="18" t="str">
+        <f t="shared" si="17"/>
+        <v>De API</v>
+      </c>
+      <c r="U55" s="18" t="str">
+        <f t="shared" si="17"/>
+        <v>Macros</v>
+      </c>
+      <c r="V55" s="21" t="str">
+        <f t="shared" si="17"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W55" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="X55" s="54" t="str">
+        <f t="shared" si="20"/>
+        <v>Key-GEO-55</v>
+      </c>
+      <c r="Y55" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z55" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA55" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB55" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC55" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD55" s="62" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="46">
+        <v>56</v>
+      </c>
+      <c r="B56" s="58" t="s">
+        <v>382</v>
+      </c>
+      <c r="C56" s="59" t="s">
+        <v>383</v>
+      </c>
+      <c r="D56" s="59" t="s">
+        <v>385</v>
+      </c>
+      <c r="E56" s="59" t="s">
+        <v>384</v>
+      </c>
+      <c r="F56" s="59" t="s">
+        <v>428</v>
+      </c>
+      <c r="G56" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H56" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I56" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J56" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K56" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L56" s="61" t="str">
+        <f t="shared" si="13"/>
+        <v>De API</v>
+      </c>
+      <c r="M56" s="61" t="str">
+        <f t="shared" si="13"/>
+        <v>Macros</v>
+      </c>
+      <c r="N56" s="61" t="str">
+        <f t="shared" si="13"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O56" s="61" t="str">
+        <f t="shared" si="13"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P56" s="18" t="s">
+        <v>429</v>
+      </c>
+      <c r="Q56" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="R56" s="18" t="s">
+        <v>431</v>
+      </c>
+      <c r="S56" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="T56" s="18" t="str">
+        <f t="shared" si="17"/>
+        <v>De API</v>
+      </c>
+      <c r="U56" s="18" t="str">
+        <f t="shared" si="17"/>
+        <v>Macros</v>
+      </c>
+      <c r="V56" s="21" t="str">
+        <f t="shared" si="17"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W56" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="X56" s="54" t="str">
+        <f t="shared" si="20"/>
+        <v>Key-GEO-56</v>
+      </c>
+      <c r="Y56" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z56" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA56" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB56" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC56" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD56" s="62" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="46">
+        <v>57</v>
+      </c>
+      <c r="B57" s="58" t="s">
+        <v>382</v>
+      </c>
+      <c r="C57" s="59" t="s">
+        <v>383</v>
+      </c>
+      <c r="D57" s="59" t="s">
+        <v>385</v>
+      </c>
+      <c r="E57" s="59" t="s">
+        <v>432</v>
+      </c>
+      <c r="F57" s="59" t="s">
+        <v>433</v>
+      </c>
+      <c r="G57" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H57" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I57" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J57" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K57" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L57" s="61" t="str">
+        <f t="shared" si="13"/>
+        <v>De API</v>
+      </c>
+      <c r="M57" s="61" t="str">
+        <f t="shared" si="13"/>
+        <v>Macros</v>
+      </c>
+      <c r="N57" s="61" t="str">
+        <f t="shared" si="13"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O57" s="61" t="str">
+        <f t="shared" si="13"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P57" s="18" t="s">
+        <v>434</v>
+      </c>
+      <c r="Q57" s="18" t="s">
+        <v>435</v>
+      </c>
+      <c r="R57" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="S57" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="T57" s="18" t="str">
+        <f t="shared" si="17"/>
+        <v>De API</v>
+      </c>
+      <c r="U57" s="18" t="str">
+        <f t="shared" si="17"/>
+        <v>Macros</v>
+      </c>
+      <c r="V57" s="21" t="str">
+        <f t="shared" si="17"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W57" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="X57" s="54" t="str">
+        <f t="shared" si="20"/>
+        <v>Key-GEO-57</v>
+      </c>
+      <c r="Y57" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z57" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA57" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB57" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC57" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD57" s="62" t="s">
         <v>9</v>
       </c>
     </row>
@@ -8487,124 +9122,130 @@
     <sortCondition ref="E1:E805"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B53">
-    <cfRule type="cellIs" dxfId="70" priority="2" operator="equal">
+  <conditionalFormatting sqref="A2:B57">
+    <cfRule type="cellIs" dxfId="71" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A54:X1048576 A1:Q1 S1:X1 C2:E2 P2 AD2:XFD2 D3:E8 C3:C51 D9:D27">
-    <cfRule type="cellIs" dxfId="69" priority="258" operator="equal">
+  <conditionalFormatting sqref="A58:X1048576 A1:Q1 S1:X1 C2:E2 P2 AE2:XFD2 D3:E8 C3:C51 D9:D27">
+    <cfRule type="cellIs" dxfId="70" priority="262" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E57:F57">
+    <cfRule type="duplicateValues" dxfId="69" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F2:F27">
-    <cfRule type="duplicateValues" dxfId="68" priority="1046"/>
-    <cfRule type="cellIs" dxfId="67" priority="64" operator="equal">
+    <cfRule type="duplicateValues" dxfId="68" priority="1050"/>
+    <cfRule type="cellIs" dxfId="67" priority="68" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F28:F45 Q2:Q51 P28:P29 AD28:XFD29 P34:P41 AD34:XFD41 P43:P45 AD43:XFD45">
-    <cfRule type="cellIs" dxfId="66" priority="125" operator="equal">
+  <conditionalFormatting sqref="F28:F45 Q2:Q51 P28:P29 AE28:XFD29 P34:P41 AE34:XFD41 P43:P45 AE43:XFD45">
+    <cfRule type="cellIs" dxfId="66" priority="129" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28:F45">
-    <cfRule type="duplicateValues" dxfId="65" priority="1028"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="1027"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="1025"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="1032"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="1031"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="1029"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F46:F47">
-    <cfRule type="duplicateValues" dxfId="62" priority="995"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="999"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F51">
-    <cfRule type="duplicateValues" dxfId="61" priority="1031"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="1035"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F52:F53">
-    <cfRule type="duplicateValues" dxfId="60" priority="3"/>
+  <conditionalFormatting sqref="F52">
+    <cfRule type="duplicateValues" dxfId="60" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F54:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="59" priority="259"/>
+  <conditionalFormatting sqref="F53:F56">
+    <cfRule type="duplicateValues" dxfId="59" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F54:F1048576 F1:F51">
-    <cfRule type="duplicateValues" dxfId="58" priority="58"/>
+  <conditionalFormatting sqref="F58:F1048576 F1">
+    <cfRule type="duplicateValues" dxfId="58" priority="263"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F54:F1048576">
-    <cfRule type="duplicateValues" dxfId="57" priority="788"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="775"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="768"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="760"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="251"/>
+  <conditionalFormatting sqref="F58:F1048576 F1:F51">
+    <cfRule type="duplicateValues" dxfId="57" priority="62"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R53">
-    <cfRule type="cellIs" dxfId="52" priority="1" operator="equal">
+  <conditionalFormatting sqref="F58:F1048576">
+    <cfRule type="duplicateValues" dxfId="56" priority="792"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="779"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="772"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="764"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="255"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R1:R52">
+    <cfRule type="cellIs" dxfId="51" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X54:X1048576 X1">
-    <cfRule type="duplicateValues" dxfId="51" priority="587"/>
+  <conditionalFormatting sqref="X58:X1048576 X1">
+    <cfRule type="duplicateValues" dxfId="50" priority="591"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y50">
-    <cfRule type="duplicateValues" dxfId="50" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="duplicateValues" dxfId="46" priority="89"/>
-    <cfRule type="cellIs" dxfId="45" priority="88" operator="equal">
+    <cfRule type="duplicateValues" dxfId="45" priority="93"/>
+    <cfRule type="cellIs" dxfId="44" priority="92" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA3">
-    <cfRule type="duplicateValues" dxfId="44" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA3:AA8 AA17:AA27 AA10:AA14">
-    <cfRule type="duplicateValues" dxfId="40" priority="1043"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="1047"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA4:AA8 AA19:AA27 AA10:AA14">
-    <cfRule type="duplicateValues" dxfId="39" priority="1040"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="1044"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA4:AA8 AA19:AA27">
-    <cfRule type="duplicateValues" dxfId="38" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA9">
-    <cfRule type="duplicateValues" dxfId="37" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA10:AA14">
-    <cfRule type="duplicateValues" dxfId="32" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA15:AA16">
-    <cfRule type="duplicateValues" dxfId="28" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA17:AA18">
-    <cfRule type="duplicateValues" dxfId="20" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA19:AA27">
-    <cfRule type="duplicateValues" dxfId="15" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="94"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB1:XFD1 AB54:XFD1048576">
-    <cfRule type="cellIs" dxfId="14" priority="12" operator="equal">
+  <conditionalFormatting sqref="AB1:XFD1 AB58:XFD1048576">
+    <cfRule type="cellIs" dxfId="13" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8616,15 +9257,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="8" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="9" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="7" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="7"/>
+    <col min="1" max="1" width="2.85546875" style="8" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="9" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="7" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -8689,7 +9330,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="3" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="3" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="5">
         <v>2</v>
       </c>
@@ -8756,7 +9397,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8771,15 +9412,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" style="15" customWidth="1"/>
-    <col min="2" max="2" width="7.53515625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="11.3046875" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" style="15" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19">
         <v>0</v>
       </c>
@@ -8802,7 +9443,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -8828,15 +9469,15 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -8845,29 +9486,29 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A426B82-2E19-47C6-9DDF-914E7B26E6D0}">
   <dimension ref="A1:AG7"/>
-  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.2" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" style="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.3828125" style="31" customWidth="1"/>
-    <col min="3" max="3" width="6.3828125" style="31" customWidth="1"/>
-    <col min="4" max="5" width="3.15234375" style="31" customWidth="1"/>
-    <col min="6" max="6" width="3.15234375" style="33" customWidth="1"/>
-    <col min="7" max="7" width="3.15234375" style="31" customWidth="1"/>
-    <col min="8" max="8" width="3.53515625" style="33" customWidth="1"/>
-    <col min="9" max="9" width="6.84375" style="33" customWidth="1"/>
-    <col min="10" max="10" width="4.69140625" style="33" customWidth="1"/>
-    <col min="11" max="11" width="37.84375" style="33" customWidth="1"/>
-    <col min="12" max="12" width="3.3828125" style="31" customWidth="1"/>
-    <col min="13" max="13" width="3.84375" style="31" customWidth="1"/>
-    <col min="14" max="14" width="5.3046875" style="31" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.69140625" style="31" customWidth="1"/>
-    <col min="16" max="16" width="6.3828125" style="31" customWidth="1"/>
-    <col min="17" max="17" width="7.69140625" style="31" customWidth="1"/>
-    <col min="18" max="33" width="3.84375" style="31" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.3046875" style="31"/>
+    <col min="1" max="1" width="2.5703125" style="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" style="31" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" style="31" customWidth="1"/>
+    <col min="4" max="5" width="3.140625" style="31" customWidth="1"/>
+    <col min="6" max="6" width="3.140625" style="33" customWidth="1"/>
+    <col min="7" max="7" width="3.140625" style="31" customWidth="1"/>
+    <col min="8" max="8" width="3.5703125" style="33" customWidth="1"/>
+    <col min="9" max="9" width="6.85546875" style="33" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" style="33" customWidth="1"/>
+    <col min="11" max="11" width="37.85546875" style="33" customWidth="1"/>
+    <col min="12" max="12" width="3.42578125" style="31" customWidth="1"/>
+    <col min="13" max="13" width="3.85546875" style="31" customWidth="1"/>
+    <col min="14" max="14" width="5.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" style="31" customWidth="1"/>
+    <col min="16" max="16" width="6.42578125" style="31" customWidth="1"/>
+    <col min="17" max="17" width="7.7109375" style="31" customWidth="1"/>
+    <col min="18" max="33" width="3.85546875" style="31" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.28515625" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="28" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:33" s="28" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>10</v>
       </c>
@@ -8968,7 +9609,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:33" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:33" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30">
         <v>1</v>
       </c>
@@ -9069,15 +9710,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="30">
         <v>2</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>391</v>
-      </c>
-      <c r="C3" s="59" t="s">
-        <v>386</v>
+        <v>387</v>
+      </c>
+      <c r="C3" s="74" t="s">
+        <v>428</v>
       </c>
       <c r="D3" s="64" t="s">
         <v>9</v>
@@ -9101,26 +9742,26 @@
         <v>78</v>
       </c>
       <c r="K3" s="67" t="s">
+        <v>388</v>
+      </c>
+      <c r="L3" s="69" t="s">
+        <v>389</v>
+      </c>
+      <c r="M3" s="45" t="s">
+        <v>390</v>
+      </c>
+      <c r="N3" s="69" t="s">
+        <v>391</v>
+      </c>
+      <c r="O3" s="45" t="s">
         <v>392</v>
-      </c>
-      <c r="L3" s="69" t="s">
-        <v>393</v>
-      </c>
-      <c r="M3" s="45" t="s">
-        <v>394</v>
-      </c>
-      <c r="N3" s="69" t="s">
-        <v>395</v>
-      </c>
-      <c r="O3" s="45" t="s">
-        <v>396</v>
       </c>
       <c r="P3" s="71" t="str">
         <f t="shared" ref="P3:P7" si="0">IF(Q3="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
       <c r="Q3" s="72" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="R3" s="66" t="s">
         <v>9</v>
@@ -9171,15 +9812,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="30">
         <v>3</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>398</v>
-      </c>
-      <c r="C4" s="59" t="s">
-        <v>386</v>
+        <v>394</v>
+      </c>
+      <c r="C4" s="74" t="s">
+        <v>428</v>
       </c>
       <c r="D4" s="64" t="s">
         <v>9</v>
@@ -9203,26 +9844,26 @@
         <v>78</v>
       </c>
       <c r="K4" s="67" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="L4" s="69" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="M4" s="45" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="N4" s="69" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="O4" s="45" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="P4" s="71" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q4" s="72" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="R4" s="66" t="s">
         <v>9</v>
@@ -9273,15 +9914,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="30">
         <v>4</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>402</v>
-      </c>
-      <c r="C5" s="59" t="s">
-        <v>386</v>
+        <v>398</v>
+      </c>
+      <c r="C5" s="74" t="s">
+        <v>428</v>
       </c>
       <c r="D5" s="64" t="s">
         <v>9</v>
@@ -9305,26 +9946,26 @@
         <v>78</v>
       </c>
       <c r="K5" s="67" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="L5" s="69" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="M5" s="45" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="N5" s="69" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="O5" s="45" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="P5" s="71" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q5" s="72" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="R5" s="66" t="s">
         <v>9</v>
@@ -9375,15 +10016,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="30">
         <v>5</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>406</v>
-      </c>
-      <c r="C6" s="59" t="s">
-        <v>386</v>
+        <v>402</v>
+      </c>
+      <c r="C6" s="74" t="s">
+        <v>428</v>
       </c>
       <c r="D6" s="64" t="s">
         <v>9</v>
@@ -9407,26 +10048,26 @@
         <v>78</v>
       </c>
       <c r="K6" s="67" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="L6" s="69" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="M6" s="45" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="N6" s="69" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="O6" s="45" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="P6" s="71" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q6" s="72" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="R6" s="66" t="s">
         <v>9</v>
@@ -9477,15 +10118,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" s="70" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="30">
         <v>6</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>410</v>
-      </c>
-      <c r="C7" s="59" t="s">
-        <v>386</v>
+        <v>406</v>
+      </c>
+      <c r="C7" s="74" t="s">
+        <v>428</v>
       </c>
       <c r="D7" s="64" t="s">
         <v>9</v>
@@ -9509,26 +10150,26 @@
         <v>78</v>
       </c>
       <c r="K7" s="67" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="L7" s="69" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="M7" s="45" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="N7" s="69" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="O7" s="45" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="P7" s="71" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q7" s="72" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="R7" s="66" t="s">
         <v>9</v>
@@ -9582,40 +10223,35 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1 A2:B2 A8:XFD1048576 H2:O2 AH2:XFD2 A3:A7">
-    <cfRule type="cellIs" dxfId="9" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B2 B8:B1048576">
-    <cfRule type="duplicateValues" dxfId="8" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="1030"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1031"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B7">
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
     <cfRule type="duplicateValues" dxfId="5" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2">
-    <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:G7">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:I7">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:Q2">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:AG7">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/EST/Ontologia_Geotecnica.xlsx
+++ b/Versão5/EST/Ontologia_Geotecnica.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036E1875-145F-4ACA-8F6D-AFE491A02D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11864C92-5175-44CD-A56A-FB9770B04081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="440">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -1223,15 +1223,6 @@
     <t>Projeto</t>
   </si>
   <si>
-    <t>De.API</t>
-  </si>
-  <si>
-    <t>Métodos</t>
-  </si>
-  <si>
-    <t>Macros</t>
-  </si>
-  <si>
     <t>Geotécnica</t>
   </si>
   <si>
@@ -1370,9 +1361,6 @@
     <t>Define a Function to filter objects in an application</t>
   </si>
   <si>
-    <t>Códigos.Visuais</t>
-  </si>
-  <si>
     <t>Bloco.de.Código</t>
   </si>
   <si>
@@ -1386,6 +1374,24 @@
   </si>
   <si>
     <t>KML</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>API.Plataforma</t>
+  </si>
+  <si>
+    <t>API.Macros</t>
+  </si>
+  <si>
+    <t>API.Método</t>
+  </si>
+  <si>
+    <t>API.Macros.Visuais</t>
+  </si>
+  <si>
+    <t>API.Método.Visual</t>
   </si>
 </sst>
 </file>
@@ -1497,7 +1503,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="27">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1648,12 +1654,6 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE89F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -1741,7 +1741,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1956,14 +1956,62 @@
     <xf numFmtId="0" fontId="4" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="72">
+  <dxfs count="75">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2646,14 +2694,6 @@
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -3290,7 +3330,7 @@
       </c>
       <c r="B18" s="25">
         <f ca="1">NOW()</f>
-        <v>46268.697182870368</v>
+        <v>46273.688355787039</v>
       </c>
       <c r="C18" s="36" t="s">
         <v>87</v>
@@ -3411,10 +3451,10 @@
     <col min="16" max="16" width="35.140625" customWidth="1"/>
     <col min="17" max="17" width="35.85546875" customWidth="1"/>
     <col min="18" max="18" width="38.140625" customWidth="1"/>
-    <col min="19" max="19" width="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.28515625" style="76" customWidth="1"/>
     <col min="20" max="20" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13" customWidth="1"/>
-    <col min="22" max="22" width="7.85546875" customWidth="1"/>
+    <col min="22" max="22" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="6.7109375" customWidth="1"/>
     <col min="25" max="25" width="32.140625" customWidth="1"/>
@@ -3480,22 +3520,22 @@
       <c r="R1" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="S1" s="29" t="s">
+      <c r="S1" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="T1" s="29" t="s">
+      <c r="T1" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="U1" s="29" t="s">
+      <c r="U1" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="V1" s="29" t="s">
+      <c r="V1" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="29" t="s">
+      <c r="W1" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="X1" s="47" t="s">
+      <c r="X1" s="78" t="s">
         <v>8</v>
       </c>
       <c r="Y1" s="49" t="s">
@@ -3514,7 +3554,7 @@
         <v>82</v>
       </c>
       <c r="AD1" s="49" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3576,7 +3616,7 @@
       <c r="R2" s="21" t="s">
         <v>285</v>
       </c>
-      <c r="S2" s="21" t="s">
+      <c r="S2" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T2" s="21" t="str">
@@ -3592,7 +3632,7 @@
         <v>Compactação</v>
       </c>
       <c r="W2" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X2" s="54" t="str">
         <f t="shared" ref="X2:X51" si="5">CONCATENATE("Key-GEO-",A2)</f>
@@ -3676,7 +3716,7 @@
       <c r="R3" s="21" t="s">
         <v>286</v>
       </c>
-      <c r="S3" s="21" t="s">
+      <c r="S3" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T3" s="21" t="str">
@@ -3692,7 +3732,7 @@
         <v>Compactação</v>
       </c>
       <c r="W3" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X3" s="54" t="str">
         <f t="shared" si="5"/>
@@ -3776,7 +3816,7 @@
       <c r="R4" s="21" t="s">
         <v>287</v>
       </c>
-      <c r="S4" s="21" t="s">
+      <c r="S4" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T4" s="21" t="str">
@@ -3792,7 +3832,7 @@
         <v>Compactação</v>
       </c>
       <c r="W4" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X4" s="54" t="str">
         <f t="shared" si="5"/>
@@ -3876,7 +3916,7 @@
       <c r="R5" s="21" t="s">
         <v>288</v>
       </c>
-      <c r="S5" s="21" t="s">
+      <c r="S5" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T5" s="21" t="str">
@@ -3892,7 +3932,7 @@
         <v>Compactação</v>
       </c>
       <c r="W5" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X5" s="54" t="str">
         <f t="shared" si="5"/>
@@ -3976,7 +4016,7 @@
       <c r="R6" s="21" t="s">
         <v>289</v>
       </c>
-      <c r="S6" s="21" t="s">
+      <c r="S6" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T6" s="21" t="str">
@@ -3992,7 +4032,7 @@
         <v>Compactação</v>
       </c>
       <c r="W6" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X6" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4076,7 +4116,7 @@
       <c r="R7" s="21" t="s">
         <v>290</v>
       </c>
-      <c r="S7" s="21" t="s">
+      <c r="S7" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T7" s="21" t="str">
@@ -4092,7 +4132,7 @@
         <v>Compactação</v>
       </c>
       <c r="W7" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X7" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4176,7 +4216,7 @@
       <c r="R8" s="21" t="s">
         <v>291</v>
       </c>
-      <c r="S8" s="21" t="s">
+      <c r="S8" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T8" s="21" t="str">
@@ -4192,7 +4232,7 @@
         <v>Compactação</v>
       </c>
       <c r="W8" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X8" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4276,7 +4316,7 @@
       <c r="R9" s="21" t="s">
         <v>292</v>
       </c>
-      <c r="S9" s="21" t="s">
+      <c r="S9" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T9" s="21" t="str">
@@ -4292,7 +4332,7 @@
         <v>Escavações</v>
       </c>
       <c r="W9" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X9" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4376,7 +4416,7 @@
       <c r="R10" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="S10" s="21" t="s">
+      <c r="S10" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T10" s="21" t="str">
@@ -4392,7 +4432,7 @@
         <v>Escavações</v>
       </c>
       <c r="W10" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X10" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4476,7 +4516,7 @@
       <c r="R11" s="21" t="s">
         <v>294</v>
       </c>
-      <c r="S11" s="21" t="s">
+      <c r="S11" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T11" s="21" t="str">
@@ -4492,7 +4532,7 @@
         <v>Escavações</v>
       </c>
       <c r="W11" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X11" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4576,7 +4616,7 @@
       <c r="R12" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="S12" s="21" t="s">
+      <c r="S12" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T12" s="21" t="str">
@@ -4592,7 +4632,7 @@
         <v>Escavações</v>
       </c>
       <c r="W12" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X12" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4676,7 +4716,7 @@
       <c r="R13" s="21" t="s">
         <v>296</v>
       </c>
-      <c r="S13" s="21" t="s">
+      <c r="S13" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T13" s="21" t="str">
@@ -4692,7 +4732,7 @@
         <v>Escavações</v>
       </c>
       <c r="W13" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X13" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4776,7 +4816,7 @@
       <c r="R14" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="S14" s="21" t="s">
+      <c r="S14" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T14" s="21" t="str">
@@ -4792,7 +4832,7 @@
         <v>Escavações</v>
       </c>
       <c r="W14" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X14" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4876,7 +4916,7 @@
       <c r="R15" s="21" t="s">
         <v>298</v>
       </c>
-      <c r="S15" s="21" t="s">
+      <c r="S15" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T15" s="21" t="str">
@@ -4892,7 +4932,7 @@
         <v>Escavações</v>
       </c>
       <c r="W15" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X15" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4976,7 +5016,7 @@
       <c r="R16" s="21" t="s">
         <v>299</v>
       </c>
-      <c r="S16" s="21" t="s">
+      <c r="S16" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T16" s="21" t="str">
@@ -4992,7 +5032,7 @@
         <v>Escavações</v>
       </c>
       <c r="W16" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X16" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5076,7 +5116,7 @@
       <c r="R17" s="21" t="s">
         <v>300</v>
       </c>
-      <c r="S17" s="21" t="s">
+      <c r="S17" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T17" s="21" t="str">
@@ -5092,7 +5132,7 @@
         <v>Escavações</v>
       </c>
       <c r="W17" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X17" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5176,7 +5216,7 @@
       <c r="R18" s="21" t="s">
         <v>301</v>
       </c>
-      <c r="S18" s="21" t="s">
+      <c r="S18" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T18" s="21" t="str">
@@ -5192,7 +5232,7 @@
         <v>Escavações</v>
       </c>
       <c r="W18" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X18" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5276,7 +5316,7 @@
       <c r="R19" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="S19" s="21" t="s">
+      <c r="S19" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T19" s="21" t="str">
@@ -5292,7 +5332,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W19" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X19" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5376,7 +5416,7 @@
       <c r="R20" s="21" t="s">
         <v>302</v>
       </c>
-      <c r="S20" s="21" t="s">
+      <c r="S20" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T20" s="21" t="str">
@@ -5392,7 +5432,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W20" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X20" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5476,7 +5516,7 @@
       <c r="R21" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="S21" s="21" t="s">
+      <c r="S21" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T21" s="21" t="str">
@@ -5492,7 +5532,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W21" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X21" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5576,7 +5616,7 @@
       <c r="R22" s="21" t="s">
         <v>304</v>
       </c>
-      <c r="S22" s="21" t="s">
+      <c r="S22" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T22" s="21" t="str">
@@ -5592,7 +5632,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W22" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X22" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5676,7 +5716,7 @@
       <c r="R23" s="21" t="s">
         <v>305</v>
       </c>
-      <c r="S23" s="21" t="s">
+      <c r="S23" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T23" s="21" t="str">
@@ -5692,7 +5732,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W23" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X23" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5776,7 +5816,7 @@
       <c r="R24" s="21" t="s">
         <v>306</v>
       </c>
-      <c r="S24" s="21" t="s">
+      <c r="S24" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T24" s="21" t="str">
@@ -5792,7 +5832,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W24" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X24" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5876,7 +5916,7 @@
       <c r="R25" s="21" t="s">
         <v>307</v>
       </c>
-      <c r="S25" s="21" t="s">
+      <c r="S25" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T25" s="21" t="str">
@@ -5892,7 +5932,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W25" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X25" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5976,7 +6016,7 @@
       <c r="R26" s="21" t="s">
         <v>308</v>
       </c>
-      <c r="S26" s="21" t="s">
+      <c r="S26" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T26" s="21" t="str">
@@ -5992,7 +6032,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W26" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X26" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6076,7 +6116,7 @@
       <c r="R27" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="S27" s="21" t="s">
+      <c r="S27" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T27" s="21" t="str">
@@ -6092,7 +6132,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W27" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X27" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6176,7 +6216,7 @@
       <c r="R28" s="21" t="s">
         <v>310</v>
       </c>
-      <c r="S28" s="21" t="s">
+      <c r="S28" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T28" s="21" t="str">
@@ -6192,7 +6232,7 @@
         <v>Pontos.do.Modelo</v>
       </c>
       <c r="W28" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X28" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6276,7 +6316,7 @@
       <c r="R29" s="21" t="s">
         <v>311</v>
       </c>
-      <c r="S29" s="21" t="s">
+      <c r="S29" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T29" s="21" t="str">
@@ -6292,7 +6332,7 @@
         <v>Pontos.do.Modelo</v>
       </c>
       <c r="W29" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X29" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6376,7 +6416,7 @@
       <c r="R30" s="21" t="s">
         <v>312</v>
       </c>
-      <c r="S30" s="21" t="s">
+      <c r="S30" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T30" s="21" t="str">
@@ -6392,7 +6432,7 @@
         <v>Pontos.do.Modelo</v>
       </c>
       <c r="W30" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X30" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6476,7 +6516,7 @@
       <c r="R31" s="21" t="s">
         <v>313</v>
       </c>
-      <c r="S31" s="21" t="s">
+      <c r="S31" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T31" s="21" t="str">
@@ -6492,7 +6532,7 @@
         <v>Pontos.do.Modelo</v>
       </c>
       <c r="W31" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X31" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6576,7 +6616,7 @@
       <c r="R32" s="21" t="s">
         <v>314</v>
       </c>
-      <c r="S32" s="21" t="s">
+      <c r="S32" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T32" s="21" t="str">
@@ -6592,7 +6632,7 @@
         <v>Sondagens</v>
       </c>
       <c r="W32" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X32" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6676,7 +6716,7 @@
       <c r="R33" s="21" t="s">
         <v>315</v>
       </c>
-      <c r="S33" s="21" t="s">
+      <c r="S33" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T33" s="21" t="str">
@@ -6692,7 +6732,7 @@
         <v>Sondagens</v>
       </c>
       <c r="W33" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X33" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6776,7 +6816,7 @@
       <c r="R34" s="21" t="s">
         <v>316</v>
       </c>
-      <c r="S34" s="21" t="s">
+      <c r="S34" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T34" s="21" t="str">
@@ -6792,7 +6832,7 @@
         <v>Topografia</v>
       </c>
       <c r="W34" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X34" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6876,7 +6916,7 @@
       <c r="R35" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="S35" s="21" t="s">
+      <c r="S35" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T35" s="21" t="str">
@@ -6892,7 +6932,7 @@
         <v>Topografia</v>
       </c>
       <c r="W35" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X35" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6976,7 +7016,7 @@
       <c r="R36" s="21" t="s">
         <v>318</v>
       </c>
-      <c r="S36" s="21" t="s">
+      <c r="S36" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T36" s="21" t="str">
@@ -6992,7 +7032,7 @@
         <v>Topografia</v>
       </c>
       <c r="W36" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X36" s="54" t="str">
         <f t="shared" si="5"/>
@@ -7076,7 +7116,7 @@
       <c r="R37" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="S37" s="21" t="s">
+      <c r="S37" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T37" s="21" t="str">
@@ -7092,7 +7132,7 @@
         <v>Topografia</v>
       </c>
       <c r="W37" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X37" s="54" t="str">
         <f t="shared" si="5"/>
@@ -7176,7 +7216,7 @@
       <c r="R38" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="S38" s="21" t="s">
+      <c r="S38" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T38" s="21" t="str">
@@ -7192,7 +7232,7 @@
         <v>Topografia</v>
       </c>
       <c r="W38" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X38" s="54" t="str">
         <f t="shared" si="5"/>
@@ -7276,7 +7316,7 @@
       <c r="R39" s="21" t="s">
         <v>321</v>
       </c>
-      <c r="S39" s="21" t="s">
+      <c r="S39" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T39" s="21" t="str">
@@ -7292,7 +7332,7 @@
         <v>Topografia</v>
       </c>
       <c r="W39" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X39" s="54" t="str">
         <f t="shared" si="5"/>
@@ -7376,7 +7416,7 @@
       <c r="R40" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="S40" s="21" t="s">
+      <c r="S40" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T40" s="21" t="str">
@@ -7392,7 +7432,7 @@
         <v>Topografia</v>
       </c>
       <c r="W40" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X40" s="54" t="str">
         <f t="shared" si="5"/>
@@ -7476,7 +7516,7 @@
       <c r="R41" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="S41" s="21" t="s">
+      <c r="S41" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T41" s="21" t="str">
@@ -7492,7 +7532,7 @@
         <v>Topografia</v>
       </c>
       <c r="W41" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X41" s="54" t="str">
         <f t="shared" si="5"/>
@@ -7576,7 +7616,7 @@
       <c r="R42" s="21" t="s">
         <v>324</v>
       </c>
-      <c r="S42" s="21" t="s">
+      <c r="S42" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T42" s="21" t="str">
@@ -7592,7 +7632,7 @@
         <v>Topografia</v>
       </c>
       <c r="W42" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X42" s="54" t="str">
         <f t="shared" si="5"/>
@@ -7676,7 +7716,7 @@
       <c r="R43" s="21" t="s">
         <v>325</v>
       </c>
-      <c r="S43" s="21" t="s">
+      <c r="S43" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T43" s="21" t="str">
@@ -7692,7 +7732,7 @@
         <v>Curvas.de.Nível</v>
       </c>
       <c r="W43" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X43" s="54" t="str">
         <f t="shared" si="5"/>
@@ -7776,7 +7816,7 @@
       <c r="R44" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="S44" s="21" t="s">
+      <c r="S44" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T44" s="21" t="str">
@@ -7792,7 +7832,7 @@
         <v>Curvas.de.Nível</v>
       </c>
       <c r="W44" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X44" s="54" t="str">
         <f t="shared" si="5"/>
@@ -7876,7 +7916,7 @@
       <c r="R45" s="21" t="s">
         <v>327</v>
       </c>
-      <c r="S45" s="21" t="s">
+      <c r="S45" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T45" s="21" t="str">
@@ -7892,7 +7932,7 @@
         <v>Curvas.de.Nível</v>
       </c>
       <c r="W45" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X45" s="54" t="str">
         <f t="shared" si="5"/>
@@ -7976,7 +8016,7 @@
       <c r="R46" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="S46" s="21" t="s">
+      <c r="S46" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T46" s="21" t="str">
@@ -7992,7 +8032,7 @@
         <v>Loteamento</v>
       </c>
       <c r="W46" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X46" s="54" t="str">
         <f t="shared" si="5"/>
@@ -8076,7 +8116,7 @@
       <c r="R47" s="21" t="s">
         <v>328</v>
       </c>
-      <c r="S47" s="21" t="s">
+      <c r="S47" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T47" s="21" t="str">
@@ -8092,7 +8132,7 @@
         <v>Loteamento</v>
       </c>
       <c r="W47" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X47" s="54" t="str">
         <f t="shared" si="5"/>
@@ -8176,7 +8216,7 @@
       <c r="R48" s="21" t="s">
         <v>329</v>
       </c>
-      <c r="S48" s="21" t="s">
+      <c r="S48" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T48" s="21" t="str">
@@ -8192,7 +8232,7 @@
         <v>Paisagismo</v>
       </c>
       <c r="W48" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X48" s="54" t="str">
         <f t="shared" si="5"/>
@@ -8276,7 +8316,7 @@
       <c r="R49" s="21" t="s">
         <v>330</v>
       </c>
-      <c r="S49" s="21" t="s">
+      <c r="S49" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T49" s="21" t="str">
@@ -8292,7 +8332,7 @@
         <v>Paisagismo</v>
       </c>
       <c r="W49" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X49" s="54" t="str">
         <f t="shared" si="5"/>
@@ -8376,7 +8416,7 @@
       <c r="R50" s="21" t="s">
         <v>331</v>
       </c>
-      <c r="S50" s="21" t="s">
+      <c r="S50" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T50" s="21" t="str">
@@ -8392,7 +8432,7 @@
         <v>Paisagismo</v>
       </c>
       <c r="W50" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X50" s="54" t="str">
         <f t="shared" si="5"/>
@@ -8476,7 +8516,7 @@
       <c r="R51" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="S51" s="21" t="s">
+      <c r="S51" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T51" s="21" t="str">
@@ -8492,7 +8532,7 @@
         <v>Paisagismo</v>
       </c>
       <c r="W51" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X51" s="54" t="str">
         <f t="shared" si="5"/>
@@ -8525,16 +8565,16 @@
         <v>382</v>
       </c>
       <c r="C52" s="59" t="s">
+        <v>407</v>
+      </c>
+      <c r="D52" s="59" t="s">
         <v>410</v>
       </c>
-      <c r="D52" s="59" t="s">
-        <v>413</v>
-      </c>
       <c r="E52" s="59" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="F52" s="59" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G52" s="60" t="s">
         <v>9</v>
@@ -8568,15 +8608,15 @@
         <v>Terreno</v>
       </c>
       <c r="P52" s="61" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="Q52" s="61" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="R52" s="18" t="s">
-        <v>415</v>
-      </c>
-      <c r="S52" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="S52" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T52" s="18" t="str">
@@ -8592,7 +8632,7 @@
         <v>Solos</v>
       </c>
       <c r="W52" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X52" s="54" t="str">
         <f t="shared" ref="X52:X57" si="20">CONCATENATE("Key-GEO-",A52)</f>
@@ -8617,82 +8657,82 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:30" s="75" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="46">
         <v>53</v>
       </c>
       <c r="B53" s="58" t="s">
-        <v>382</v>
+        <v>434</v>
       </c>
       <c r="C53" s="59" t="s">
-        <v>383</v>
+        <v>435</v>
       </c>
       <c r="D53" s="59" t="s">
-        <v>385</v>
+        <v>436</v>
       </c>
       <c r="E53" s="59" t="s">
-        <v>384</v>
+        <v>437</v>
       </c>
       <c r="F53" s="59" t="s">
+        <v>413</v>
+      </c>
+      <c r="G53" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H53" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I53" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J53" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K53" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L53" s="61" t="str">
+        <f t="shared" ref="L53:M57" si="21">CONCATENATE("", C53)</f>
+        <v>API.Plataforma</v>
+      </c>
+      <c r="M53" s="61" t="str">
+        <f t="shared" si="21"/>
+        <v>API.Macros</v>
+      </c>
+      <c r="N53" s="61" t="str">
+        <f t="shared" ref="N53:O57" si="22">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E53),"."," ")," De "," de "))</f>
+        <v>API Método</v>
+      </c>
+      <c r="O53" s="61" t="str">
+        <f t="shared" si="22"/>
+        <v>Função Auxiliar</v>
+      </c>
+      <c r="P53" s="18" t="s">
+        <v>414</v>
+      </c>
+      <c r="Q53" s="18" t="s">
+        <v>415</v>
+      </c>
+      <c r="R53" s="18" t="s">
         <v>416</v>
       </c>
-      <c r="G53" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="H53" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="I53" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="J53" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="K53" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="L53" s="61" t="str">
-        <f t="shared" si="13"/>
-        <v>De API</v>
-      </c>
-      <c r="M53" s="61" t="str">
-        <f t="shared" si="13"/>
-        <v>Macros</v>
-      </c>
-      <c r="N53" s="61" t="str">
-        <f t="shared" si="13"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O53" s="61" t="str">
-        <f t="shared" si="13"/>
-        <v>Função Auxiliar</v>
-      </c>
-      <c r="P53" s="18" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q53" s="18" t="s">
-        <v>418</v>
-      </c>
-      <c r="R53" s="18" t="s">
-        <v>419</v>
-      </c>
-      <c r="S53" s="18" t="s">
+      <c r="S53" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T53" s="18" t="str">
         <f t="shared" si="17"/>
-        <v>De API</v>
+        <v>API Plataforma</v>
       </c>
       <c r="U53" s="18" t="str">
         <f t="shared" si="17"/>
-        <v>Macros</v>
+        <v>API Macros</v>
       </c>
       <c r="V53" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>Métodos</v>
+        <v>API Método</v>
       </c>
       <c r="W53" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X53" s="54" t="str">
         <f t="shared" si="20"/>
@@ -8717,82 +8757,82 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:30" s="75" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="46">
         <v>54</v>
       </c>
       <c r="B54" s="58" t="s">
-        <v>382</v>
+        <v>434</v>
       </c>
       <c r="C54" s="59" t="s">
-        <v>383</v>
+        <v>435</v>
       </c>
       <c r="D54" s="59" t="s">
-        <v>385</v>
+        <v>436</v>
       </c>
       <c r="E54" s="59" t="s">
-        <v>384</v>
+        <v>437</v>
       </c>
       <c r="F54" s="59" t="s">
+        <v>417</v>
+      </c>
+      <c r="G54" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H54" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I54" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J54" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K54" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L54" s="61" t="str">
+        <f t="shared" si="21"/>
+        <v>API.Plataforma</v>
+      </c>
+      <c r="M54" s="61" t="str">
+        <f t="shared" si="21"/>
+        <v>API.Macros</v>
+      </c>
+      <c r="N54" s="61" t="str">
+        <f t="shared" si="22"/>
+        <v>API Método</v>
+      </c>
+      <c r="O54" s="61" t="str">
+        <f t="shared" si="22"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P54" s="18" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q54" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="R54" s="18" t="s">
         <v>420</v>
       </c>
-      <c r="G54" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="H54" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="I54" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="J54" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="K54" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="L54" s="61" t="str">
-        <f t="shared" si="13"/>
-        <v>De API</v>
-      </c>
-      <c r="M54" s="61" t="str">
-        <f t="shared" si="13"/>
-        <v>Macros</v>
-      </c>
-      <c r="N54" s="61" t="str">
-        <f t="shared" si="13"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O54" s="61" t="str">
-        <f t="shared" si="13"/>
-        <v>Função Global</v>
-      </c>
-      <c r="P54" s="18" t="s">
-        <v>421</v>
-      </c>
-      <c r="Q54" s="18" t="s">
-        <v>422</v>
-      </c>
-      <c r="R54" s="18" t="s">
-        <v>423</v>
-      </c>
-      <c r="S54" s="18" t="s">
+      <c r="S54" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T54" s="18" t="str">
         <f t="shared" si="17"/>
-        <v>De API</v>
+        <v>API Plataforma</v>
       </c>
       <c r="U54" s="18" t="str">
         <f t="shared" si="17"/>
-        <v>Macros</v>
+        <v>API Macros</v>
       </c>
       <c r="V54" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>Métodos</v>
+        <v>API Método</v>
       </c>
       <c r="W54" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X54" s="54" t="str">
         <f t="shared" si="20"/>
@@ -8817,82 +8857,82 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:30" s="75" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="46">
         <v>55</v>
       </c>
       <c r="B55" s="58" t="s">
-        <v>382</v>
+        <v>434</v>
       </c>
       <c r="C55" s="59" t="s">
-        <v>383</v>
+        <v>435</v>
       </c>
       <c r="D55" s="59" t="s">
-        <v>385</v>
+        <v>436</v>
       </c>
       <c r="E55" s="59" t="s">
-        <v>384</v>
+        <v>437</v>
       </c>
       <c r="F55" s="59" t="s">
+        <v>421</v>
+      </c>
+      <c r="G55" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H55" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I55" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J55" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K55" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L55" s="61" t="str">
+        <f t="shared" si="21"/>
+        <v>API.Plataforma</v>
+      </c>
+      <c r="M55" s="61" t="str">
+        <f t="shared" si="21"/>
+        <v>API.Macros</v>
+      </c>
+      <c r="N55" s="61" t="str">
+        <f t="shared" si="22"/>
+        <v>API Método</v>
+      </c>
+      <c r="O55" s="61" t="str">
+        <f t="shared" si="22"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P55" s="18" t="s">
+        <v>422</v>
+      </c>
+      <c r="Q55" s="18" t="s">
+        <v>423</v>
+      </c>
+      <c r="R55" s="18" t="s">
         <v>424</v>
       </c>
-      <c r="G55" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="H55" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="I55" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="J55" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="K55" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="L55" s="61" t="str">
-        <f t="shared" si="13"/>
-        <v>De API</v>
-      </c>
-      <c r="M55" s="61" t="str">
-        <f t="shared" si="13"/>
-        <v>Macros</v>
-      </c>
-      <c r="N55" s="61" t="str">
-        <f t="shared" si="13"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O55" s="61" t="str">
-        <f t="shared" si="13"/>
-        <v>Função Local</v>
-      </c>
-      <c r="P55" s="18" t="s">
-        <v>425</v>
-      </c>
-      <c r="Q55" s="18" t="s">
-        <v>426</v>
-      </c>
-      <c r="R55" s="18" t="s">
-        <v>427</v>
-      </c>
-      <c r="S55" s="18" t="s">
+      <c r="S55" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T55" s="18" t="str">
         <f t="shared" si="17"/>
-        <v>De API</v>
+        <v>API Plataforma</v>
       </c>
       <c r="U55" s="18" t="str">
         <f t="shared" si="17"/>
-        <v>Macros</v>
+        <v>API Macros</v>
       </c>
       <c r="V55" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>Métodos</v>
+        <v>API Método</v>
       </c>
       <c r="W55" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X55" s="54" t="str">
         <f t="shared" si="20"/>
@@ -8917,82 +8957,82 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:30" s="75" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="46">
         <v>56</v>
       </c>
       <c r="B56" s="58" t="s">
-        <v>382</v>
+        <v>434</v>
       </c>
       <c r="C56" s="59" t="s">
-        <v>383</v>
+        <v>435</v>
       </c>
       <c r="D56" s="59" t="s">
-        <v>385</v>
+        <v>436</v>
       </c>
       <c r="E56" s="59" t="s">
-        <v>384</v>
+        <v>437</v>
       </c>
       <c r="F56" s="59" t="s">
+        <v>425</v>
+      </c>
+      <c r="G56" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H56" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I56" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J56" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K56" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L56" s="61" t="str">
+        <f t="shared" si="21"/>
+        <v>API.Plataforma</v>
+      </c>
+      <c r="M56" s="61" t="str">
+        <f t="shared" si="21"/>
+        <v>API.Macros</v>
+      </c>
+      <c r="N56" s="61" t="str">
+        <f t="shared" si="22"/>
+        <v>API Método</v>
+      </c>
+      <c r="O56" s="61" t="str">
+        <f t="shared" si="22"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P56" s="18" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q56" s="18" t="s">
+        <v>427</v>
+      </c>
+      <c r="R56" s="18" t="s">
         <v>428</v>
       </c>
-      <c r="G56" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="H56" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="I56" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="J56" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="K56" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="L56" s="61" t="str">
-        <f t="shared" si="13"/>
-        <v>De API</v>
-      </c>
-      <c r="M56" s="61" t="str">
-        <f t="shared" si="13"/>
-        <v>Macros</v>
-      </c>
-      <c r="N56" s="61" t="str">
-        <f t="shared" si="13"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O56" s="61" t="str">
-        <f t="shared" si="13"/>
-        <v>Função Filtro</v>
-      </c>
-      <c r="P56" s="18" t="s">
-        <v>429</v>
-      </c>
-      <c r="Q56" s="18" t="s">
-        <v>430</v>
-      </c>
-      <c r="R56" s="18" t="s">
-        <v>431</v>
-      </c>
-      <c r="S56" s="18" t="s">
+      <c r="S56" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T56" s="18" t="str">
         <f t="shared" si="17"/>
-        <v>De API</v>
+        <v>API Plataforma</v>
       </c>
       <c r="U56" s="18" t="str">
         <f t="shared" si="17"/>
-        <v>Macros</v>
+        <v>API Macros</v>
       </c>
       <c r="V56" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>Métodos</v>
+        <v>API Método</v>
       </c>
       <c r="W56" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X56" s="54" t="str">
         <f t="shared" si="20"/>
@@ -9017,82 +9057,82 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:30" s="75" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="46">
         <v>57</v>
       </c>
       <c r="B57" s="58" t="s">
-        <v>382</v>
+        <v>434</v>
       </c>
       <c r="C57" s="59" t="s">
-        <v>383</v>
+        <v>435</v>
       </c>
       <c r="D57" s="59" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="E57" s="59" t="s">
+        <v>439</v>
+      </c>
+      <c r="F57" s="59" t="s">
+        <v>429</v>
+      </c>
+      <c r="G57" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H57" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="I57" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J57" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="K57" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L57" s="61" t="str">
+        <f t="shared" si="21"/>
+        <v>API.Plataforma</v>
+      </c>
+      <c r="M57" s="61" t="str">
+        <f t="shared" si="21"/>
+        <v>API.Macros.Visuais</v>
+      </c>
+      <c r="N57" s="61" t="str">
+        <f t="shared" si="22"/>
+        <v>API Método Visual</v>
+      </c>
+      <c r="O57" s="61" t="str">
+        <f t="shared" si="22"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P57" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="Q57" s="18" t="s">
+        <v>431</v>
+      </c>
+      <c r="R57" s="18" t="s">
         <v>432</v>
       </c>
-      <c r="F57" s="59" t="s">
-        <v>433</v>
-      </c>
-      <c r="G57" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="H57" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="I57" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="J57" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="K57" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="L57" s="61" t="str">
-        <f t="shared" si="13"/>
-        <v>De API</v>
-      </c>
-      <c r="M57" s="61" t="str">
-        <f t="shared" si="13"/>
-        <v>Macros</v>
-      </c>
-      <c r="N57" s="61" t="str">
-        <f t="shared" si="13"/>
-        <v>Códigos Visuais</v>
-      </c>
-      <c r="O57" s="61" t="str">
-        <f t="shared" si="13"/>
-        <v>Bloco de Código</v>
-      </c>
-      <c r="P57" s="18" t="s">
-        <v>434</v>
-      </c>
-      <c r="Q57" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="R57" s="18" t="s">
-        <v>436</v>
-      </c>
-      <c r="S57" s="18" t="s">
+      <c r="S57" s="74" t="s">
         <v>9</v>
       </c>
       <c r="T57" s="18" t="str">
         <f t="shared" si="17"/>
-        <v>De API</v>
+        <v>API Plataforma</v>
       </c>
       <c r="U57" s="18" t="str">
         <f t="shared" si="17"/>
-        <v>Macros</v>
+        <v>API Macros Visuais</v>
       </c>
       <c r="V57" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>Códigos Visuais</v>
+        <v>API Método Visual</v>
       </c>
       <c r="W57" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="X57" s="54" t="str">
         <f t="shared" si="20"/>
@@ -9122,132 +9162,130 @@
     <sortCondition ref="E1:E805"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B57">
-    <cfRule type="cellIs" dxfId="71" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:B52 A53:A57">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:X1048576 A1:Q1 S1:X1 C2:E2 P2 AE2:XFD2 D3:E8 C3:C51 D9:D27">
-    <cfRule type="cellIs" dxfId="70" priority="262" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="265" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E57:F57">
-    <cfRule type="duplicateValues" dxfId="69" priority="2"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F2:F27">
-    <cfRule type="duplicateValues" dxfId="68" priority="1050"/>
-    <cfRule type="cellIs" dxfId="67" priority="68" operator="equal">
+    <cfRule type="duplicateValues" dxfId="72" priority="1053"/>
+    <cfRule type="cellIs" dxfId="71" priority="71" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28:F45 Q2:Q51 P28:P29 AE28:XFD29 P34:P41 AE34:XFD41 P43:P45 AE43:XFD45">
-    <cfRule type="cellIs" dxfId="66" priority="129" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="132" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28:F45">
-    <cfRule type="duplicateValues" dxfId="65" priority="1032"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="1031"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="1029"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="1035"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="1034"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="1032"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F46:F47">
-    <cfRule type="duplicateValues" dxfId="62" priority="999"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="1002"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F51">
-    <cfRule type="duplicateValues" dxfId="61" priority="1035"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="1038"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52">
-    <cfRule type="duplicateValues" dxfId="60" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F53:F56">
-    <cfRule type="duplicateValues" dxfId="59" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F58:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="58" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="266"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F58:F1048576 F1:F51">
-    <cfRule type="duplicateValues" dxfId="57" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F58:F1048576">
-    <cfRule type="duplicateValues" dxfId="56" priority="792"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="779"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="772"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="764"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="255"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="795"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="782"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="775"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="767"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="258"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R52">
-    <cfRule type="cellIs" dxfId="51" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X58:X1048576 X1">
-    <cfRule type="duplicateValues" dxfId="50" priority="591"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="594"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y50">
-    <cfRule type="duplicateValues" dxfId="49" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="duplicateValues" dxfId="45" priority="93"/>
-    <cfRule type="cellIs" dxfId="44" priority="92" operator="equal">
+    <cfRule type="duplicateValues" dxfId="49" priority="96"/>
+    <cfRule type="cellIs" dxfId="48" priority="95" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA3">
-    <cfRule type="duplicateValues" dxfId="43" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="91"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA3:AA8 AA17:AA27 AA10:AA14">
-    <cfRule type="duplicateValues" dxfId="39" priority="1047"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="1050"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA4:AA8 AA19:AA27 AA10:AA14">
-    <cfRule type="duplicateValues" dxfId="38" priority="1044"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="1047"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA4:AA8 AA19:AA27">
-    <cfRule type="duplicateValues" dxfId="37" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA9">
-    <cfRule type="duplicateValues" dxfId="36" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA10:AA14">
-    <cfRule type="duplicateValues" dxfId="31" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA15:AA16">
+    <cfRule type="duplicateValues" dxfId="31" priority="40"/>
     <cfRule type="duplicateValues" dxfId="30" priority="46"/>
     <cfRule type="duplicateValues" dxfId="29" priority="45"/>
     <cfRule type="duplicateValues" dxfId="28" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA15:AA16">
     <cfRule type="duplicateValues" dxfId="27" priority="43"/>
     <cfRule type="duplicateValues" dxfId="26" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA17:AA18">
-    <cfRule type="duplicateValues" dxfId="19" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA19:AA27">
-    <cfRule type="duplicateValues" dxfId="14" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1:XFD1 AB58:XFD1048576">
-    <cfRule type="cellIs" dxfId="13" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F53:F57">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9397,7 +9435,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9469,15 +9507,15 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="15" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -9715,10 +9753,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>387</v>
-      </c>
-      <c r="C3" s="74" t="s">
-        <v>428</v>
+        <v>384</v>
+      </c>
+      <c r="C3" s="59" t="s">
+        <v>425</v>
       </c>
       <c r="D3" s="64" t="s">
         <v>9</v>
@@ -9742,26 +9780,26 @@
         <v>78</v>
       </c>
       <c r="K3" s="67" t="s">
+        <v>385</v>
+      </c>
+      <c r="L3" s="69" t="s">
+        <v>386</v>
+      </c>
+      <c r="M3" s="45" t="s">
+        <v>387</v>
+      </c>
+      <c r="N3" s="69" t="s">
         <v>388</v>
       </c>
-      <c r="L3" s="69" t="s">
+      <c r="O3" s="45" t="s">
         <v>389</v>
-      </c>
-      <c r="M3" s="45" t="s">
-        <v>390</v>
-      </c>
-      <c r="N3" s="69" t="s">
-        <v>391</v>
-      </c>
-      <c r="O3" s="45" t="s">
-        <v>392</v>
       </c>
       <c r="P3" s="71" t="str">
         <f t="shared" ref="P3:P7" si="0">IF(Q3="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
       <c r="Q3" s="72" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="R3" s="66" t="s">
         <v>9</v>
@@ -9817,10 +9855,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>394</v>
-      </c>
-      <c r="C4" s="74" t="s">
-        <v>428</v>
+        <v>391</v>
+      </c>
+      <c r="C4" s="59" t="s">
+        <v>425</v>
       </c>
       <c r="D4" s="64" t="s">
         <v>9</v>
@@ -9844,26 +9882,26 @@
         <v>78</v>
       </c>
       <c r="K4" s="67" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="L4" s="69" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="M4" s="45" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="N4" s="69" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="O4" s="45" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="P4" s="71" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q4" s="72" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="R4" s="66" t="s">
         <v>9</v>
@@ -9919,10 +9957,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>398</v>
-      </c>
-      <c r="C5" s="74" t="s">
-        <v>428</v>
+        <v>395</v>
+      </c>
+      <c r="C5" s="59" t="s">
+        <v>425</v>
       </c>
       <c r="D5" s="64" t="s">
         <v>9</v>
@@ -9946,26 +9984,26 @@
         <v>78</v>
       </c>
       <c r="K5" s="67" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="L5" s="69" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="M5" s="45" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="N5" s="69" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="O5" s="45" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="P5" s="71" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q5" s="72" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="R5" s="66" t="s">
         <v>9</v>
@@ -10021,10 +10059,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>402</v>
-      </c>
-      <c r="C6" s="74" t="s">
-        <v>428</v>
+        <v>399</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>425</v>
       </c>
       <c r="D6" s="64" t="s">
         <v>9</v>
@@ -10048,26 +10086,26 @@
         <v>78</v>
       </c>
       <c r="K6" s="67" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="L6" s="69" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="M6" s="45" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="N6" s="69" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="O6" s="45" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="P6" s="71" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q6" s="72" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="R6" s="66" t="s">
         <v>9</v>
@@ -10123,10 +10161,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>406</v>
-      </c>
-      <c r="C7" s="74" t="s">
-        <v>428</v>
+        <v>403</v>
+      </c>
+      <c r="C7" s="59" t="s">
+        <v>425</v>
       </c>
       <c r="D7" s="64" t="s">
         <v>9</v>
@@ -10150,26 +10188,26 @@
         <v>78</v>
       </c>
       <c r="K7" s="67" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="L7" s="69" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="M7" s="45" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="N7" s="69" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="O7" s="45" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="P7" s="71" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q7" s="72" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="R7" s="66" t="s">
         <v>9</v>
@@ -10223,35 +10261,35 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1 A2:B2 A8:XFD1048576 H2:O2 AH2:XFD2 A3:A7">
-    <cfRule type="cellIs" dxfId="8" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B2 B8:B1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="1031"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1031"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B7">
-    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:G7">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:I7">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:Q2">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:AG7">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/EST/Ontologia_Geotecnica.xlsx
+++ b/Versão5/EST/Ontologia_Geotecnica.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11864C92-5175-44CD-A56A-FB9770B04081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E317704F-747E-48FB-A7EA-294A896D1701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1619" uniqueCount="486">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -238,28 +238,7 @@
     <t>Escola Politécnica da UFRJ</t>
   </si>
   <si>
-    <t>NormaNúmero</t>
-  </si>
-  <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>Edição</t>
-  </si>
-  <si>
-    <t>ISBN</t>
-  </si>
-  <si>
-    <t>NormaEscopo</t>
-  </si>
-  <si>
-    <t>NormaReferência1</t>
-  </si>
-  <si>
-    <t>NormaReferência2</t>
-  </si>
-  <si>
-    <t>NormaReferência3</t>
   </si>
   <si>
     <t>Observações</t>
@@ -1392,13 +1371,172 @@
   </si>
   <si>
     <t>API.Método.Visual</t>
+  </si>
+  <si>
+    <t>Norma-Número</t>
+  </si>
+  <si>
+    <t>Norma-Edição</t>
+  </si>
+  <si>
+    <t>Norma-ISBN</t>
+  </si>
+  <si>
+    <t>Norma-Escopo</t>
+  </si>
+  <si>
+    <t>Norma-Referência-01</t>
+  </si>
+  <si>
+    <t>Norma-Referência-02</t>
+  </si>
+  <si>
+    <t>Norma-Referência-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-01</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-02</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-04</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-01</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-02</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-03</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-04</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-05</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-06</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-07</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-08</t>
+  </si>
+  <si>
+    <t>Fonte-SINAPI</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-01</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-02</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-04</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-01</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-02</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-03</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-04</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-05</t>
+  </si>
+  <si>
+    <t>Fonte-Bombeiros-01</t>
+  </si>
+  <si>
+    <t>https://brasil.un.org/pt-br/sdgs</t>
+  </si>
+  <si>
+    <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
+  </si>
+  <si>
+    <t>https://museunacional.ufrj.br/hortobotanico</t>
+  </si>
+  <si>
+    <t>https://www.embrapa.br/florestas/publicacoes</t>
+  </si>
+  <si>
+    <t>https://www.arvoresgigantes.org</t>
+  </si>
+  <si>
+    <t>https://www.scielo.br/j/abb</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/inpa/pt-br/Pesquisa/colecoes/botanica</t>
+  </si>
+  <si>
+    <t>https://botanicasaopaulo.org</t>
+  </si>
+  <si>
+    <t>https://pesquisa.in.gov.br/imprensa</t>
+  </si>
+  <si>
+    <t>https://mapas.florestal.gov.br</t>
+  </si>
+  <si>
+    <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
+  </si>
+  <si>
+    <t>https://somasus.saude.gov.br/sistema/home</t>
+  </si>
+  <si>
+    <t>https://anvisalegis.datalegis.net</t>
+  </si>
+  <si>
+    <t>RDC 611/2022. Radiologia diagnóstica. Blindagem, proteção radiológica.</t>
+  </si>
+  <si>
+    <t>RDC 222/2018. Gerenciamento de resíduos. Plano de gerenciamento obrigatório.</t>
+  </si>
+  <si>
+    <t>NBR 9050. Acessibilidade. Todos os ambientes de uso público.</t>
+  </si>
+  <si>
+    <t>NBR 7256. Climatização em EAS. Obrigatória para CC, CTI, CME, hemodinâmica.</t>
+  </si>
+  <si>
+    <t>NBR 15575. Desempenho de edificações. Conforto térmico, acústico, lumínico.</t>
+  </si>
+  <si>
+    <t>NBR 13534. Instalações elétricas em EAS. Circuitos, aterramento, emergência.</t>
+  </si>
+  <si>
+    <t>NBR 12188. Gases medicinais. Centrais, redes, pontos de uso.</t>
+  </si>
+  <si>
+    <t>Segurança contra incêndio. Varia por estado, consultar regulamento local.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1502,8 +1640,16 @@
       <name val="Arial Nova Cond Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="26">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1654,6 +1800,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -1738,10 +1890,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1971,47 +2124,39 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="75">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="72">
     <dxf>
       <font>
         <b val="0"/>
@@ -2653,6 +2798,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i/>
         <color theme="0" tint="-0.499984740745262"/>
@@ -2678,13 +2833,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3126,11 +3279,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="23" customWidth="1"/>
-    <col min="2" max="2" width="39.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.140625" style="23" customWidth="1"/>
     <col min="3" max="3" width="3.42578125" style="37" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="23"/>
   </cols>
@@ -3143,7 +3296,7 @@
         <v>44</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3154,7 +3307,7 @@
         <v>46</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3162,10 +3315,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3176,7 +3329,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3188,7 +3341,7 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3200,7 +3353,7 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3211,18 +3364,18 @@
         <v>52</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="79" t="s">
         <v>53</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3233,201 +3386,463 @@
         <v>55</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>57</v>
-      </c>
       <c r="C10" s="36" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>58</v>
+        <v>434</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>59</v>
+        <v>435</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>60</v>
+        <v>436</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>61</v>
+        <v>437</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>62</v>
+        <v>438</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>63</v>
+        <v>439</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B18" s="25">
         <f ca="1">NOW()</f>
-        <v>46273.688355787039</v>
+        <v>46276.465924652781</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>90</v>
+      <c r="A20" s="79" t="s">
+        <v>83</v>
       </c>
       <c r="B20" s="24" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones integradas al español e inglés - Las traducciones deben revisarse constantemente</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>92</v>
+      <c r="A21" s="79" t="s">
+        <v>85</v>
       </c>
       <c r="B21" s="24" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","en")</f>
         <v>Built-in Spanish and English Translations - Translations must be constantly reviewed</v>
       </c>
       <c r="C21" s="36" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C24" s="36" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:3" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
-        <v>84</v>
+      <c r="A26" s="79" t="s">
+        <v>77</v>
       </c>
       <c r="B26" s="13" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize GeoTechnical project elements.</v>
       </c>
       <c r="C26" s="36" t="s">
-        <v>89</v>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="79" t="s">
+        <v>440</v>
+      </c>
+      <c r="B27" s="80" t="s">
+        <v>463</v>
+      </c>
+      <c r="C27" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="79" t="s">
+        <v>441</v>
+      </c>
+      <c r="B28" s="81" t="s">
+        <v>464</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="79" t="s">
+        <v>442</v>
+      </c>
+      <c r="B29" s="81" t="s">
+        <v>465</v>
+      </c>
+      <c r="C29" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="79" t="s">
+        <v>443</v>
+      </c>
+      <c r="B30" s="82" t="s">
+        <v>466</v>
+      </c>
+      <c r="C30" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="79" t="s">
+        <v>444</v>
+      </c>
+      <c r="B31" s="83" t="s">
+        <v>467</v>
+      </c>
+      <c r="C31" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="79" t="s">
+        <v>445</v>
+      </c>
+      <c r="B32" s="83" t="s">
+        <v>468</v>
+      </c>
+      <c r="C32" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="79" t="s">
+        <v>446</v>
+      </c>
+      <c r="B33" s="83" t="s">
+        <v>469</v>
+      </c>
+      <c r="C33" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="79" t="s">
+        <v>447</v>
+      </c>
+      <c r="B34" s="84" t="s">
+        <v>470</v>
+      </c>
+      <c r="C34" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="79" t="s">
+        <v>448</v>
+      </c>
+      <c r="B35" s="84" t="s">
+        <v>471</v>
+      </c>
+      <c r="C35" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="79" t="s">
+        <v>449</v>
+      </c>
+      <c r="B36" s="83" t="s">
+        <v>472</v>
+      </c>
+      <c r="C36" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="79" t="s">
+        <v>450</v>
+      </c>
+      <c r="B37" s="84" t="s">
+        <v>473</v>
+      </c>
+      <c r="C37" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="79" t="s">
+        <v>451</v>
+      </c>
+      <c r="B38" s="83" t="s">
+        <v>474</v>
+      </c>
+      <c r="C38" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="79" t="s">
+        <v>452</v>
+      </c>
+      <c r="B39" s="85" t="s">
+        <v>475</v>
+      </c>
+      <c r="C39" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="79" t="s">
+        <v>453</v>
+      </c>
+      <c r="B40" s="85" t="s">
+        <v>476</v>
+      </c>
+      <c r="C40" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="79" t="s">
+        <v>454</v>
+      </c>
+      <c r="B41" s="86" t="s">
+        <v>477</v>
+      </c>
+      <c r="C41" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="79" t="s">
+        <v>455</v>
+      </c>
+      <c r="B42" s="87" t="s">
+        <v>478</v>
+      </c>
+      <c r="C42" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="79" t="s">
+        <v>456</v>
+      </c>
+      <c r="B43" s="87" t="s">
+        <v>479</v>
+      </c>
+      <c r="C43" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="79" t="s">
+        <v>457</v>
+      </c>
+      <c r="B44" s="87" t="s">
+        <v>480</v>
+      </c>
+      <c r="C44" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="79" t="s">
+        <v>458</v>
+      </c>
+      <c r="B45" s="87" t="s">
+        <v>481</v>
+      </c>
+      <c r="C45" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="79" t="s">
+        <v>459</v>
+      </c>
+      <c r="B46" s="87" t="s">
+        <v>482</v>
+      </c>
+      <c r="C46" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="79" t="s">
+        <v>460</v>
+      </c>
+      <c r="B47" s="87" t="s">
+        <v>483</v>
+      </c>
+      <c r="C47" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="79" t="s">
+        <v>461</v>
+      </c>
+      <c r="B48" s="87" t="s">
+        <v>484</v>
+      </c>
+      <c r="C48" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="79" t="s">
+        <v>462</v>
+      </c>
+      <c r="B49" s="87" t="s">
+        <v>485</v>
+      </c>
+      <c r="C49" s="36" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{DA779E44-F107-489D-9C13-D5FE37E1E0D7}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{A1648351-B1CE-4E00-8DC4-BBCD607CB7A8}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{4F4D46F5-73D9-4BF8-8F65-A88D00BF39BD}"/>
+    <hyperlink ref="B39" r:id="rId4" location="categoria_888" xr:uid="{B9ECE629-209C-42AF-A870-DADE1D5EB73D}"/>
+    <hyperlink ref="B40" r:id="rId5" xr:uid="{754937FF-8D8F-4FAA-890C-964399B8A943}"/>
+    <hyperlink ref="B41" r:id="rId6" xr:uid="{BCD1099E-E1E7-4FBD-AB5E-44B9BFDEBB95}"/>
+    <hyperlink ref="B30" r:id="rId7" xr:uid="{74B8FF72-A178-45A6-A789-06E21D569CA0}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -3482,7 +3897,7 @@
         <v>38</v>
       </c>
       <c r="F1" s="47" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G1" s="48" t="s">
         <v>0</v>
@@ -3506,7 +3921,7 @@
         <v>6</v>
       </c>
       <c r="N1" s="29" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="O1" s="29" t="s">
         <v>7</v>
@@ -3518,10 +3933,10 @@
         <v>42</v>
       </c>
       <c r="R1" s="50" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="S1" s="77" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="T1" s="50" t="s">
         <v>33</v>
@@ -3539,22 +3954,22 @@
         <v>8</v>
       </c>
       <c r="Y1" s="49" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="Z1" s="49" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="AA1" s="49" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="AB1" s="49" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="AC1" s="49" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AD1" s="49" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3562,19 +3977,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C2" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D2" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E2" s="51" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F2" s="52" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>9</v>
@@ -3608,13 +4023,13 @@
         <v>Solo Reforçado</v>
       </c>
       <c r="P2" s="21" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="Q2" s="34" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="R2" s="21" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="S2" s="74" t="s">
         <v>9</v>
@@ -3632,7 +4047,7 @@
         <v>Compactação</v>
       </c>
       <c r="W2" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X2" s="54" t="str">
         <f t="shared" ref="X2:X51" si="5">CONCATENATE("Key-GEO-",A2)</f>
@@ -3645,13 +4060,13 @@
         <v>9</v>
       </c>
       <c r="AA2" s="56" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="AB2" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC2" s="21" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AD2" s="62" t="s">
         <v>9</v>
@@ -3662,19 +4077,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C3" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D3" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E3" s="51" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F3" s="52" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>9</v>
@@ -3708,13 +4123,13 @@
         <v>Solo Reforçado Dinamicamente</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="Q3" s="34" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="S3" s="74" t="s">
         <v>9</v>
@@ -3732,7 +4147,7 @@
         <v>Compactação</v>
       </c>
       <c r="W3" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X3" s="54" t="str">
         <f t="shared" si="5"/>
@@ -3745,13 +4160,13 @@
         <v>9</v>
       </c>
       <c r="AA3" s="56" t="s">
+        <v>261</v>
+      </c>
+      <c r="AB3" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC3" s="21" t="s">
         <v>268</v>
-      </c>
-      <c r="AB3" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC3" s="21" t="s">
-        <v>275</v>
       </c>
       <c r="AD3" s="62" t="s">
         <v>9</v>
@@ -3762,19 +4177,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C4" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D4" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E4" s="51" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F4" s="52" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>9</v>
@@ -3808,13 +4223,13 @@
         <v>Solo Reforçado Groute</v>
       </c>
       <c r="P4" s="21" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="Q4" s="34" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="R4" s="21" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="S4" s="74" t="s">
         <v>9</v>
@@ -3832,7 +4247,7 @@
         <v>Compactação</v>
       </c>
       <c r="W4" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X4" s="54" t="str">
         <f t="shared" si="5"/>
@@ -3845,13 +4260,13 @@
         <v>9</v>
       </c>
       <c r="AA4" s="56" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="AB4" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC4" s="21" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AD4" s="62" t="s">
         <v>9</v>
@@ -3862,19 +4277,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D5" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E5" s="51" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F5" s="52" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>9</v>
@@ -3908,13 +4323,13 @@
         <v>Solo Reforçado Substituído</v>
       </c>
       <c r="P5" s="21" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="Q5" s="34" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="R5" s="21" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="S5" s="74" t="s">
         <v>9</v>
@@ -3932,7 +4347,7 @@
         <v>Compactação</v>
       </c>
       <c r="W5" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X5" s="54" t="str">
         <f t="shared" si="5"/>
@@ -3945,13 +4360,13 @@
         <v>9</v>
       </c>
       <c r="AA5" s="56" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="AB5" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC5" s="21" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AD5" s="62" t="s">
         <v>9</v>
@@ -3962,19 +4377,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D6" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E6" s="51" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F6" s="52" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>9</v>
@@ -4008,13 +4423,13 @@
         <v>Solo Reforçado Rolado</v>
       </c>
       <c r="P6" s="21" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="Q6" s="34" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="R6" s="21" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="S6" s="74" t="s">
         <v>9</v>
@@ -4032,7 +4447,7 @@
         <v>Compactação</v>
       </c>
       <c r="W6" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X6" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4045,13 +4460,13 @@
         <v>9</v>
       </c>
       <c r="AA6" s="56" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="AB6" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC6" s="21" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AD6" s="62" t="s">
         <v>9</v>
@@ -4062,19 +4477,19 @@
         <v>7</v>
       </c>
       <c r="B7" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E7" s="51" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F7" s="52" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>9</v>
@@ -4108,13 +4523,13 @@
         <v>Solo Reforçado PréCarregado</v>
       </c>
       <c r="P7" s="21" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="Q7" s="34" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="R7" s="21" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="S7" s="74" t="s">
         <v>9</v>
@@ -4132,7 +4547,7 @@
         <v>Compactação</v>
       </c>
       <c r="W7" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X7" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4145,13 +4560,13 @@
         <v>9</v>
       </c>
       <c r="AA7" s="56" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="AB7" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC7" s="21" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AD7" s="62" t="s">
         <v>9</v>
@@ -4162,19 +4577,19 @@
         <v>8</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E8" s="51" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F8" s="52" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>9</v>
@@ -4208,13 +4623,13 @@
         <v>Solo Reforçado Drenado</v>
       </c>
       <c r="P8" s="21" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="Q8" s="34" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="R8" s="21" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="S8" s="74" t="s">
         <v>9</v>
@@ -4232,7 +4647,7 @@
         <v>Compactação</v>
       </c>
       <c r="W8" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X8" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4245,13 +4660,13 @@
         <v>9</v>
       </c>
       <c r="AA8" s="56" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="AB8" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC8" s="21" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AD8" s="62" t="s">
         <v>9</v>
@@ -4262,19 +4677,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E9" s="51" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="F9" s="52" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>9</v>
@@ -4308,13 +4723,13 @@
         <v>Escavação</v>
       </c>
       <c r="P9" s="21" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="Q9" s="34" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="R9" s="21" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="S9" s="74" t="s">
         <v>9</v>
@@ -4332,7 +4747,7 @@
         <v>Escavações</v>
       </c>
       <c r="W9" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X9" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4345,13 +4760,13 @@
         <v>9</v>
       </c>
       <c r="AA9" s="56" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="AB9" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC9" s="21" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AD9" s="62" t="s">
         <v>9</v>
@@ -4362,19 +4777,19 @@
         <v>10</v>
       </c>
       <c r="B10" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D10" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E10" s="51" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="F10" s="52" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>9</v>
@@ -4408,13 +4823,13 @@
         <v>Escavação Base</v>
       </c>
       <c r="P10" s="21" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="Q10" s="34" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="R10" s="21" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="S10" s="74" t="s">
         <v>9</v>
@@ -4432,7 +4847,7 @@
         <v>Escavações</v>
       </c>
       <c r="W10" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X10" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4445,13 +4860,13 @@
         <v>9</v>
       </c>
       <c r="AA10" s="56" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="AB10" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC10" s="21" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AD10" s="62" t="s">
         <v>9</v>
@@ -4462,19 +4877,19 @@
         <v>11</v>
       </c>
       <c r="B11" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="F11" s="52" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>9</v>
@@ -4508,13 +4923,13 @@
         <v>Escavação Corte</v>
       </c>
       <c r="P11" s="21" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="Q11" s="34" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="R11" s="21" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="S11" s="74" t="s">
         <v>9</v>
@@ -4532,7 +4947,7 @@
         <v>Escavações</v>
       </c>
       <c r="W11" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X11" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4545,13 +4960,13 @@
         <v>9</v>
       </c>
       <c r="AA11" s="56" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="AB11" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC11" s="21" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AD11" s="62" t="s">
         <v>9</v>
@@ -4562,19 +4977,19 @@
         <v>12</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E12" s="51" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="F12" s="52" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>9</v>
@@ -4608,13 +5023,13 @@
         <v>Escavação Dragagem</v>
       </c>
       <c r="P12" s="21" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="Q12" s="34" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="R12" s="21" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="S12" s="74" t="s">
         <v>9</v>
@@ -4632,7 +5047,7 @@
         <v>Escavações</v>
       </c>
       <c r="W12" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X12" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4645,13 +5060,13 @@
         <v>9</v>
       </c>
       <c r="AA12" s="56" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="AB12" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC12" s="21" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AD12" s="62" t="s">
         <v>9</v>
@@ -4662,19 +5077,19 @@
         <v>13</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C13" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="F13" s="52" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>9</v>
@@ -4708,13 +5123,13 @@
         <v>Escavação Terreno</v>
       </c>
       <c r="P13" s="21" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="Q13" s="34" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="R13" s="21" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="S13" s="74" t="s">
         <v>9</v>
@@ -4732,7 +5147,7 @@
         <v>Escavações</v>
       </c>
       <c r="W13" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X13" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4745,13 +5160,13 @@
         <v>9</v>
       </c>
       <c r="AA13" s="56" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AB13" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC13" s="21" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AD13" s="62" t="s">
         <v>9</v>
@@ -4762,19 +5177,19 @@
         <v>14</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C14" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D14" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E14" s="51" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="F14" s="52" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>9</v>
@@ -4808,13 +5223,13 @@
         <v>Escavação SobreEscavação</v>
       </c>
       <c r="P14" s="21" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="Q14" s="34" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="R14" s="21" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="S14" s="74" t="s">
         <v>9</v>
@@ -4832,7 +5247,7 @@
         <v>Escavações</v>
       </c>
       <c r="W14" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X14" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4845,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="AA14" s="56" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="AB14" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC14" s="21" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AD14" s="62" t="s">
         <v>9</v>
@@ -4862,19 +5277,19 @@
         <v>15</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C15" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D15" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="F15" s="52" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>9</v>
@@ -4908,13 +5323,13 @@
         <v>Escavação Fresagem</v>
       </c>
       <c r="P15" s="21" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="Q15" s="34" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="R15" s="21" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="S15" s="74" t="s">
         <v>9</v>
@@ -4932,7 +5347,7 @@
         <v>Escavações</v>
       </c>
       <c r="W15" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X15" s="54" t="str">
         <f t="shared" si="5"/>
@@ -4945,13 +5360,13 @@
         <v>9</v>
       </c>
       <c r="AA15" s="56" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AB15" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC15" s="21" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AD15" s="62" t="s">
         <v>9</v>
@@ -4962,19 +5377,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C16" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D16" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E16" s="51" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="F16" s="52" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>9</v>
@@ -5008,13 +5423,13 @@
         <v>Escavação Banqueta</v>
       </c>
       <c r="P16" s="21" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="Q16" s="34" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="R16" s="21" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="S16" s="74" t="s">
         <v>9</v>
@@ -5032,7 +5447,7 @@
         <v>Escavações</v>
       </c>
       <c r="W16" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X16" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5045,13 +5460,13 @@
         <v>9</v>
       </c>
       <c r="AA16" s="56" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="AB16" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC16" s="21" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AD16" s="62" t="s">
         <v>9</v>
@@ -5062,19 +5477,19 @@
         <v>17</v>
       </c>
       <c r="B17" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C17" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="F17" s="52" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>9</v>
@@ -5108,13 +5523,13 @@
         <v>Escavação Remoção</v>
       </c>
       <c r="P17" s="21" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="Q17" s="34" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="R17" s="21" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="S17" s="74" t="s">
         <v>9</v>
@@ -5132,7 +5547,7 @@
         <v>Escavações</v>
       </c>
       <c r="W17" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X17" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5145,13 +5560,13 @@
         <v>9</v>
       </c>
       <c r="AA17" s="56" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="AB17" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC17" s="21" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AD17" s="62" t="s">
         <v>9</v>
@@ -5162,19 +5577,19 @@
         <v>18</v>
       </c>
       <c r="B18" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C18" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D18" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E18" s="51" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="F18" s="52" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>9</v>
@@ -5208,13 +5623,13 @@
         <v>Escavação Trincheira</v>
       </c>
       <c r="P18" s="21" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="Q18" s="34" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="R18" s="21" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="S18" s="74" t="s">
         <v>9</v>
@@ -5232,7 +5647,7 @@
         <v>Escavações</v>
       </c>
       <c r="W18" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X18" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5245,13 +5660,13 @@
         <v>9</v>
       </c>
       <c r="AA18" s="56" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="AB18" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC18" s="21" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AD18" s="62" t="s">
         <v>9</v>
@@ -5262,19 +5677,19 @@
         <v>19</v>
       </c>
       <c r="B19" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C19" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F19" s="52" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>9</v>
@@ -5308,13 +5723,13 @@
         <v>Terrapleno</v>
       </c>
       <c r="P19" s="21" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="Q19" s="34" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="R19" s="21" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="S19" s="74" t="s">
         <v>9</v>
@@ -5332,7 +5747,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W19" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X19" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5345,13 +5760,13 @@
         <v>9</v>
       </c>
       <c r="AA19" s="56" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="AB19" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC19" s="21" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AD19" s="62" t="s">
         <v>9</v>
@@ -5362,19 +5777,19 @@
         <v>20</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C20" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D20" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E20" s="51" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F20" s="52" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>9</v>
@@ -5408,13 +5823,13 @@
         <v>Aterro Terrapleno</v>
       </c>
       <c r="P20" s="21" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="Q20" s="34" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="R20" s="21" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="S20" s="74" t="s">
         <v>9</v>
@@ -5432,7 +5847,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W20" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X20" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5445,13 +5860,13 @@
         <v>9</v>
       </c>
       <c r="AA20" s="56" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AB20" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC20" s="21" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AD20" s="62" t="s">
         <v>9</v>
@@ -5462,19 +5877,19 @@
         <v>21</v>
       </c>
       <c r="B21" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C21" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D21" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F21" s="52" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>9</v>
@@ -5508,13 +5923,13 @@
         <v>Aterro Reenchimento</v>
       </c>
       <c r="P21" s="21" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="Q21" s="34" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="R21" s="21" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="S21" s="74" t="s">
         <v>9</v>
@@ -5532,7 +5947,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W21" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X21" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5545,13 +5960,13 @@
         <v>9</v>
       </c>
       <c r="AA21" s="56" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="AB21" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC21" s="21" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AD21" s="62" t="s">
         <v>9</v>
@@ -5562,19 +5977,19 @@
         <v>22</v>
       </c>
       <c r="B22" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C22" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D22" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E22" s="51" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F22" s="52" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>9</v>
@@ -5608,13 +6023,13 @@
         <v>Aterro Contrapeso</v>
       </c>
       <c r="P22" s="21" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="Q22" s="34" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="R22" s="21" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="S22" s="74" t="s">
         <v>9</v>
@@ -5632,7 +6047,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W22" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X22" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5645,13 +6060,13 @@
         <v>9</v>
       </c>
       <c r="AA22" s="56" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="AB22" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC22" s="21" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AD22" s="62" t="s">
         <v>9</v>
@@ -5662,19 +6077,19 @@
         <v>23</v>
       </c>
       <c r="B23" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C23" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D23" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F23" s="52" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>9</v>
@@ -5708,13 +6123,13 @@
         <v>Aterro Preenchimento</v>
       </c>
       <c r="P23" s="21" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="Q23" s="34" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="R23" s="21" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="S23" s="74" t="s">
         <v>9</v>
@@ -5732,7 +6147,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W23" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X23" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5745,13 +6160,13 @@
         <v>9</v>
       </c>
       <c r="AA23" s="56" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="AB23" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC23" s="21" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AD23" s="62" t="s">
         <v>9</v>
@@ -5762,19 +6177,19 @@
         <v>24</v>
       </c>
       <c r="B24" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C24" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D24" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E24" s="51" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F24" s="52" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>9</v>
@@ -5808,13 +6223,13 @@
         <v>Aterro Inclinado</v>
       </c>
       <c r="P24" s="21" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="Q24" s="34" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="R24" s="21" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="S24" s="74" t="s">
         <v>9</v>
@@ -5832,7 +6247,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W24" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X24" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5845,13 +6260,13 @@
         <v>9</v>
       </c>
       <c r="AA24" s="56" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="AB24" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC24" s="21" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AD24" s="62" t="s">
         <v>9</v>
@@ -5862,19 +6277,19 @@
         <v>25</v>
       </c>
       <c r="B25" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C25" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F25" s="52" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>9</v>
@@ -5908,13 +6323,13 @@
         <v>Aterro Subterrâneo</v>
       </c>
       <c r="P25" s="21" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="Q25" s="34" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="R25" s="21" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="S25" s="74" t="s">
         <v>9</v>
@@ -5932,7 +6347,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W25" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X25" s="54" t="str">
         <f t="shared" si="5"/>
@@ -5945,13 +6360,13 @@
         <v>9</v>
       </c>
       <c r="AA25" s="56" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AB25" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC25" s="21" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AD25" s="62" t="s">
         <v>9</v>
@@ -5962,19 +6377,19 @@
         <v>26</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C26" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D26" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E26" s="51" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F26" s="52" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>9</v>
@@ -6008,13 +6423,13 @@
         <v>Aterro Camada</v>
       </c>
       <c r="P26" s="21" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="Q26" s="34" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="R26" s="21" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="S26" s="74" t="s">
         <v>9</v>
@@ -6032,7 +6447,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W26" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X26" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6045,13 +6460,13 @@
         <v>9</v>
       </c>
       <c r="AA26" s="56" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="AB26" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC26" s="21" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AD26" s="62" t="s">
         <v>9</v>
@@ -6062,19 +6477,19 @@
         <v>27</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C27" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D27" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F27" s="52" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>9</v>
@@ -6108,13 +6523,13 @@
         <v>Aterro Transição</v>
       </c>
       <c r="P27" s="21" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="Q27" s="34" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="R27" s="21" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="S27" s="74" t="s">
         <v>9</v>
@@ -6132,7 +6547,7 @@
         <v>Terraplenagens</v>
       </c>
       <c r="W27" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X27" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6145,13 +6560,13 @@
         <v>9</v>
       </c>
       <c r="AA27" s="56" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="AB27" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC27" s="21" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AD27" s="62" t="s">
         <v>9</v>
@@ -6162,19 +6577,19 @@
         <v>28</v>
       </c>
       <c r="B28" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C28" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D28" s="51" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E28" s="42" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="F28" s="42" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>9</v>
@@ -6208,13 +6623,13 @@
         <v>Ponto Interno</v>
       </c>
       <c r="P28" s="34" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="Q28" s="34" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="R28" s="21" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="S28" s="74" t="s">
         <v>9</v>
@@ -6232,26 +6647,26 @@
         <v>Pontos.do.Modelo</v>
       </c>
       <c r="W28" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X28" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-28</v>
       </c>
       <c r="Y28" s="21" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="Z28" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AA28" s="21" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="AB28" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC28" s="21" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AD28" s="62" t="s">
         <v>9</v>
@@ -6262,19 +6677,19 @@
         <v>29</v>
       </c>
       <c r="B29" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C29" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D29" s="51" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="F29" s="42" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>9</v>
@@ -6308,13 +6723,13 @@
         <v>Ponto Perimetral</v>
       </c>
       <c r="P29" s="34" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="Q29" s="34" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="R29" s="21" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="S29" s="74" t="s">
         <v>9</v>
@@ -6332,26 +6747,26 @@
         <v>Pontos.do.Modelo</v>
       </c>
       <c r="W29" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X29" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-29</v>
       </c>
       <c r="Y29" s="21" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="Z29" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AA29" s="21" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="AB29" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC29" s="21" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AD29" s="62" t="s">
         <v>9</v>
@@ -6362,19 +6777,19 @@
         <v>30</v>
       </c>
       <c r="B30" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C30" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D30" s="51" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E30" s="42" t="s">
+        <v>196</v>
+      </c>
+      <c r="F30" s="42" t="s">
         <v>203</v>
-      </c>
-      <c r="F30" s="42" t="s">
-        <v>210</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>9</v>
@@ -6408,13 +6823,13 @@
         <v>Ponto Região</v>
       </c>
       <c r="P30" s="21" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="Q30" s="34" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="R30" s="21" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="S30" s="74" t="s">
         <v>9</v>
@@ -6432,26 +6847,26 @@
         <v>Pontos.do.Modelo</v>
       </c>
       <c r="W30" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X30" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-30</v>
       </c>
       <c r="Y30" s="21" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="Z30" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AA30" s="21" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="AB30" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC30" s="21" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AD30" s="62" t="s">
         <v>9</v>
@@ -6462,19 +6877,19 @@
         <v>31</v>
       </c>
       <c r="B31" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C31" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D31" s="51" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E31" s="42" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="F31" s="42" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>9</v>
@@ -6508,13 +6923,13 @@
         <v>Ponto Superfície</v>
       </c>
       <c r="P31" s="21" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="Q31" s="34" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="R31" s="21" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="S31" s="74" t="s">
         <v>9</v>
@@ -6532,26 +6947,26 @@
         <v>Pontos.do.Modelo</v>
       </c>
       <c r="W31" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X31" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-31</v>
       </c>
       <c r="Y31" s="21" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="Z31" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AA31" s="21" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="AB31" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC31" s="21" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AD31" s="62" t="s">
         <v>9</v>
@@ -6562,19 +6977,19 @@
         <v>32</v>
       </c>
       <c r="B32" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C32" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D32" s="51" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E32" s="51" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F32" s="42" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>9</v>
@@ -6608,13 +7023,13 @@
         <v>Ponto Sondagem</v>
       </c>
       <c r="P32" s="21" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="Q32" s="34" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="R32" s="21" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="S32" s="74" t="s">
         <v>9</v>
@@ -6632,7 +7047,7 @@
         <v>Sondagens</v>
       </c>
       <c r="W32" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X32" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6645,13 +7060,13 @@
         <v>9</v>
       </c>
       <c r="AA32" s="56" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AB32" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC32" s="21" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AD32" s="62" t="s">
         <v>9</v>
@@ -6662,19 +7077,19 @@
         <v>33</v>
       </c>
       <c r="B33" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C33" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D33" s="51" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F33" s="42" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>9</v>
@@ -6708,13 +7123,13 @@
         <v>Ponto Sondagem Definido</v>
       </c>
       <c r="P33" s="21" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="Q33" s="34" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="R33" s="21" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="S33" s="74" t="s">
         <v>9</v>
@@ -6732,7 +7147,7 @@
         <v>Sondagens</v>
       </c>
       <c r="W33" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X33" s="54" t="str">
         <f t="shared" si="5"/>
@@ -6745,13 +7160,13 @@
         <v>9</v>
       </c>
       <c r="AA33" s="56" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="AB33" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC33" s="21" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AD33" s="62" t="s">
         <v>9</v>
@@ -6762,19 +7177,19 @@
         <v>34</v>
       </c>
       <c r="B34" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C34" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D34" s="51" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F34" s="42" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>9</v>
@@ -6808,13 +7223,13 @@
         <v>Topografia Sólida</v>
       </c>
       <c r="P34" s="34" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="Q34" s="34" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="R34" s="21" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="S34" s="74" t="s">
         <v>9</v>
@@ -6832,26 +7247,26 @@
         <v>Topografia</v>
       </c>
       <c r="W34" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X34" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-34</v>
       </c>
       <c r="Y34" s="21" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="Z34" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AA34" s="21" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="AB34" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC34" s="21" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AD34" s="62" t="s">
         <v>9</v>
@@ -6862,19 +7277,19 @@
         <v>35</v>
       </c>
       <c r="B35" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C35" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D35" s="51" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E35" s="42" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F35" s="42" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>9</v>
@@ -6908,13 +7323,13 @@
         <v>Topografia Malha</v>
       </c>
       <c r="P35" s="34" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="Q35" s="34" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="R35" s="21" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="S35" s="74" t="s">
         <v>9</v>
@@ -6932,26 +7347,26 @@
         <v>Topografia</v>
       </c>
       <c r="W35" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X35" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-35</v>
       </c>
       <c r="Y35" s="21" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="Z35" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AA35" s="21" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="AB35" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC35" s="21" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AD35" s="62" t="s">
         <v>9</v>
@@ -6962,19 +7377,19 @@
         <v>36</v>
       </c>
       <c r="B36" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C36" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D36" s="51" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E36" s="42" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F36" s="42" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>9</v>
@@ -7008,13 +7423,13 @@
         <v>Topografia Sólida Núcleo</v>
       </c>
       <c r="P36" s="34" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="Q36" s="34" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="R36" s="21" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="S36" s="74" t="s">
         <v>9</v>
@@ -7032,26 +7447,26 @@
         <v>Topografia</v>
       </c>
       <c r="W36" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X36" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-36</v>
       </c>
       <c r="Y36" s="21" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="Z36" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AA36" s="21" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="AB36" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC36" s="21" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AD36" s="62" t="s">
         <v>9</v>
@@ -7062,19 +7477,19 @@
         <v>37</v>
       </c>
       <c r="B37" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C37" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D37" s="51" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E37" s="42" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F37" s="42" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>9</v>
@@ -7108,13 +7523,13 @@
         <v>Topografia Sólida Substrato</v>
       </c>
       <c r="P37" s="34" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="Q37" s="34" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="R37" s="21" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="S37" s="74" t="s">
         <v>9</v>
@@ -7132,26 +7547,26 @@
         <v>Topografia</v>
       </c>
       <c r="W37" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X37" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-37</v>
       </c>
       <c r="Y37" s="21" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="Z37" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AA37" s="21" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="AB37" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC37" s="21" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AD37" s="62" t="s">
         <v>9</v>
@@ -7162,19 +7577,19 @@
         <v>38</v>
       </c>
       <c r="B38" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C38" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D38" s="51" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E38" s="42" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F38" s="42" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>9</v>
@@ -7208,13 +7623,13 @@
         <v>Topografia Sólida Membrana</v>
       </c>
       <c r="P38" s="34" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="Q38" s="34" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="R38" s="21" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="S38" s="74" t="s">
         <v>9</v>
@@ -7232,26 +7647,26 @@
         <v>Topografia</v>
       </c>
       <c r="W38" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X38" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-38</v>
       </c>
       <c r="Y38" s="21" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="Z38" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AA38" s="21" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="AB38" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC38" s="21" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AD38" s="62" t="s">
         <v>9</v>
@@ -7262,19 +7677,19 @@
         <v>39</v>
       </c>
       <c r="B39" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C39" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D39" s="51" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E39" s="42" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F39" s="42" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>9</v>
@@ -7308,13 +7723,13 @@
         <v>Topografia Sólida Isolamento</v>
       </c>
       <c r="P39" s="34" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="Q39" s="34" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="R39" s="21" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="S39" s="74" t="s">
         <v>9</v>
@@ -7332,26 +7747,26 @@
         <v>Topografia</v>
       </c>
       <c r="W39" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X39" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-39</v>
       </c>
       <c r="Y39" s="21" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Z39" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AA39" s="21" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="AB39" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC39" s="21" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AD39" s="62" t="s">
         <v>9</v>
@@ -7362,19 +7777,19 @@
         <v>40</v>
       </c>
       <c r="B40" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C40" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D40" s="51" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E40" s="42" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F40" s="42" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>9</v>
@@ -7408,13 +7823,13 @@
         <v>Topografia Sólida Superfície</v>
       </c>
       <c r="P40" s="34" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="Q40" s="34" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="R40" s="21" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="S40" s="74" t="s">
         <v>9</v>
@@ -7432,26 +7847,26 @@
         <v>Topografia</v>
       </c>
       <c r="W40" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X40" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-40</v>
       </c>
       <c r="Y40" s="21" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="Z40" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AA40" s="21" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="AB40" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC40" s="21" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AD40" s="62" t="s">
         <v>9</v>
@@ -7462,19 +7877,19 @@
         <v>41</v>
       </c>
       <c r="B41" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C41" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D41" s="51" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E41" s="42" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F41" s="42" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>9</v>
@@ -7508,13 +7923,13 @@
         <v>Topografia Sólida Agua</v>
       </c>
       <c r="P41" s="34" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="Q41" s="34" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="R41" s="21" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="S41" s="74" t="s">
         <v>9</v>
@@ -7532,26 +7947,26 @@
         <v>Topografia</v>
       </c>
       <c r="W41" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X41" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-41</v>
       </c>
       <c r="Y41" s="21" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="Z41" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AA41" s="21" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="AB41" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC41" s="21" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AD41" s="62" t="s">
         <v>9</v>
@@ -7562,19 +7977,19 @@
         <v>42</v>
       </c>
       <c r="B42" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C42" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D42" s="51" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E42" s="42" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F42" s="42" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>9</v>
@@ -7608,13 +8023,13 @@
         <v>Topografia Sólida Vazio</v>
       </c>
       <c r="P42" s="21" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="Q42" s="34" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="R42" s="21" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="S42" s="74" t="s">
         <v>9</v>
@@ -7632,26 +8047,26 @@
         <v>Topografia</v>
       </c>
       <c r="W42" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X42" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-42</v>
       </c>
       <c r="Y42" s="56" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="Z42" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AA42" s="56" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="AB42" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC42" s="21" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AD42" s="62" t="s">
         <v>9</v>
@@ -7662,19 +8077,19 @@
         <v>43</v>
       </c>
       <c r="B43" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C43" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D43" s="51" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="E43" s="42" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="F43" s="42" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>9</v>
@@ -7708,13 +8123,13 @@
         <v>Curva de 10</v>
       </c>
       <c r="P43" s="34" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="Q43" s="34" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="R43" s="21" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="S43" s="74" t="s">
         <v>9</v>
@@ -7732,26 +8147,26 @@
         <v>Curvas.de.Nível</v>
       </c>
       <c r="W43" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X43" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-43</v>
       </c>
       <c r="Y43" s="21" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="Z43" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AA43" s="21" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="AB43" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC43" s="21" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AD43" s="62" t="s">
         <v>9</v>
@@ -7762,19 +8177,19 @@
         <v>44</v>
       </c>
       <c r="B44" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C44" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D44" s="51" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="E44" s="42" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="F44" s="42" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>9</v>
@@ -7808,13 +8223,13 @@
         <v>Curva de 05</v>
       </c>
       <c r="P44" s="34" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="Q44" s="34" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="R44" s="21" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="S44" s="74" t="s">
         <v>9</v>
@@ -7832,26 +8247,26 @@
         <v>Curvas.de.Nível</v>
       </c>
       <c r="W44" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X44" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-44</v>
       </c>
       <c r="Y44" s="21" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="Z44" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AA44" s="21" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="AB44" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC44" s="21" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AD44" s="62" t="s">
         <v>9</v>
@@ -7862,19 +8277,19 @@
         <v>45</v>
       </c>
       <c r="B45" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C45" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D45" s="51" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="E45" s="42" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="F45" s="42" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>9</v>
@@ -7908,13 +8323,13 @@
         <v>Curva de 01</v>
       </c>
       <c r="P45" s="34" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="Q45" s="34" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="R45" s="21" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="S45" s="74" t="s">
         <v>9</v>
@@ -7932,26 +8347,26 @@
         <v>Curvas.de.Nível</v>
       </c>
       <c r="W45" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X45" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-45</v>
       </c>
       <c r="Y45" s="21" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z45" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AA45" s="21" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="AB45" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC45" s="21" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AD45" s="62" t="s">
         <v>9</v>
@@ -7962,19 +8377,19 @@
         <v>46</v>
       </c>
       <c r="B46" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C46" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D46" s="51" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E46" s="51" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="F46" s="51" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>9</v>
@@ -8008,13 +8423,13 @@
         <v>Divisa</v>
       </c>
       <c r="P46" s="21" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="Q46" s="34" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="R46" s="21" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="S46" s="74" t="s">
         <v>9</v>
@@ -8032,26 +8447,26 @@
         <v>Loteamento</v>
       </c>
       <c r="W46" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X46" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-46</v>
       </c>
       <c r="Y46" s="21" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="Z46" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AA46" s="21" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="AB46" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC46" s="21" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AD46" s="62" t="s">
         <v>9</v>
@@ -8062,19 +8477,19 @@
         <v>47</v>
       </c>
       <c r="B47" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C47" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D47" s="51" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E47" s="51" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="F47" s="51" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>9</v>
@@ -8108,13 +8523,13 @@
         <v>Divisa Segmento</v>
       </c>
       <c r="P47" s="21" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="Q47" s="34" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="R47" s="21" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="S47" s="74" t="s">
         <v>9</v>
@@ -8132,26 +8547,26 @@
         <v>Loteamento</v>
       </c>
       <c r="W47" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X47" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-47</v>
       </c>
       <c r="Y47" s="41" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="Z47" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AA47" s="21" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="AB47" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC47" s="21" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AD47" s="62" t="s">
         <v>9</v>
@@ -8162,19 +8577,19 @@
         <v>48</v>
       </c>
       <c r="B48" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C48" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D48" s="51" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E48" s="51" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F48" s="52" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>9</v>
@@ -8208,13 +8623,13 @@
         <v>Paisagístico</v>
       </c>
       <c r="P48" s="21" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="Q48" s="34" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="R48" s="21" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="S48" s="74" t="s">
         <v>9</v>
@@ -8232,26 +8647,26 @@
         <v>Paisagismo</v>
       </c>
       <c r="W48" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X48" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-48</v>
       </c>
       <c r="Y48" s="56" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="Z48" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AA48" s="56" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="AB48" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC48" s="21" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="AD48" s="62" t="s">
         <v>9</v>
@@ -8262,19 +8677,19 @@
         <v>49</v>
       </c>
       <c r="B49" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C49" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D49" s="51" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E49" s="51" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F49" s="52" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>9</v>
@@ -8308,13 +8723,13 @@
         <v>Pavimentação</v>
       </c>
       <c r="P49" s="21" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="Q49" s="34" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="R49" s="21" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="S49" s="74" t="s">
         <v>9</v>
@@ -8332,7 +8747,7 @@
         <v>Paisagismo</v>
       </c>
       <c r="W49" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X49" s="54" t="str">
         <f t="shared" si="5"/>
@@ -8345,13 +8760,13 @@
         <v>9</v>
       </c>
       <c r="AA49" s="56" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="AB49" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC49" s="21" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="AD49" s="62" t="s">
         <v>9</v>
@@ -8362,19 +8777,19 @@
         <v>50</v>
       </c>
       <c r="B50" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C50" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D50" s="51" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E50" s="51" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F50" s="51" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>9</v>
@@ -8408,13 +8823,13 @@
         <v>Estacionamento</v>
       </c>
       <c r="P50" s="21" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="Q50" s="34" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="R50" s="21" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="S50" s="74" t="s">
         <v>9</v>
@@ -8432,26 +8847,26 @@
         <v>Paisagismo</v>
       </c>
       <c r="W50" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X50" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-50</v>
       </c>
       <c r="Y50" s="21" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Z50" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AA50" s="56" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="AB50" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC50" s="21" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="AD50" s="62" t="s">
         <v>9</v>
@@ -8462,19 +8877,19 @@
         <v>51</v>
       </c>
       <c r="B51" s="51" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C51" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D51" s="51" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E51" s="51" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F51" s="52" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>9</v>
@@ -8508,13 +8923,13 @@
         <v>Vegetação</v>
       </c>
       <c r="P51" s="21" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="Q51" s="34" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="R51" s="21" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="S51" s="74" t="s">
         <v>9</v>
@@ -8532,26 +8947,26 @@
         <v>Paisagismo</v>
       </c>
       <c r="W51" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X51" s="54" t="str">
         <f t="shared" si="5"/>
         <v>Key-GEO-51</v>
       </c>
       <c r="Y51" s="56" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="Z51" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AA51" s="56" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="AB51" s="62" t="s">
         <v>9</v>
       </c>
       <c r="AC51" s="21" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="AD51" s="62" t="s">
         <v>9</v>
@@ -8562,19 +8977,19 @@
         <v>52</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="C52" s="59" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="D52" s="59" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="E52" s="59" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="F52" s="59" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="G52" s="60" t="s">
         <v>9</v>
@@ -8592,7 +9007,7 @@
         <v>9</v>
       </c>
       <c r="L52" s="61" t="str">
-        <f t="shared" ref="L52:O57" si="13">SUBSTITUTE(CONCATENATE("", C52), ".", " ")</f>
+        <f t="shared" ref="L52" si="13">SUBSTITUTE(CONCATENATE("", C52), ".", " ")</f>
         <v>De Geotécnica</v>
       </c>
       <c r="M52" s="61" t="str">
@@ -8608,13 +9023,13 @@
         <v>Terreno</v>
       </c>
       <c r="P52" s="61" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="Q52" s="61" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="R52" s="18" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="S52" s="74" t="s">
         <v>9</v>
@@ -8632,7 +9047,7 @@
         <v>Solos</v>
       </c>
       <c r="W52" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X52" s="54" t="str">
         <f t="shared" ref="X52:X57" si="20">CONCATENATE("Key-GEO-",A52)</f>
@@ -8662,19 +9077,19 @@
         <v>53</v>
       </c>
       <c r="B53" s="58" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="C53" s="59" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="D53" s="59" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="E53" s="59" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="F53" s="59" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="G53" s="60" t="s">
         <v>9</v>
@@ -8708,13 +9123,13 @@
         <v>Função Auxiliar</v>
       </c>
       <c r="P53" s="18" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="Q53" s="18" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="R53" s="18" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="S53" s="74" t="s">
         <v>9</v>
@@ -8732,7 +9147,7 @@
         <v>API Método</v>
       </c>
       <c r="W53" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X53" s="54" t="str">
         <f t="shared" si="20"/>
@@ -8762,19 +9177,19 @@
         <v>54</v>
       </c>
       <c r="B54" s="58" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="C54" s="59" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="D54" s="59" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="E54" s="59" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="F54" s="59" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="G54" s="60" t="s">
         <v>9</v>
@@ -8808,13 +9223,13 @@
         <v>Função Global</v>
       </c>
       <c r="P54" s="18" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="Q54" s="18" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="R54" s="18" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="S54" s="74" t="s">
         <v>9</v>
@@ -8832,7 +9247,7 @@
         <v>API Método</v>
       </c>
       <c r="W54" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X54" s="54" t="str">
         <f t="shared" si="20"/>
@@ -8862,19 +9277,19 @@
         <v>55</v>
       </c>
       <c r="B55" s="58" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="C55" s="59" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="D55" s="59" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="E55" s="59" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="F55" s="59" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="G55" s="60" t="s">
         <v>9</v>
@@ -8908,13 +9323,13 @@
         <v>Função Local</v>
       </c>
       <c r="P55" s="18" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="Q55" s="18" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="R55" s="18" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="S55" s="74" t="s">
         <v>9</v>
@@ -8932,7 +9347,7 @@
         <v>API Método</v>
       </c>
       <c r="W55" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X55" s="54" t="str">
         <f t="shared" si="20"/>
@@ -8962,19 +9377,19 @@
         <v>56</v>
       </c>
       <c r="B56" s="58" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="C56" s="59" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="D56" s="59" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="E56" s="59" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="F56" s="59" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="G56" s="60" t="s">
         <v>9</v>
@@ -9008,13 +9423,13 @@
         <v>Função Filtro</v>
       </c>
       <c r="P56" s="18" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="Q56" s="18" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="R56" s="18" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="S56" s="74" t="s">
         <v>9</v>
@@ -9032,7 +9447,7 @@
         <v>API Método</v>
       </c>
       <c r="W56" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X56" s="54" t="str">
         <f t="shared" si="20"/>
@@ -9062,19 +9477,19 @@
         <v>57</v>
       </c>
       <c r="B57" s="58" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="C57" s="59" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="D57" s="59" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="E57" s="59" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="F57" s="59" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="G57" s="60" t="s">
         <v>9</v>
@@ -9108,13 +9523,13 @@
         <v>Bloco de Código</v>
       </c>
       <c r="P57" s="18" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="Q57" s="18" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="R57" s="18" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="S57" s="74" t="s">
         <v>9</v>
@@ -9132,7 +9547,7 @@
         <v>API Método Visual</v>
       </c>
       <c r="W57" s="21" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X57" s="54" t="str">
         <f t="shared" si="20"/>
@@ -9163,129 +9578,129 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:B52 A53:A57">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:X1048576 A1:Q1 S1:X1 C2:E2 P2 AE2:XFD2 D3:E8 C3:C51 D9:D27">
-    <cfRule type="cellIs" dxfId="74" priority="265" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="265" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F27">
-    <cfRule type="duplicateValues" dxfId="72" priority="1053"/>
-    <cfRule type="cellIs" dxfId="71" priority="71" operator="equal">
+    <cfRule type="duplicateValues" dxfId="69" priority="1053"/>
+    <cfRule type="cellIs" dxfId="68" priority="71" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28:F45 Q2:Q51 P28:P29 AE28:XFD29 P34:P41 AE34:XFD41 P43:P45 AE43:XFD45">
-    <cfRule type="cellIs" dxfId="70" priority="132" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="132" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28:F45">
-    <cfRule type="duplicateValues" dxfId="69" priority="1035"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="1034"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="1032"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="1035"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="1034"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="1032"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F46:F47">
-    <cfRule type="duplicateValues" dxfId="66" priority="1002"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="1002"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F51">
-    <cfRule type="duplicateValues" dxfId="65" priority="1038"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="1038"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52">
-    <cfRule type="duplicateValues" dxfId="64" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F53:F57">
+    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F58:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="62" priority="266"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="266"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F58:F1048576 F1:F51">
-    <cfRule type="duplicateValues" dxfId="61" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F58:F1048576">
-    <cfRule type="duplicateValues" dxfId="60" priority="795"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="782"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="775"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="767"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="795"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="782"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="775"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="767"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="258"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R52">
-    <cfRule type="cellIs" dxfId="55" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X58:X1048576 X1">
-    <cfRule type="duplicateValues" dxfId="54" priority="594"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="594"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y50">
-    <cfRule type="duplicateValues" dxfId="53" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="duplicateValues" dxfId="49" priority="96"/>
-    <cfRule type="cellIs" dxfId="48" priority="95" operator="equal">
+    <cfRule type="duplicateValues" dxfId="45" priority="96"/>
+    <cfRule type="cellIs" dxfId="44" priority="95" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA3">
-    <cfRule type="duplicateValues" dxfId="47" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="93"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="91"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA3:AA8 AA17:AA27 AA10:AA14">
-    <cfRule type="duplicateValues" dxfId="43" priority="1050"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="1050"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA4:AA8 AA19:AA27 AA10:AA14">
-    <cfRule type="duplicateValues" dxfId="42" priority="1047"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="1047"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA4:AA8 AA19:AA27">
-    <cfRule type="duplicateValues" dxfId="41" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA9">
-    <cfRule type="duplicateValues" dxfId="40" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA10:AA14">
-    <cfRule type="duplicateValues" dxfId="35" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA15:AA16">
-    <cfRule type="duplicateValues" dxfId="31" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA17:AA18">
-    <cfRule type="duplicateValues" dxfId="23" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA19:AA27">
-    <cfRule type="duplicateValues" dxfId="18" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1:XFD1 AB58:XFD1048576">
-    <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F53:F57">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9435,7 +9850,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9463,22 +9878,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9507,15 +9922,15 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="15" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -9551,97 +9966,97 @@
         <v>10</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D1" s="40" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>44</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>44</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="I1" s="27" t="s">
         <v>44</v>
       </c>
       <c r="J1" s="27" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="K1" s="27" t="s">
         <v>44</v>
       </c>
       <c r="L1" s="40" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="M1" s="40" t="s">
         <v>44</v>
       </c>
       <c r="N1" s="40" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="O1" s="40" t="s">
         <v>44</v>
       </c>
       <c r="P1" s="40" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="Q1" s="40" t="s">
         <v>44</v>
       </c>
       <c r="R1" s="40" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="S1" s="40" t="s">
         <v>44</v>
       </c>
       <c r="T1" s="40" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="U1" s="40" t="s">
         <v>44</v>
       </c>
       <c r="V1" s="40" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="W1" s="40" t="s">
         <v>44</v>
       </c>
       <c r="X1" s="40" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="Y1" s="40" t="s">
         <v>44</v>
       </c>
       <c r="Z1" s="40" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="AA1" s="40" t="s">
         <v>44</v>
       </c>
       <c r="AB1" s="40" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="AC1" s="40" t="s">
         <v>44</v>
       </c>
       <c r="AD1" s="40" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="AE1" s="40" t="s">
         <v>44</v>
       </c>
       <c r="AF1" s="40" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="AG1" s="40" t="s">
         <v>44</v>
@@ -9652,10 +10067,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="C2" s="55" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D2" s="64" t="s">
         <v>9</v>
@@ -9670,16 +10085,16 @@
         <v>9</v>
       </c>
       <c r="H2" s="38" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="I2" s="45" t="s">
+        <v>364</v>
+      </c>
+      <c r="J2" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="K2" s="39" t="s">
         <v>371</v>
-      </c>
-      <c r="J2" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="K2" s="39" t="s">
-        <v>378</v>
       </c>
       <c r="L2" s="69" t="s">
         <v>9</v>
@@ -9753,10 +10168,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="C3" s="59" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="D3" s="64" t="s">
         <v>9</v>
@@ -9777,29 +10192,29 @@
         <v>9</v>
       </c>
       <c r="J3" s="68" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="K3" s="67" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="L3" s="69" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="M3" s="45" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="N3" s="69" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="O3" s="45" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="P3" s="71" t="str">
         <f t="shared" ref="P3:P7" si="0">IF(Q3="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
       <c r="Q3" s="72" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="R3" s="66" t="s">
         <v>9</v>
@@ -9855,10 +10270,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="C4" s="59" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="D4" s="64" t="s">
         <v>9</v>
@@ -9879,29 +10294,29 @@
         <v>9</v>
       </c>
       <c r="J4" s="68" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="K4" s="67" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="L4" s="69" t="s">
+        <v>379</v>
+      </c>
+      <c r="M4" s="45" t="s">
+        <v>380</v>
+      </c>
+      <c r="N4" s="69" t="s">
+        <v>381</v>
+      </c>
+      <c r="O4" s="45" t="s">
         <v>386</v>
-      </c>
-      <c r="M4" s="45" t="s">
-        <v>387</v>
-      </c>
-      <c r="N4" s="69" t="s">
-        <v>388</v>
-      </c>
-      <c r="O4" s="45" t="s">
-        <v>393</v>
       </c>
       <c r="P4" s="71" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q4" s="72" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="R4" s="66" t="s">
         <v>9</v>
@@ -9957,10 +10372,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="D5" s="64" t="s">
         <v>9</v>
@@ -9981,29 +10396,29 @@
         <v>9</v>
       </c>
       <c r="J5" s="68" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="K5" s="67" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="L5" s="69" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="M5" s="45" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="N5" s="69" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="O5" s="45" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="P5" s="71" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q5" s="72" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="R5" s="66" t="s">
         <v>9</v>
@@ -10059,10 +10474,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="D6" s="64" t="s">
         <v>9</v>
@@ -10083,29 +10498,29 @@
         <v>9</v>
       </c>
       <c r="J6" s="68" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="K6" s="67" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="L6" s="69" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="M6" s="45" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="N6" s="69" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="O6" s="45" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="P6" s="71" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q6" s="72" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="R6" s="66" t="s">
         <v>9</v>
@@ -10161,10 +10576,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="C7" s="59" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="D7" s="64" t="s">
         <v>9</v>
@@ -10185,29 +10600,29 @@
         <v>9</v>
       </c>
       <c r="J7" s="68" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="K7" s="67" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="L7" s="69" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="M7" s="45" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="N7" s="69" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="O7" s="45" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="P7" s="71" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q7" s="72" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="R7" s="66" t="s">
         <v>9</v>
@@ -10261,35 +10676,35 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1 A2:B2 A8:XFD1048576 H2:O2 AH2:XFD2 A3:A7">
-    <cfRule type="cellIs" dxfId="12" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B2 B8:B1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="1031"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1031"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B7">
-    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:G7">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:I7">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:Q2">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:AG7">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
